--- a/research/traditional_assets/database/data/france/france_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/france/france_rubber_tires.xlsx
@@ -650,10 +650,10 @@
         <v>0.1086519539308118</v>
       </c>
       <c r="X2">
-        <v>0.1014253056371165</v>
+        <v>0.1013993280709772</v>
       </c>
       <c r="Y2">
-        <v>0.007226648293695265</v>
+        <v>0.007252625859834563</v>
       </c>
       <c r="Z2">
         <v>1.354557674344429</v>
@@ -662,10 +662,10 @@
         <v>0.1318251962925333</v>
       </c>
       <c r="AB2">
-        <v>0.08682023955504249</v>
+        <v>0.08680109836395217</v>
       </c>
       <c r="AC2">
-        <v>0.04500495673749084</v>
+        <v>0.04502409792858117</v>
       </c>
       <c r="AD2">
         <v>8298.5</v>
@@ -787,10 +787,10 @@
         <v>0.1086519539308118</v>
       </c>
       <c r="X3">
-        <v>0.1014253056371165</v>
+        <v>0.1013993280709772</v>
       </c>
       <c r="Y3">
-        <v>0.007226648293695265</v>
+        <v>0.007252625859834563</v>
       </c>
       <c r="Z3">
         <v>1.354557674344429</v>
@@ -799,10 +799,10 @@
         <v>0.1318251962925333</v>
       </c>
       <c r="AB3">
-        <v>0.08682023955504249</v>
+        <v>0.08680109836395217</v>
       </c>
       <c r="AC3">
-        <v>0.04500495673749084</v>
+        <v>0.04502409792858117</v>
       </c>
       <c r="AD3">
         <v>8298.5</v>
@@ -1139,49 +1139,49 @@
         <v>13.8812594840668</v>
       </c>
       <c r="F2">
-        <v>3.02956998679044</v>
+        <v>3.0078097595142</v>
       </c>
       <c r="G2">
         <v>1.48628076082674</v>
       </c>
       <c r="H2">
-        <v>3.3886341655622</v>
+        <v>3.55806587384031</v>
       </c>
       <c r="I2">
         <v>0.263164571011781</v>
       </c>
       <c r="J2">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="K2">
         <v>23235</v>
       </c>
       <c r="L2">
-        <v>14431.2584511842</v>
+        <v>14698.1367100107</v>
       </c>
       <c r="M2">
         <v>28231.2</v>
       </c>
       <c r="N2">
-        <v>30049.0584511842</v>
+        <v>31261.9417100107</v>
       </c>
       <c r="O2">
         <v>8298.5</v>
       </c>
       <c r="P2">
-        <v>18920.1</v>
+        <v>19866.105</v>
       </c>
       <c r="Q2">
-        <v>0.08682023955504251</v>
+        <v>0.08680109836395219</v>
       </c>
       <c r="R2">
-        <v>0.08433866465758361</v>
+        <v>0.0828261776721869</v>
       </c>
       <c r="S2">
         <v>0.0459274624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.101425305637117</v>
+        <v>0.101399328070977</v>
       </c>
       <c r="X2">
-        <v>0.139030467898608</v>
+        <v>0.145653719727404</v>
       </c>
       <c r="Y2">
         <v>1.08373439107826</v>
       </c>
       <c r="Z2">
-        <v>1.81638668229845</v>
+        <v>1.9463348551179</v>
       </c>
       <c r="AA2">
         <v>8298.5</v>
@@ -1236,7 +1236,7 @@
         <v>23235</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08967316136405082</v>
+        <v>0.08965267216515078</v>
       </c>
       <c r="C2">
-        <v>29697.72150420939</v>
+        <v>29697.731589053</v>
       </c>
       <c r="D2">
-        <v>26395.42150420939</v>
+        <v>26395.43158905301</v>
       </c>
       <c r="E2">
         <v>-8298.5</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08967316136405082</v>
+        <v>0.08965267216515078</v>
       </c>
       <c r="T2">
         <v>0.8547702034345666</v>
       </c>
       <c r="U2">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.0895377530856097</v>
+        <v>0.08950681510970691</v>
       </c>
       <c r="C3">
-        <v>29464.10443282856</v>
+        <v>29470.48262138197</v>
       </c>
       <c r="D3">
-        <v>26477.13943282856</v>
+        <v>26483.51762138197</v>
       </c>
       <c r="E3">
         <v>-7983.165</v>
@@ -1539,37 +1539,37 @@
         <v>3659.1</v>
       </c>
       <c r="M3">
-        <v>18.17484251528018</v>
+        <v>17.73337351528019</v>
       </c>
       <c r="N3">
-        <v>3640.92515748472</v>
+        <v>3641.36662648472</v>
       </c>
       <c r="O3">
-        <v>910.23128937118</v>
+        <v>910.3416566211799</v>
       </c>
       <c r="P3">
-        <v>2730.69386811354</v>
+        <v>2731.02496986354</v>
       </c>
       <c r="Q3">
-        <v>4654.993868113539</v>
+        <v>4655.324969863539</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09000553379862697</v>
+        <v>0.08998488937852314</v>
       </c>
       <c r="T3">
         <v>0.8612457352787678</v>
       </c>
       <c r="U3">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>201.3277417355158</v>
+        <v>206.3397580188051</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08940234480716858</v>
+        <v>0.08936095805426304</v>
       </c>
       <c r="C4">
-        <v>29230.99491598779</v>
+        <v>29243.82353831747</v>
       </c>
       <c r="D4">
-        <v>26559.36491598779</v>
+        <v>26572.19353831746</v>
       </c>
       <c r="E4">
         <v>-7667.83</v>
@@ -1621,37 +1621,37 @@
         <v>3659.1</v>
       </c>
       <c r="M4">
-        <v>36.34968503056037</v>
+        <v>35.46674703056037</v>
       </c>
       <c r="N4">
-        <v>3622.750314969439</v>
+        <v>3623.63325296944</v>
       </c>
       <c r="O4">
-        <v>905.6875787423598</v>
+        <v>905.9083132423599</v>
       </c>
       <c r="P4">
-        <v>2717.06273622708</v>
+        <v>2717.72493972708</v>
       </c>
       <c r="Q4">
-        <v>4641.36273622708</v>
+        <v>4642.02493972708</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09034468934411283</v>
+        <v>0.09032388653502554</v>
       </c>
       <c r="T4">
         <v>0.8678534208340752</v>
       </c>
       <c r="U4">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>100.6638708677579</v>
+        <v>103.1698790094025</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08926693652872744</v>
+        <v>0.08921510099881916</v>
       </c>
       <c r="C5">
-        <v>28998.39769709153</v>
+        <v>29017.76028517553</v>
       </c>
       <c r="D5">
-        <v>26642.10269709153</v>
+        <v>26661.46528517553</v>
       </c>
       <c r="E5">
         <v>-7352.495</v>
@@ -1703,37 +1703,37 @@
         <v>3659.1</v>
       </c>
       <c r="M5">
-        <v>54.52452754584056</v>
+        <v>53.20012054584056</v>
       </c>
       <c r="N5">
-        <v>3604.575472454159</v>
+        <v>3605.899879454159</v>
       </c>
       <c r="O5">
-        <v>901.1438681135398</v>
+        <v>901.4749698635399</v>
       </c>
       <c r="P5">
-        <v>2703.43160434062</v>
+        <v>2704.42490959062</v>
       </c>
       <c r="Q5">
-        <v>4627.731604340619</v>
+        <v>4628.724909590619</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09069083778744375</v>
+        <v>0.09066987332362077</v>
       </c>
       <c r="T5">
         <v>0.8745973473286672</v>
       </c>
       <c r="U5">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.1092472451719</v>
+        <v>68.77991933960169</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08913152825028635</v>
+        <v>0.0890692439433753</v>
       </c>
       <c r="C6">
-        <v>28766.31757883552</v>
+        <v>28792.29888743683</v>
       </c>
       <c r="D6">
-        <v>26725.35757883552</v>
+        <v>26751.33888743684</v>
       </c>
       <c r="E6">
         <v>-7037.16</v>
@@ -1785,37 +1785,37 @@
         <v>3659.1</v>
       </c>
       <c r="M6">
-        <v>72.69937006112073</v>
+        <v>70.93349406112074</v>
       </c>
       <c r="N6">
-        <v>3586.400629938879</v>
+        <v>3588.166505938879</v>
       </c>
       <c r="O6">
-        <v>896.6001574847198</v>
+        <v>897.0416264847198</v>
       </c>
       <c r="P6">
-        <v>2689.80047245416</v>
+        <v>2691.124879454159</v>
       </c>
       <c r="Q6">
-        <v>4614.10047245416</v>
+        <v>4615.424879454159</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09104419765667741</v>
+        <v>0.09102306817031175</v>
       </c>
       <c r="T6">
         <v>0.8814817722918967</v>
       </c>
       <c r="U6">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.33193543387894</v>
+        <v>51.58493950470127</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08899611997184523</v>
+        <v>0.08892338688793143</v>
       </c>
       <c r="C7">
-        <v>28534.75942413626</v>
+        <v>28567.44545210249</v>
       </c>
       <c r="D7">
-        <v>26809.13442413626</v>
+        <v>26841.82045210249</v>
       </c>
       <c r="E7">
         <v>-6721.825</v>
@@ -1867,37 +1867,37 @@
         <v>3659.1</v>
       </c>
       <c r="M7">
-        <v>90.87421257640094</v>
+        <v>88.66686757640095</v>
       </c>
       <c r="N7">
-        <v>3568.225787423599</v>
+        <v>3570.433132423599</v>
       </c>
       <c r="O7">
-        <v>892.0564468558997</v>
+        <v>892.6082831058998</v>
       </c>
       <c r="P7">
-        <v>2676.169340567699</v>
+        <v>2677.824849317699</v>
       </c>
       <c r="Q7">
-        <v>4600.469340567699</v>
+        <v>4602.124849317699</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09140499668105284</v>
+        <v>0.09138369869798568</v>
       </c>
       <c r="T7">
         <v>0.88851113251751</v>
       </c>
       <c r="U7">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.26554834710313</v>
+        <v>41.26795160376101</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08886071169340409</v>
+        <v>0.08877752983248755</v>
       </c>
       <c r="C8">
-        <v>28303.7281570777</v>
+        <v>28343.20616907732</v>
       </c>
       <c r="D8">
-        <v>26893.4381570777</v>
+        <v>26932.91616907731</v>
       </c>
       <c r="E8">
         <v>-6406.49</v>
@@ -1949,37 +1949,37 @@
         <v>3659.1</v>
       </c>
       <c r="M8">
-        <v>109.0490550916811</v>
+        <v>106.4002410916811</v>
       </c>
       <c r="N8">
-        <v>3550.050944908319</v>
+        <v>3552.699758908319</v>
       </c>
       <c r="O8">
-        <v>887.5127362270797</v>
+        <v>888.1749397270797</v>
       </c>
       <c r="P8">
-        <v>2662.538208681239</v>
+        <v>2664.524819181239</v>
       </c>
       <c r="Q8">
-        <v>4586.838208681239</v>
+        <v>4588.824819181239</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09177347228041496</v>
+        <v>0.09175200221561013</v>
       </c>
       <c r="T8">
         <v>0.8956900535989872</v>
       </c>
       <c r="U8">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.55462362258595</v>
+        <v>34.38995966980085</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08872530341496296</v>
+        <v>0.08863167277704367</v>
       </c>
       <c r="C9">
-        <v>28073.22876387608</v>
+        <v>28119.58731258137</v>
       </c>
       <c r="D9">
-        <v>26978.27376387608</v>
+        <v>27024.63231258138</v>
       </c>
       <c r="E9">
         <v>-6091.155</v>
@@ -2031,37 +2031,37 @@
         <v>3659.1</v>
       </c>
       <c r="M9">
-        <v>127.2238976069613</v>
+        <v>124.1336146069613</v>
       </c>
       <c r="N9">
-        <v>3531.876102393039</v>
+        <v>3534.966385393039</v>
       </c>
       <c r="O9">
-        <v>882.9690255982597</v>
+        <v>883.7415963482597</v>
       </c>
       <c r="P9">
-        <v>2648.907076794779</v>
+        <v>2651.224789044779</v>
       </c>
       <c r="Q9">
-        <v>4573.207076794779</v>
+        <v>4575.524789044779</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09214987208621497</v>
+        <v>0.09212822623898995</v>
       </c>
       <c r="T9">
         <v>0.9030233600800662</v>
       </c>
       <c r="U9">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.76110596221653</v>
+        <v>29.47710828840072</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08858989513652185</v>
+        <v>0.08848581572159982</v>
       </c>
       <c r="C10">
-        <v>27843.26629386299</v>
+        <v>27896.59524259059</v>
       </c>
       <c r="D10">
-        <v>27063.64629386299</v>
+        <v>27116.97524259059</v>
       </c>
       <c r="E10">
         <v>-5775.82</v>
@@ -2113,37 +2113,37 @@
         <v>3659.1</v>
       </c>
       <c r="M10">
-        <v>145.3987401222415</v>
+        <v>141.8669881222415</v>
       </c>
       <c r="N10">
-        <v>3513.701259877758</v>
+        <v>3517.233011877759</v>
       </c>
       <c r="O10">
-        <v>878.4253149694396</v>
+        <v>879.3082529694396</v>
       </c>
       <c r="P10">
-        <v>2635.275944908319</v>
+        <v>2637.924758908319</v>
       </c>
       <c r="Q10">
-        <v>4559.575944908318</v>
+        <v>4562.224758908318</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09253445449648892</v>
+        <v>0.09251262904548671</v>
       </c>
       <c r="T10">
         <v>0.9105160862672558</v>
       </c>
       <c r="U10">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.16596771693947</v>
+        <v>25.79246975235063</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08845448685808073</v>
+        <v>0.08833995866615593</v>
       </c>
       <c r="C11">
-        <v>27613.84586048723</v>
+        <v>27674.23640630689</v>
       </c>
       <c r="D11">
-        <v>27149.56086048723</v>
+        <v>27209.95140630689</v>
       </c>
       <c r="E11">
         <v>-5460.485000000001</v>
@@ -2195,37 +2195,37 @@
         <v>3659.1</v>
       </c>
       <c r="M11">
-        <v>163.5735826375217</v>
+        <v>159.6003616375217</v>
       </c>
       <c r="N11">
-        <v>3495.526417362478</v>
+        <v>3499.499638362478</v>
       </c>
       <c r="O11">
-        <v>873.8816043406196</v>
+        <v>874.8749095906196</v>
       </c>
       <c r="P11">
-        <v>2621.644813021859</v>
+        <v>2624.624728771859</v>
       </c>
       <c r="Q11">
-        <v>4545.944813021859</v>
+        <v>4548.924728771859</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09292748926742822</v>
+        <v>0.09290548026531306</v>
       </c>
       <c r="T11">
         <v>0.9181734877552624</v>
       </c>
       <c r="U11">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.36974908172397</v>
+        <v>22.92663977986723</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08831907857963961</v>
+        <v>0.08819410161071208</v>
       </c>
       <c r="C12">
-        <v>27384.97264233571</v>
+        <v>27452.5173396586</v>
       </c>
       <c r="D12">
-        <v>27236.02264233571</v>
+        <v>27303.56733965861</v>
       </c>
       <c r="E12">
         <v>-5145.15</v>
@@ -2277,37 +2277,37 @@
         <v>3659.1</v>
       </c>
       <c r="M12">
-        <v>181.7484251528019</v>
+        <v>177.3337351528019</v>
       </c>
       <c r="N12">
-        <v>3477.351574847198</v>
+        <v>3481.766264847198</v>
       </c>
       <c r="O12">
-        <v>869.3378937117996</v>
+        <v>870.4415662117995</v>
       </c>
       <c r="P12">
-        <v>2608.013681135399</v>
+        <v>2611.324698635398</v>
       </c>
       <c r="Q12">
-        <v>4532.313681135398</v>
+        <v>4535.624698635398</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09332925814438839</v>
+        <v>0.09330706151224669</v>
       </c>
       <c r="T12">
         <v>0.9260010537207803</v>
       </c>
       <c r="U12">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.13277417355157</v>
+        <v>20.6339758018805</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08818367030119849</v>
+        <v>0.0880482445552682</v>
       </c>
       <c r="C13">
-        <v>27156.65188417398</v>
+        <v>27231.44466883222</v>
       </c>
       <c r="D13">
-        <v>27323.03688417398</v>
+        <v>27397.82966883222</v>
       </c>
       <c r="E13">
         <v>-4829.815000000001</v>
@@ -2359,37 +2359,37 @@
         <v>3659.1</v>
       </c>
       <c r="M13">
-        <v>199.923267668082</v>
+        <v>195.0671086680821</v>
       </c>
       <c r="N13">
-        <v>3459.176732331918</v>
+        <v>3464.032891331918</v>
       </c>
       <c r="O13">
-        <v>864.7941830829794</v>
+        <v>866.0082228329794</v>
       </c>
       <c r="P13">
-        <v>2594.382549248938</v>
+        <v>2598.024668498938</v>
       </c>
       <c r="Q13">
-        <v>4518.682549248938</v>
+        <v>4522.324668498938</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09374005553543756</v>
+        <v>0.0937176670568642</v>
       </c>
       <c r="T13">
         <v>0.9340045200450742</v>
       </c>
       <c r="U13">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.30252197595597</v>
+        <v>18.75815981989137</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08804826202275737</v>
+        <v>0.08790238749982433</v>
       </c>
       <c r="C14">
-        <v>26928.88889800679</v>
+        <v>27011.02511183566</v>
       </c>
       <c r="D14">
-        <v>27410.60889800679</v>
+        <v>27492.74511183566</v>
       </c>
       <c r="E14">
         <v>-4514.48</v>
@@ -2441,37 +2441,37 @@
         <v>3659.1</v>
       </c>
       <c r="M14">
-        <v>218.0981101833622</v>
+        <v>212.8004821833622</v>
       </c>
       <c r="N14">
-        <v>3441.001889816638</v>
+        <v>3446.299517816637</v>
       </c>
       <c r="O14">
-        <v>860.2504724541594</v>
+        <v>861.5748794541594</v>
       </c>
       <c r="P14">
-        <v>2580.751417362478</v>
+        <v>2584.724638362478</v>
       </c>
       <c r="Q14">
-        <v>4505.051417362478</v>
+        <v>4509.024638362478</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09416018923082875</v>
+        <v>0.09413760454567757</v>
       </c>
       <c r="T14">
         <v>0.9421898833312836</v>
       </c>
       <c r="U14">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.77731181129298</v>
+        <v>17.19497983490042</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08791285374431625</v>
+        <v>0.08775653044438046</v>
       </c>
       <c r="C15">
-        <v>26701.68906415907</v>
+        <v>26791.26548009442</v>
       </c>
       <c r="D15">
-        <v>27498.74406415907</v>
+        <v>27588.32048009442</v>
       </c>
       <c r="E15">
         <v>-4199.145</v>
@@ -2523,37 +2523,37 @@
         <v>3659.1</v>
       </c>
       <c r="M15">
-        <v>236.2729526986424</v>
+        <v>230.5338556986424</v>
       </c>
       <c r="N15">
-        <v>3422.827047301358</v>
+        <v>3428.566144301357</v>
       </c>
       <c r="O15">
-        <v>855.7067618253394</v>
+        <v>857.1415360753393</v>
       </c>
       <c r="P15">
-        <v>2567.120285476018</v>
+        <v>2571.424608226018</v>
       </c>
       <c r="Q15">
-        <v>4491.420285476018</v>
+        <v>4495.724608226017</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.094589981172091</v>
+        <v>0.09456719576986596</v>
       </c>
       <c r="T15">
         <v>0.9505634158884404</v>
       </c>
       <c r="U15">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.48674936427044</v>
+        <v>15.87228907836962</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08777744546587513</v>
+        <v>0.08761067338893659</v>
       </c>
       <c r="C16">
-        <v>26475.05783237784</v>
+        <v>26572.17268008092</v>
       </c>
       <c r="D16">
-        <v>27587.44783237784</v>
+        <v>27684.56268008092</v>
       </c>
       <c r="E16">
         <v>-3883.809999999999</v>
@@ -2605,37 +2605,37 @@
         <v>3659.1</v>
       </c>
       <c r="M16">
-        <v>254.4477952139226</v>
+        <v>248.2672292139226</v>
       </c>
       <c r="N16">
-        <v>3404.652204786077</v>
+        <v>3410.832770786077</v>
       </c>
       <c r="O16">
-        <v>851.1630511965193</v>
+        <v>852.7081926965193</v>
       </c>
       <c r="P16">
-        <v>2553.489153589558</v>
+        <v>2558.124578089558</v>
       </c>
       <c r="Q16">
-        <v>4477.789153589558</v>
+        <v>4482.424578089558</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09502976827477796</v>
+        <v>0.09500677748764012</v>
       </c>
       <c r="T16">
         <v>0.9591316817608799</v>
       </c>
       <c r="U16">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.38055298110826</v>
+        <v>14.73855414420036</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08764203718743399</v>
+        <v>0.08746481633349271</v>
       </c>
       <c r="C17">
-        <v>26249.00072295551</v>
+        <v>26353.75371497827</v>
       </c>
       <c r="D17">
-        <v>27676.72572295551</v>
+        <v>27781.47871497826</v>
       </c>
       <c r="E17">
         <v>-3568.475</v>
@@ -2687,37 +2687,37 @@
         <v>3659.1</v>
       </c>
       <c r="M17">
-        <v>272.6226377292028</v>
+        <v>266.0006027292028</v>
       </c>
       <c r="N17">
-        <v>3386.477362270797</v>
+        <v>3393.099397270797</v>
       </c>
       <c r="O17">
-        <v>846.6193405676993</v>
+        <v>848.2748493176992</v>
       </c>
       <c r="P17">
-        <v>2539.858021703098</v>
+        <v>2544.824547953098</v>
       </c>
       <c r="Q17">
-        <v>4464.158021703097</v>
+        <v>4469.124547953097</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09547990330929285</v>
+        <v>0.09545670230465603</v>
       </c>
       <c r="T17">
         <v>0.9679015538891416</v>
       </c>
       <c r="U17">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.42184944903438</v>
+        <v>13.75598386792034</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08750662890899288</v>
+        <v>0.08731895927804884</v>
       </c>
       <c r="C18">
-        <v>26023.5233278751</v>
+        <v>26136.01568637889</v>
       </c>
       <c r="D18">
-        <v>27766.58332787511</v>
+        <v>27879.07568637889</v>
       </c>
       <c r="E18">
         <v>-3253.14</v>
@@ -2769,37 +2769,37 @@
         <v>3659.1</v>
       </c>
       <c r="M18">
-        <v>290.7974802444829</v>
+        <v>283.733976244483</v>
       </c>
       <c r="N18">
-        <v>3368.302519755517</v>
+        <v>3375.366023755517</v>
       </c>
       <c r="O18">
-        <v>842.0756299388793</v>
+        <v>843.8415059388792</v>
       </c>
       <c r="P18">
-        <v>2526.226889816638</v>
+        <v>2531.524517816638</v>
       </c>
       <c r="Q18">
-        <v>4450.526889816638</v>
+        <v>4455.824517816638</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09594075584462952</v>
+        <v>0.09591733961731518</v>
       </c>
       <c r="T18">
         <v>0.9768802324966475</v>
       </c>
       <c r="U18">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.58298385846973</v>
+        <v>12.89623487617532</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08737122063055176</v>
+        <v>0.08717310222260496</v>
       </c>
       <c r="C19">
-        <v>25798.63131197782</v>
+        <v>25918.96579601929</v>
       </c>
       <c r="D19">
-        <v>27857.02631197782</v>
+        <v>27977.36079601929</v>
       </c>
       <c r="E19">
         <v>-2937.804999999999</v>
@@ -2851,37 +2851,37 @@
         <v>3659.1</v>
       </c>
       <c r="M19">
-        <v>308.9723227597632</v>
+        <v>301.4673497597632</v>
       </c>
       <c r="N19">
-        <v>3350.127677240237</v>
+        <v>3357.632650240237</v>
       </c>
       <c r="O19">
-        <v>837.5319193100592</v>
+        <v>839.4081625600592</v>
       </c>
       <c r="P19">
-        <v>2512.595757930178</v>
+        <v>2518.224487680177</v>
       </c>
       <c r="Q19">
-        <v>4436.895757930177</v>
+        <v>4442.524487680177</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09641271326033574</v>
+        <v>0.09638907662425528</v>
       </c>
       <c r="T19">
         <v>0.9860752648055392</v>
       </c>
       <c r="U19">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.84280833738327</v>
+        <v>12.13763282463559</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08723581235211064</v>
+        <v>0.08702724516716109</v>
       </c>
       <c r="C20">
-        <v>25574.33041415349</v>
+        <v>25702.61134755147</v>
       </c>
       <c r="D20">
-        <v>27948.06041415349</v>
+        <v>28076.34134755147</v>
       </c>
       <c r="E20">
         <v>-2622.47</v>
@@ -2933,37 +2933,37 @@
         <v>3659.1</v>
       </c>
       <c r="M20">
-        <v>327.1471652750433</v>
+        <v>319.2007232750433</v>
       </c>
       <c r="N20">
-        <v>3331.952834724957</v>
+        <v>3339.899276724957</v>
       </c>
       <c r="O20">
-        <v>832.9882086812391</v>
+        <v>834.9748191812391</v>
       </c>
       <c r="P20">
-        <v>2498.964626043718</v>
+        <v>2504.924457543717</v>
       </c>
       <c r="Q20">
-        <v>4423.264626043718</v>
+        <v>4429.224457543717</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.0968961818325226</v>
+        <v>0.09687231941185243</v>
       </c>
       <c r="T20">
         <v>0.9954945661951353</v>
       </c>
       <c r="U20">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.18487454086198</v>
+        <v>11.46331988993361</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08710040407366952</v>
+        <v>0.08688138811171724</v>
       </c>
       <c r="C21">
-        <v>25350.62644855447</v>
+        <v>25486.95974835219</v>
       </c>
       <c r="D21">
-        <v>28039.69144855447</v>
+        <v>28176.02474835219</v>
       </c>
       <c r="E21">
         <v>-2307.135</v>
@@ -3015,37 +3015,37 @@
         <v>3659.1</v>
       </c>
       <c r="M21">
-        <v>345.3220077903235</v>
+        <v>336.9340967903235</v>
       </c>
       <c r="N21">
-        <v>3313.777992209677</v>
+        <v>3322.165903209676</v>
       </c>
       <c r="O21">
-        <v>828.4444980524191</v>
+        <v>830.5414758024191</v>
       </c>
       <c r="P21">
-        <v>2485.333494157258</v>
+        <v>2491.624427407257</v>
       </c>
       <c r="Q21">
-        <v>4409.633494157257</v>
+        <v>4415.924427407257</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09739158790031903</v>
+        <v>0.09736749412013102</v>
       </c>
       <c r="T21">
         <v>1.005146442927685</v>
       </c>
       <c r="U21">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.5961969334482</v>
+        <v>10.85998726414764</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08696499579522841</v>
+        <v>0.08673553105627337</v>
       </c>
       <c r="C22">
-        <v>25127.52530583349</v>
+        <v>25272.01851137089</v>
       </c>
       <c r="D22">
-        <v>28131.92530583349</v>
+        <v>28276.4185113709</v>
       </c>
       <c r="E22">
         <v>-1991.799999999999</v>
@@ -3097,37 +3097,37 @@
         <v>3659.1</v>
       </c>
       <c r="M22">
-        <v>363.4968503056037</v>
+        <v>354.6674703056038</v>
       </c>
       <c r="N22">
-        <v>3295.603149694396</v>
+        <v>3304.432529694396</v>
       </c>
       <c r="O22">
-        <v>823.900787423599</v>
+        <v>826.108132423599</v>
       </c>
       <c r="P22">
-        <v>2471.702362270797</v>
+        <v>2478.324397270797</v>
       </c>
       <c r="Q22">
-        <v>4396.002362270797</v>
+        <v>4402.624397270796</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09789937911981036</v>
+        <v>0.09787504819611656</v>
       </c>
       <c r="T22">
         <v>1.015039616578548</v>
       </c>
       <c r="U22">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.06638708677578</v>
+        <v>10.31698790094025</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08682958751678727</v>
+        <v>0.08658967400082948</v>
       </c>
       <c r="C23">
-        <v>24905.03295440605</v>
+        <v>25057.7952570172</v>
       </c>
       <c r="D23">
-        <v>28224.76795440605</v>
+        <v>28377.5302570172</v>
       </c>
       <c r="E23">
         <v>-1676.465</v>
@@ -3179,37 +3179,37 @@
         <v>3659.1</v>
       </c>
       <c r="M23">
-        <v>381.6716928208839</v>
+        <v>372.4008438208839</v>
       </c>
       <c r="N23">
-        <v>3277.428307179116</v>
+        <v>3286.699156179116</v>
       </c>
       <c r="O23">
-        <v>819.357076794779</v>
+        <v>821.674789044779</v>
       </c>
       <c r="P23">
-        <v>2458.071230384337</v>
+        <v>2465.024367134337</v>
       </c>
       <c r="Q23">
-        <v>4382.371230384337</v>
+        <v>4389.324367134337</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09842002581321285</v>
+        <v>0.09839545174238021</v>
       </c>
       <c r="T23">
         <v>1.025183250321838</v>
       </c>
       <c r="U23">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.587035320738844</v>
+        <v>9.82570276280024</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08669417923834614</v>
+        <v>0.08644381694538561</v>
       </c>
       <c r="C24">
-        <v>24683.1554417377</v>
+        <v>24844.29771508911</v>
       </c>
       <c r="D24">
-        <v>28318.2254417377</v>
+        <v>28479.36771508911</v>
       </c>
       <c r="E24">
         <v>-1361.13</v>
@@ -3261,37 +3261,37 @@
         <v>3659.1</v>
       </c>
       <c r="M24">
-        <v>399.8465353361641</v>
+        <v>390.1342173361641</v>
       </c>
       <c r="N24">
-        <v>3259.253464663836</v>
+        <v>3268.965782663836</v>
       </c>
       <c r="O24">
-        <v>814.813366165959</v>
+        <v>817.241445665959</v>
       </c>
       <c r="P24">
-        <v>2444.440098497877</v>
+        <v>2451.724336997877</v>
       </c>
       <c r="Q24">
-        <v>4368.740098497877</v>
+        <v>4376.024336997876</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0989540224218308</v>
+        <v>0.09892919896931729</v>
       </c>
       <c r="T24">
         <v>1.035586977238032</v>
       </c>
       <c r="U24">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.151260987977986</v>
+        <v>9.379079909945684</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08655877095990504</v>
+        <v>0.08629795988994175</v>
       </c>
       <c r="C25">
-        <v>24461.89889565735</v>
+        <v>24631.53372674289</v>
       </c>
       <c r="D25">
-        <v>28412.30389565735</v>
+        <v>28581.93872674289</v>
       </c>
       <c r="E25">
         <v>-1045.795</v>
@@ -3343,37 +3343,37 @@
         <v>3659.1</v>
       </c>
       <c r="M25">
-        <v>418.0213778514442</v>
+        <v>407.8675908514443</v>
       </c>
       <c r="N25">
-        <v>3241.078622148555</v>
+        <v>3251.232409148556</v>
       </c>
       <c r="O25">
-        <v>810.2696555371389</v>
+        <v>812.8081022871389</v>
       </c>
       <c r="P25">
-        <v>2430.808966611417</v>
+        <v>2438.424306861417</v>
       </c>
       <c r="Q25">
-        <v>4355.108966611417</v>
+        <v>4362.724306861417</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09950188907223104</v>
+        <v>0.09947680976059041</v>
       </c>
       <c r="T25">
         <v>1.046260930827375</v>
       </c>
       <c r="U25">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04322746249690056</v>
+        <v>0.04217746249690056</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.753380075457205</v>
+        <v>8.971293826904567</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08662136268146391</v>
+        <v>0.08642210283449787</v>
       </c>
       <c r="C26">
-        <v>24102.99908308213</v>
+        <v>24228.85105670432</v>
       </c>
       <c r="D26">
-        <v>28368.73908308213</v>
+        <v>28494.59105670432</v>
       </c>
       <c r="E26">
         <v>-730.46</v>
@@ -3425,37 +3425,37 @@
         <v>3659.1</v>
       </c>
       <c r="M26">
-        <v>444.5210643667245</v>
+        <v>436.9530243667245</v>
       </c>
       <c r="N26">
-        <v>3214.578935633275</v>
+        <v>3222.146975633275</v>
       </c>
       <c r="O26">
-        <v>803.6447339083188</v>
+        <v>805.5367439083188</v>
       </c>
       <c r="P26">
-        <v>2410.934201724956</v>
+        <v>2416.610231724957</v>
       </c>
       <c r="Q26">
-        <v>4335.234201724956</v>
+        <v>4340.910231724956</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1000641732660629</v>
+        <v>0.1000388313621602</v>
       </c>
       <c r="T26">
         <v>1.057215777932227</v>
       </c>
       <c r="U26">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.231555922356216</v>
+        <v>8.374126727474032</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08649420440302277</v>
+        <v>0.08628749577905399</v>
       </c>
       <c r="C27">
-        <v>23876.30864749294</v>
+        <v>24008.25081182852</v>
       </c>
       <c r="D27">
-        <v>28457.38364749294</v>
+        <v>28589.32581182852</v>
       </c>
       <c r="E27">
         <v>-415.125</v>
@@ -3507,37 +3507,37 @@
         <v>3659.1</v>
       </c>
       <c r="M27">
-        <v>463.0427753820047</v>
+        <v>455.1594003820047</v>
       </c>
       <c r="N27">
-        <v>3196.057224617995</v>
+        <v>3203.940599617995</v>
       </c>
       <c r="O27">
-        <v>799.0143061544989</v>
+        <v>800.9851499044988</v>
       </c>
       <c r="P27">
-        <v>2397.042918463497</v>
+        <v>2402.955449713496</v>
       </c>
       <c r="Q27">
-        <v>4321.342918463497</v>
+        <v>4327.255449713496</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1006414517050635</v>
+        <v>0.1006158402064385</v>
       </c>
       <c r="T27">
         <v>1.068462754293208</v>
       </c>
       <c r="U27">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.902293685461968</v>
+        <v>8.039161658375072</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08636704612458167</v>
+        <v>0.08615288872361014</v>
       </c>
       <c r="C28">
-        <v>23650.17392849049</v>
+        <v>23788.28258943429</v>
       </c>
       <c r="D28">
-        <v>28546.58392849049</v>
+        <v>28684.69258943429</v>
       </c>
       <c r="E28">
         <v>-99.78999999999905</v>
@@ -3589,37 +3589,37 @@
         <v>3659.1</v>
       </c>
       <c r="M28">
-        <v>481.5644863972849</v>
+        <v>473.3657763972849</v>
       </c>
       <c r="N28">
-        <v>3177.535513602715</v>
+        <v>3185.734223602715</v>
       </c>
       <c r="O28">
-        <v>794.3838784006788</v>
+        <v>796.4335559006788</v>
       </c>
       <c r="P28">
-        <v>2383.151635202036</v>
+        <v>2389.300667702037</v>
       </c>
       <c r="Q28">
-        <v>4307.451635202036</v>
+        <v>4313.600667702036</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1012343322640372</v>
+        <v>0.1012084438843459</v>
       </c>
       <c r="T28">
         <v>1.08001370298827</v>
       </c>
       <c r="U28">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.5983593129442</v>
+        <v>7.729963133052953</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08623988784614055</v>
+        <v>0.08601828166816626</v>
       </c>
       <c r="C29">
-        <v>23424.60016822321</v>
+        <v>23568.95273549285</v>
       </c>
       <c r="D29">
-        <v>28636.34516822321</v>
+        <v>28780.69773549285</v>
       </c>
       <c r="E29">
         <v>215.5450000000001</v>
@@ -3671,37 +3671,37 @@
         <v>3659.1</v>
       </c>
       <c r="M29">
-        <v>500.0861974125651</v>
+        <v>491.5721524125651</v>
       </c>
       <c r="N29">
-        <v>3159.013802587435</v>
+        <v>3167.527847587435</v>
       </c>
       <c r="O29">
-        <v>789.7534506468587</v>
+        <v>791.8819618968587</v>
       </c>
       <c r="P29">
-        <v>2369.260351940576</v>
+        <v>2375.645885690576</v>
       </c>
       <c r="Q29">
-        <v>4293.560351940576</v>
+        <v>4299.945885690576</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1018434561259964</v>
+        <v>0.1018172832794563</v>
       </c>
       <c r="T29">
         <v>1.091881116031142</v>
       </c>
       <c r="U29">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.31693859764997</v>
+        <v>7.44366820219914</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08611272956769943</v>
+        <v>0.08588367461272239</v>
       </c>
       <c r="C30">
-        <v>23199.59267498065</v>
+        <v>23350.26768121826</v>
       </c>
       <c r="D30">
-        <v>28726.67267498065</v>
+        <v>28877.34768121826</v>
       </c>
       <c r="E30">
         <v>530.880000000001</v>
@@ -3753,37 +3753,37 @@
         <v>3659.1</v>
       </c>
       <c r="M30">
-        <v>518.6079084278452</v>
+        <v>509.7785284278453</v>
       </c>
       <c r="N30">
-        <v>3140.492091572155</v>
+        <v>3149.321471572155</v>
       </c>
       <c r="O30">
-        <v>785.1230228930386</v>
+        <v>787.3303678930387</v>
       </c>
       <c r="P30">
-        <v>2355.369068679116</v>
+        <v>2361.991103679116</v>
       </c>
       <c r="Q30">
-        <v>4279.669068679115</v>
+        <v>4286.291103679116</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1024695000952323</v>
+        <v>0.1024430348799864</v>
       </c>
       <c r="T30">
         <v>1.104078179436315</v>
       </c>
       <c r="U30">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.055619362019613</v>
+        <v>7.177822909263456</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08598557128925829</v>
+        <v>0.0857490675572785</v>
       </c>
       <c r="C31">
-        <v>22975.15682423994</v>
+        <v>23132.2339445037</v>
       </c>
       <c r="D31">
-        <v>28817.57182423995</v>
+        <v>28974.6489445037</v>
       </c>
       <c r="E31">
         <v>846.2150000000001</v>
@@ -3835,37 +3835,37 @@
         <v>3659.1</v>
       </c>
       <c r="M31">
-        <v>537.1296194431254</v>
+        <v>527.9849044431254</v>
       </c>
       <c r="N31">
-        <v>3121.970380556874</v>
+        <v>3131.115095556875</v>
       </c>
       <c r="O31">
-        <v>780.4925951392186</v>
+        <v>782.7787738892187</v>
       </c>
       <c r="P31">
-        <v>2341.477785417655</v>
+        <v>2348.336321667656</v>
       </c>
       <c r="Q31">
-        <v>4265.777785417655</v>
+        <v>4272.636321667656</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1031131791058551</v>
+        <v>0.1030864132861653</v>
       </c>
       <c r="T31">
         <v>1.116618822092339</v>
       </c>
       <c r="U31">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04405246249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.812322142639627</v>
+        <v>6.930311774461269</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08635341301081717</v>
+        <v>0.08561446050183463</v>
       </c>
       <c r="C32">
-        <v>22398.43062571993</v>
+        <v>22914.85813138656</v>
       </c>
       <c r="D32">
-        <v>28556.18062571993</v>
+        <v>29072.60813138656</v>
       </c>
       <c r="E32">
         <v>1161.549999999999</v>
@@ -3917,45 +3917,45 @@
         <v>3659.1</v>
       </c>
       <c r="M32">
-        <v>576.4634404584056</v>
+        <v>546.1912804584056</v>
       </c>
       <c r="N32">
-        <v>3082.636559541595</v>
+        <v>3112.908719541594</v>
       </c>
       <c r="O32">
-        <v>770.6591398853986</v>
+        <v>778.2271798853985</v>
       </c>
       <c r="P32">
-        <v>2311.977419656196</v>
+        <v>2334.681539656196</v>
       </c>
       <c r="Q32">
-        <v>4236.277419656195</v>
+        <v>4258.981539656195</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1037752489453529</v>
+        <v>0.1037481739325207</v>
       </c>
       <c r="T32">
         <v>1.129517768824249</v>
       </c>
       <c r="U32">
-        <v>0.06093661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04570246249690057</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.347497071263136</v>
+        <v>6.699301381979226</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08624275473237604</v>
+        <v>0.08587510344639077</v>
       </c>
       <c r="C33">
-        <v>22161.23020897982</v>
+        <v>22410.4388985928</v>
       </c>
       <c r="D33">
-        <v>28634.31520897982</v>
+        <v>28883.5238985928</v>
       </c>
       <c r="E33">
         <v>1476.885</v>
@@ -3999,37 +3999,37 @@
         <v>3659.1</v>
       </c>
       <c r="M33">
-        <v>595.6788884736858</v>
+        <v>581.0158109736858</v>
       </c>
       <c r="N33">
-        <v>3063.421111526314</v>
+        <v>3078.084189026314</v>
       </c>
       <c r="O33">
-        <v>765.8552778815786</v>
+        <v>769.5210472565785</v>
       </c>
       <c r="P33">
-        <v>2297.565833644736</v>
+        <v>2308.563141769735</v>
       </c>
       <c r="Q33">
-        <v>4221.865833644735</v>
+        <v>4232.863141769735</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.104456509214981</v>
+        <v>0.1044291160468864</v>
       </c>
       <c r="T33">
         <v>1.142790598070127</v>
       </c>
       <c r="U33">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04570246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.142739101222388</v>
+        <v>6.297763212102537</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08613209645393494</v>
+        <v>0.08575324639094689</v>
       </c>
       <c r="C34">
-        <v>21924.45854448569</v>
+        <v>22183.19839631359</v>
       </c>
       <c r="D34">
-        <v>28712.87854448569</v>
+        <v>28971.61839631359</v>
       </c>
       <c r="E34">
         <v>1792.219999999999</v>
@@ -4081,37 +4081,37 @@
         <v>3659.1</v>
       </c>
       <c r="M34">
-        <v>614.8943364889659</v>
+        <v>599.7582564889659</v>
       </c>
       <c r="N34">
-        <v>3044.205663511034</v>
+        <v>3059.341743511034</v>
       </c>
       <c r="O34">
-        <v>761.0514158777585</v>
+        <v>764.8354358777585</v>
       </c>
       <c r="P34">
-        <v>2283.154247633275</v>
+        <v>2294.506307633275</v>
       </c>
       <c r="Q34">
-        <v>4207.454247633275</v>
+        <v>4218.806307633275</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1051578065513629</v>
+        <v>0.1051300858704981</v>
       </c>
       <c r="T34">
         <v>1.156453804646767</v>
       </c>
       <c r="U34">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04570246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.950778504309189</v>
+        <v>6.100958111724333</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08602143817549382</v>
+        <v>0.08563138933550303</v>
       </c>
       <c r="C35">
-        <v>21688.11917102093</v>
+        <v>21956.49691294745</v>
       </c>
       <c r="D35">
-        <v>28791.87417102093</v>
+        <v>29060.25191294745</v>
       </c>
       <c r="E35">
         <v>2107.555</v>
@@ -4163,37 +4163,37 @@
         <v>3659.1</v>
       </c>
       <c r="M35">
-        <v>634.1097845042461</v>
+        <v>618.5007020042461</v>
       </c>
       <c r="N35">
-        <v>3024.990215495754</v>
+        <v>3040.599297995754</v>
       </c>
       <c r="O35">
-        <v>756.2475538739384</v>
+        <v>760.1498244989384</v>
       </c>
       <c r="P35">
-        <v>2268.742661621815</v>
+        <v>2280.449473496815</v>
       </c>
       <c r="Q35">
-        <v>4193.042661621816</v>
+        <v>4204.749473496815</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.105880038136592</v>
+        <v>0.1058519801664565</v>
       </c>
       <c r="T35">
         <v>1.170524868136142</v>
       </c>
       <c r="U35">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04570246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.770451882966486</v>
+        <v>5.916080593187232</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08629327989705268</v>
+        <v>0.08550953228005916</v>
       </c>
       <c r="C36">
-        <v>21179.49697222016</v>
+        <v>21730.33941077325</v>
       </c>
       <c r="D36">
-        <v>28598.58697222017</v>
+        <v>29149.42941077326</v>
       </c>
       <c r="E36">
         <v>2422.890000000001</v>
@@ -4245,45 +4245,45 @@
         <v>3659.1</v>
       </c>
       <c r="M36">
-        <v>669.4073175195265</v>
+        <v>637.2431475195264</v>
       </c>
       <c r="N36">
-        <v>2989.692682480473</v>
+        <v>3021.856852480474</v>
       </c>
       <c r="O36">
-        <v>747.4231706201183</v>
+        <v>755.4642131201184</v>
       </c>
       <c r="P36">
-        <v>2242.269511860355</v>
+        <v>2266.392639360355</v>
       </c>
       <c r="Q36">
-        <v>4166.569511860354</v>
+        <v>4190.692639360355</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1066241555274341</v>
+        <v>0.1065957500471409</v>
       </c>
       <c r="T36">
         <v>1.185022327488831</v>
       </c>
       <c r="U36">
-        <v>0.06243661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04682746249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>5.466178669152753</v>
+        <v>5.742078222799372</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08619387161861157</v>
+        <v>0.08538767522461529</v>
       </c>
       <c r="C37">
-        <v>20934.54235872035</v>
+        <v>21504.73091316855</v>
       </c>
       <c r="D37">
-        <v>28668.96735872035</v>
+        <v>29239.15591316855</v>
       </c>
       <c r="E37">
         <v>2738.225</v>
@@ -4327,45 +4327,45 @@
         <v>3659.1</v>
       </c>
       <c r="M37">
-        <v>689.0957680348066</v>
+        <v>655.9855930348066</v>
       </c>
       <c r="N37">
-        <v>2970.004231965193</v>
+        <v>3003.114406965193</v>
       </c>
       <c r="O37">
-        <v>742.5010579912984</v>
+        <v>750.7786017412983</v>
       </c>
       <c r="P37">
-        <v>2227.503173973895</v>
+        <v>2252.335805223895</v>
       </c>
       <c r="Q37">
-        <v>4151.803173973894</v>
+        <v>4176.635805223895</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1073911688379944</v>
+        <v>0.1073624051549232</v>
       </c>
       <c r="T37">
         <v>1.199965862513911</v>
       </c>
       <c r="U37">
-        <v>0.06243661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04682746249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>5.310002135748389</v>
+        <v>5.578018845005103</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08609446334017044</v>
+        <v>0.08548181816917141</v>
       </c>
       <c r="C38">
-        <v>20689.93500846607</v>
+        <v>21120.02761400781</v>
       </c>
       <c r="D38">
-        <v>28739.69500846607</v>
+        <v>29169.78761400782</v>
       </c>
       <c r="E38">
         <v>3053.559999999999</v>
@@ -4409,37 +4409,37 @@
         <v>3659.1</v>
       </c>
       <c r="M38">
-        <v>708.7842185500867</v>
+        <v>683.8096865500867</v>
       </c>
       <c r="N38">
-        <v>2950.315781449913</v>
+        <v>2975.290313449913</v>
       </c>
       <c r="O38">
-        <v>737.5789453624783</v>
+        <v>743.8225783624783</v>
       </c>
       <c r="P38">
-        <v>2212.736836087435</v>
+        <v>2231.467735087435</v>
       </c>
       <c r="Q38">
-        <v>4137.036836087434</v>
+        <v>4155.767735087435</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1081821513145098</v>
+        <v>0.1081530182348238</v>
       </c>
       <c r="T38">
         <v>1.215376383008524</v>
       </c>
       <c r="U38">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.162502076422046</v>
+        <v>5.351050258531229</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08599505506172934</v>
+        <v>0.08536596111372755</v>
       </c>
       <c r="C39">
-        <v>20445.67749795642</v>
+        <v>20890.10759207868</v>
       </c>
       <c r="D39">
-        <v>28810.77249795642</v>
+        <v>29255.20259207868</v>
       </c>
       <c r="E39">
         <v>3368.895</v>
@@ -4491,37 +4491,37 @@
         <v>3659.1</v>
       </c>
       <c r="M39">
-        <v>728.472669065367</v>
+        <v>702.804400065367</v>
       </c>
       <c r="N39">
-        <v>2930.627330934633</v>
+        <v>2956.295599934633</v>
       </c>
       <c r="O39">
-        <v>732.6568327336582</v>
+        <v>739.0738999836583</v>
       </c>
       <c r="P39">
-        <v>2197.970498200975</v>
+        <v>2217.221699950975</v>
       </c>
       <c r="Q39">
-        <v>4122.270498200975</v>
+        <v>4141.521699950974</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1089982443458351</v>
+        <v>0.1089687301426577</v>
       </c>
       <c r="T39">
         <v>1.231276126375983</v>
       </c>
       <c r="U39">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.022974993275504</v>
+        <v>5.206427278570925</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.0858956467832882</v>
+        <v>0.08525010405828368</v>
       </c>
       <c r="C40">
-        <v>20201.772429242</v>
+        <v>20660.68926352078</v>
       </c>
       <c r="D40">
-        <v>28882.202429242</v>
+        <v>29341.11926352078</v>
       </c>
       <c r="E40">
         <v>3684.23</v>
@@ -4573,37 +4573,37 @@
         <v>3659.1</v>
       </c>
       <c r="M40">
-        <v>748.1611195806471</v>
+        <v>721.7991135806471</v>
       </c>
       <c r="N40">
-        <v>2910.938880419353</v>
+        <v>2937.300886419353</v>
       </c>
       <c r="O40">
-        <v>727.7347201048382</v>
+        <v>734.3252216048381</v>
       </c>
       <c r="P40">
-        <v>2183.204160314514</v>
+        <v>2202.975664814514</v>
       </c>
       <c r="Q40">
-        <v>4107.504160314515</v>
+        <v>4127.275664814514</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1098406629588161</v>
+        <v>0.1098107553378411</v>
       </c>
       <c r="T40">
         <v>1.247688764690779</v>
       </c>
       <c r="U40">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.890791440820886</v>
+        <v>5.069416034398006</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08579623850484708</v>
+        <v>0.08513424700283979</v>
       </c>
       <c r="C41">
-        <v>19958.22243024231</v>
+        <v>20431.77706147224</v>
       </c>
       <c r="D41">
-        <v>28953.98743024231</v>
+        <v>29427.54206147224</v>
       </c>
       <c r="E41">
         <v>3999.565000000001</v>
@@ -4655,37 +4655,37 @@
         <v>3659.1</v>
       </c>
       <c r="M41">
-        <v>767.8495700959273</v>
+        <v>740.7938270959273</v>
       </c>
       <c r="N41">
-        <v>2891.250429904072</v>
+        <v>2918.306172904073</v>
       </c>
       <c r="O41">
-        <v>722.8126074760181</v>
+        <v>729.5765432260182</v>
       </c>
       <c r="P41">
-        <v>2168.437822428054</v>
+        <v>2188.729629678055</v>
       </c>
       <c r="Q41">
-        <v>4092.737822428054</v>
+        <v>4113.029629678054</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1107107018541899</v>
+        <v>0.1106803879164731</v>
       </c>
       <c r="T41">
         <v>1.264639522294584</v>
       </c>
       <c r="U41">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.765386532081888</v>
+        <v>4.93943100787498</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08569683022640598</v>
+        <v>0.08501838994739593</v>
       </c>
       <c r="C42">
-        <v>19715.03015506811</v>
+        <v>20203.37547145582</v>
       </c>
       <c r="D42">
-        <v>29026.13015506812</v>
+        <v>29514.47547145582</v>
       </c>
       <c r="E42">
         <v>4314.900000000001</v>
@@ -4737,37 +4737,37 @@
         <v>3659.1</v>
       </c>
       <c r="M42">
-        <v>787.5380206112076</v>
+        <v>759.7885406112076</v>
       </c>
       <c r="N42">
-        <v>2871.561979388792</v>
+        <v>2899.311459388792</v>
       </c>
       <c r="O42">
-        <v>717.8904948471981</v>
+        <v>724.827864847198</v>
       </c>
       <c r="P42">
-        <v>2153.671484541594</v>
+        <v>2174.483594541594</v>
       </c>
       <c r="Q42">
-        <v>4077.971484541594</v>
+        <v>4098.783594541594</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1116097420460762</v>
+        <v>0.1115790082477262</v>
       </c>
       <c r="T42">
         <v>1.28215530515185</v>
       </c>
       <c r="U42">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.64625186877984</v>
+        <v>4.815945232678104</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08559742194796485</v>
+        <v>0.08490253289195207</v>
       </c>
       <c r="C43">
-        <v>19472.1982843486</v>
+        <v>19975.48903215498</v>
       </c>
       <c r="D43">
-        <v>29098.6332843486</v>
+        <v>29601.92403215498</v>
       </c>
       <c r="E43">
         <v>4630.235000000001</v>
@@ -4819,37 +4819,37 @@
         <v>3659.1</v>
       </c>
       <c r="M43">
-        <v>807.2264711264877</v>
+        <v>778.7832541264877</v>
       </c>
       <c r="N43">
-        <v>2851.873528873512</v>
+        <v>2880.316745873512</v>
       </c>
       <c r="O43">
-        <v>712.9683822183781</v>
+        <v>720.0791864683781</v>
       </c>
       <c r="P43">
-        <v>2138.905146655135</v>
+        <v>2160.237559405135</v>
       </c>
       <c r="Q43">
-        <v>4063.205146655134</v>
+        <v>4084.537559405134</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1125392581766705</v>
+        <v>0.1125080902851235</v>
       </c>
       <c r="T43">
         <v>1.30026484336021</v>
       </c>
       <c r="U43">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.532928652468138</v>
+        <v>4.698483153832298</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08549801366952373</v>
+        <v>0.0847866758365082</v>
       </c>
       <c r="C44">
-        <v>19229.72952556327</v>
+        <v>19748.12233620379</v>
       </c>
       <c r="D44">
-        <v>29171.49952556327</v>
+        <v>29689.89233620379</v>
       </c>
       <c r="E44">
         <v>4945.57</v>
@@ -4901,37 +4901,37 @@
         <v>3659.1</v>
       </c>
       <c r="M44">
-        <v>826.9149216417678</v>
+        <v>797.7779676417679</v>
       </c>
       <c r="N44">
-        <v>2832.185078358232</v>
+        <v>2861.322032358232</v>
       </c>
       <c r="O44">
-        <v>708.0462695895581</v>
+        <v>715.330508089558</v>
       </c>
       <c r="P44">
-        <v>2124.138808768674</v>
+        <v>2145.991524268674</v>
       </c>
       <c r="Q44">
-        <v>4048.438808768674</v>
+        <v>4070.291524268674</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1135008265876301</v>
+        <v>0.1134692096341551</v>
       </c>
       <c r="T44">
         <v>1.31899884840334</v>
       </c>
       <c r="U44">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.425001779790325</v>
+        <v>4.586614507312481</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.0853986053910826</v>
+        <v>0.08467081878106432</v>
       </c>
       <c r="C45">
-        <v>18987.62661337906</v>
+        <v>19521.28003099092</v>
       </c>
       <c r="D45">
-        <v>29244.73161337906</v>
+        <v>29778.38503099092</v>
       </c>
       <c r="E45">
         <v>5260.905000000001</v>
@@ -4983,37 +4983,37 @@
         <v>3659.1</v>
       </c>
       <c r="M45">
-        <v>846.6033721570481</v>
+        <v>816.7726811570481</v>
       </c>
       <c r="N45">
-        <v>2812.496627842952</v>
+        <v>2842.327318842952</v>
       </c>
       <c r="O45">
-        <v>703.124156960738</v>
+        <v>710.581829710738</v>
       </c>
       <c r="P45">
-        <v>2109.372470882214</v>
+        <v>2131.745489132214</v>
       </c>
       <c r="Q45">
-        <v>4033.672470882213</v>
+        <v>4056.045489132214</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1144961342410796</v>
+        <v>0.1144640524691177</v>
       </c>
       <c r="T45">
         <v>1.338390186956755</v>
       </c>
       <c r="U45">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04682746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.322094761655666</v>
+        <v>4.479949053654051</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.0857611971126415</v>
+        <v>0.08455496172562045</v>
       </c>
       <c r="C46">
-        <v>18406.93676046178</v>
+        <v>19294.96681947804</v>
       </c>
       <c r="D46">
-        <v>28979.37676046178</v>
+        <v>29867.40681947803</v>
       </c>
       <c r="E46">
         <v>5576.24</v>
@@ -5065,45 +5065,45 @@
         <v>3659.1</v>
       </c>
       <c r="M46">
-        <v>885.7164586723283</v>
+        <v>835.7673946723282</v>
       </c>
       <c r="N46">
-        <v>2773.383541327672</v>
+        <v>2823.332605327671</v>
       </c>
       <c r="O46">
-        <v>693.3458853319179</v>
+        <v>705.8331513319179</v>
       </c>
       <c r="P46">
-        <v>2080.037655995754</v>
+        <v>2117.499453995753</v>
       </c>
       <c r="Q46">
-        <v>4004.337655995753</v>
+        <v>4041.799453995753</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1155269885964379</v>
+        <v>0.1154944254053289</v>
       </c>
       <c r="T46">
         <v>1.358474073315651</v>
       </c>
       <c r="U46">
-        <v>0.0638366166625341</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.131231800168781</v>
+        <v>4.378132029707368</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08567228883420036</v>
+        <v>0.08443910467017658</v>
       </c>
       <c r="C47">
-        <v>18156.2207370343</v>
+        <v>19069.18746103305</v>
       </c>
       <c r="D47">
-        <v>29043.9957370343</v>
+        <v>29956.96246103304</v>
       </c>
       <c r="E47">
         <v>5891.575000000001</v>
@@ -5147,45 +5147,45 @@
         <v>3659.1</v>
       </c>
       <c r="M47">
-        <v>905.8463781876086</v>
+        <v>854.7621081876084</v>
       </c>
       <c r="N47">
-        <v>2753.253621812391</v>
+        <v>2804.337891812392</v>
       </c>
       <c r="O47">
-        <v>688.3134054530979</v>
+        <v>701.0844729530979</v>
       </c>
       <c r="P47">
-        <v>2064.940216359294</v>
+        <v>2103.253418859294</v>
       </c>
       <c r="Q47">
-        <v>3989.240216359293</v>
+        <v>4027.553418859293</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1165953285647184</v>
+        <v>0.1165622664483115</v>
       </c>
       <c r="T47">
         <v>1.379288282814869</v>
       </c>
       <c r="U47">
-        <v>0.0638366166625341</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.039426649053919</v>
+        <v>4.280840206824983</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08558338055575924</v>
+        <v>0.08466824761473271</v>
       </c>
       <c r="C48">
-        <v>17905.79353581755</v>
+        <v>18577.24489548701</v>
       </c>
       <c r="D48">
-        <v>29108.90353581755</v>
+        <v>29780.35489548701</v>
       </c>
       <c r="E48">
         <v>6206.91</v>
@@ -5229,37 +5229,37 @@
         <v>3659.1</v>
       </c>
       <c r="M48">
-        <v>925.9762977028887</v>
+        <v>888.2622317028886</v>
       </c>
       <c r="N48">
-        <v>2733.123702297111</v>
+        <v>2770.837768297111</v>
       </c>
       <c r="O48">
-        <v>683.2809255742778</v>
+        <v>692.7094420742778</v>
       </c>
       <c r="P48">
-        <v>2049.842776722834</v>
+        <v>2078.128326222833</v>
       </c>
       <c r="Q48">
-        <v>3974.142776722833</v>
+        <v>4002.428326222833</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1177032366799722</v>
+        <v>0.1176696571595527</v>
       </c>
       <c r="T48">
         <v>1.400873388962206</v>
       </c>
       <c r="U48">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.951613026248399</v>
+        <v>4.119391627160748</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08549447227731813</v>
+        <v>0.08455989055928884</v>
       </c>
       <c r="C49">
-        <v>17655.65709753661</v>
+        <v>18345.16378294607</v>
       </c>
       <c r="D49">
-        <v>29174.10209753661</v>
+        <v>29863.60878294607</v>
       </c>
       <c r="E49">
         <v>6522.245000000001</v>
@@ -5311,37 +5311,37 @@
         <v>3659.1</v>
       </c>
       <c r="M49">
-        <v>946.1062172181689</v>
+        <v>907.5722802181689</v>
       </c>
       <c r="N49">
-        <v>2712.993782781831</v>
+        <v>2751.527719781831</v>
       </c>
       <c r="O49">
-        <v>678.2484456954578</v>
+        <v>687.8819299454577</v>
       </c>
       <c r="P49">
-        <v>2034.745337086373</v>
+        <v>2063.645789836373</v>
       </c>
       <c r="Q49">
-        <v>3959.045337086373</v>
+        <v>3987.945789836373</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1188529526486318</v>
+        <v>0.1188188361995199</v>
       </c>
       <c r="T49">
         <v>1.42327302741699</v>
       </c>
       <c r="U49">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.867536153349497</v>
+        <v>4.031744996795625</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.085405563998877</v>
+        <v>0.08445153350384496</v>
       </c>
       <c r="C50">
-        <v>17405.81338034302</v>
+        <v>18113.5494641016</v>
       </c>
       <c r="D50">
-        <v>29239.59338034302</v>
+        <v>29947.3294641016</v>
       </c>
       <c r="E50">
         <v>6837.58</v>
@@ -5393,37 +5393,37 @@
         <v>3659.1</v>
       </c>
       <c r="M50">
-        <v>966.236136733449</v>
+        <v>926.882328733449</v>
       </c>
       <c r="N50">
-        <v>2692.863863266551</v>
+        <v>2732.217671266551</v>
       </c>
       <c r="O50">
-        <v>673.2159658166377</v>
+        <v>683.0544178166377</v>
       </c>
       <c r="P50">
-        <v>2019.647897449913</v>
+        <v>2049.163253449913</v>
       </c>
       <c r="Q50">
-        <v>3943.947897449912</v>
+        <v>3973.463253449913</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1200468884622398</v>
+        <v>0.1200122144333321</v>
       </c>
       <c r="T50">
         <v>1.446534190427728</v>
       </c>
       <c r="U50">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.786962483488049</v>
+        <v>3.947750309362384</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08531665572043587</v>
+        <v>0.08434317644840109</v>
       </c>
       <c r="C51">
-        <v>17156.26436001084</v>
+        <v>17882.40587586763</v>
       </c>
       <c r="D51">
-        <v>29305.37936001084</v>
+        <v>30031.52087586762</v>
       </c>
       <c r="E51">
         <v>7152.914999999999</v>
@@ -5475,37 +5475,37 @@
         <v>3659.1</v>
       </c>
       <c r="M51">
-        <v>986.3660562487293</v>
+        <v>946.1923772487291</v>
       </c>
       <c r="N51">
-        <v>2672.733943751271</v>
+        <v>2712.907622751271</v>
       </c>
       <c r="O51">
-        <v>668.1834859378176</v>
+        <v>678.2269056878176</v>
       </c>
       <c r="P51">
-        <v>2004.550457813453</v>
+        <v>2034.680717063453</v>
       </c>
       <c r="Q51">
-        <v>3928.850457813453</v>
+        <v>3958.980717063453</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1212876452881463</v>
+        <v>0.1212523918135683</v>
       </c>
       <c r="T51">
         <v>1.470707555909475</v>
       </c>
       <c r="U51">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.709677534845435</v>
+        <v>3.867183976518253</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08522774744199477</v>
+        <v>0.08423481939295721</v>
       </c>
       <c r="C52">
-        <v>16907.01203013535</v>
+        <v>17651.73699955458</v>
       </c>
       <c r="D52">
-        <v>29371.46203013535</v>
+        <v>30116.18699955458</v>
       </c>
       <c r="E52">
         <v>7468.25</v>
@@ -5557,37 +5557,37 @@
         <v>3659.1</v>
       </c>
       <c r="M52">
-        <v>1006.495975764009</v>
+        <v>965.5024257640093</v>
       </c>
       <c r="N52">
-        <v>2652.60402423599</v>
+        <v>2693.597574235991</v>
       </c>
       <c r="O52">
-        <v>663.1510060589976</v>
+        <v>673.3993935589976</v>
       </c>
       <c r="P52">
-        <v>1989.453018176993</v>
+        <v>2020.198180676993</v>
       </c>
       <c r="Q52">
-        <v>3913.753018176993</v>
+        <v>3944.498180676993</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1225780323870889</v>
+        <v>0.1225421762890139</v>
       </c>
       <c r="T52">
         <v>1.495847856010492</v>
       </c>
       <c r="U52">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.635483984148526</v>
+        <v>3.789840296987888</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08513883916355364</v>
+        <v>0.08412646233751335</v>
       </c>
       <c r="C53">
-        <v>16658.0584023345</v>
+        <v>17421.54686149699</v>
       </c>
       <c r="D53">
-        <v>29437.8434023345</v>
+        <v>30201.33186149699</v>
       </c>
       <c r="E53">
         <v>7783.585000000001</v>
@@ -5639,37 +5639,37 @@
         <v>3659.1</v>
       </c>
       <c r="M53">
-        <v>1026.62589527929</v>
+        <v>984.8124742792896</v>
       </c>
       <c r="N53">
-        <v>2632.47410472071</v>
+        <v>2674.28752572071</v>
       </c>
       <c r="O53">
-        <v>658.1185261801775</v>
+        <v>668.5718814301775</v>
       </c>
       <c r="P53">
-        <v>1974.355578540532</v>
+        <v>2005.715644290533</v>
       </c>
       <c r="Q53">
-        <v>3898.655578540532</v>
+        <v>3930.015644290532</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.123921088347213</v>
+        <v>0.1238846050287634</v>
       </c>
       <c r="T53">
         <v>1.522014290809509</v>
       </c>
       <c r="U53">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.564199984459339</v>
+        <v>3.715529702929302</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08504993088511251</v>
+        <v>0.08401810528206947</v>
       </c>
       <c r="C54">
-        <v>16409.40550645291</v>
+        <v>17191.83953369168</v>
       </c>
       <c r="D54">
-        <v>29504.52550645291</v>
+        <v>30286.95953369168</v>
       </c>
       <c r="E54">
         <v>8098.920000000002</v>
@@ -5721,37 +5721,37 @@
         <v>3659.1</v>
       </c>
       <c r="M54">
-        <v>1046.75581479457</v>
+        <v>1004.12252279457</v>
       </c>
       <c r="N54">
-        <v>2612.34418520543</v>
+        <v>2654.97747720543</v>
       </c>
       <c r="O54">
-        <v>653.0860463013576</v>
+        <v>663.7443693013576</v>
       </c>
       <c r="P54">
-        <v>1959.258138904073</v>
+        <v>1991.233107904073</v>
       </c>
       <c r="Q54">
-        <v>3883.558138904073</v>
+        <v>3915.533107904072</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1253201049723421</v>
+        <v>0.1252829682993358</v>
       </c>
       <c r="T54">
         <v>1.549270993725152</v>
       </c>
       <c r="U54">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.495657677065891</v>
+        <v>3.6440772086422</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08496102260667139</v>
+        <v>0.08390974822662561</v>
       </c>
       <c r="C55">
-        <v>16161.05539076882</v>
+        <v>16962.61913444691</v>
       </c>
       <c r="D55">
-        <v>29571.51039076882</v>
+        <v>30373.07413444691</v>
       </c>
       <c r="E55">
         <v>8414.255000000001</v>
@@ -5803,37 +5803,37 @@
         <v>3659.1</v>
       </c>
       <c r="M55">
-        <v>1066.88573430985</v>
+        <v>1023.43257130985</v>
       </c>
       <c r="N55">
-        <v>2592.21426569015</v>
+        <v>2635.66742869015</v>
       </c>
       <c r="O55">
-        <v>648.0535664225374</v>
+        <v>658.9168571725374</v>
       </c>
       <c r="P55">
-        <v>1944.160699267612</v>
+        <v>1976.750571517612</v>
       </c>
       <c r="Q55">
-        <v>3868.460699267612</v>
+        <v>3901.050571517612</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1267786542198172</v>
+        <v>0.1267408363899326</v>
       </c>
       <c r="T55">
         <v>1.577687556339333</v>
       </c>
       <c r="U55">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.429701871838232</v>
+        <v>3.575321034894234</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08487211432823026</v>
+        <v>0.08380139117118174</v>
       </c>
       <c r="C56">
-        <v>15913.0101222039</v>
+        <v>16733.88982904272</v>
       </c>
       <c r="D56">
-        <v>29638.80012220389</v>
+        <v>30459.67982904272</v>
       </c>
       <c r="E56">
         <v>8729.59</v>
@@ -5885,37 +5885,37 @@
         <v>3659.1</v>
       </c>
       <c r="M56">
-        <v>1087.01565382513</v>
+        <v>1042.74261982513</v>
       </c>
       <c r="N56">
-        <v>2572.08434617487</v>
+        <v>2616.35738017487</v>
       </c>
       <c r="O56">
-        <v>643.0210865437175</v>
+        <v>654.0893450437175</v>
       </c>
       <c r="P56">
-        <v>1929.063259631153</v>
+        <v>1962.268035131152</v>
       </c>
       <c r="Q56">
-        <v>3853.363259631152</v>
+        <v>3886.568035131152</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1283006186519651</v>
+        <v>0.1282620900496857</v>
       </c>
       <c r="T56">
         <v>1.60733962167587</v>
       </c>
       <c r="U56">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.366188874211599</v>
+        <v>3.509111386099897</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08478320604978914</v>
+        <v>0.08369303411573786</v>
       </c>
       <c r="C57">
-        <v>15665.27178653571</v>
+        <v>16505.65583040242</v>
       </c>
       <c r="D57">
-        <v>29706.39678653571</v>
+        <v>30546.78083040243</v>
       </c>
       <c r="E57">
         <v>9044.925000000003</v>
@@ -5967,37 +5967,37 @@
         <v>3659.1</v>
       </c>
       <c r="M57">
-        <v>1107.145573340411</v>
+        <v>1062.05266834041</v>
       </c>
       <c r="N57">
-        <v>2551.954426659589</v>
+        <v>2597.047331659589</v>
       </c>
       <c r="O57">
-        <v>637.9886066648974</v>
+        <v>649.2618329148974</v>
       </c>
       <c r="P57">
-        <v>1913.965819994692</v>
+        <v>1947.785498744692</v>
       </c>
       <c r="Q57">
-        <v>3838.265819994692</v>
+        <v>3872.085498744692</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1298902259477641</v>
+        <v>0.1298509549832057</v>
       </c>
       <c r="T57">
         <v>1.63830955658292</v>
       </c>
       <c r="U57">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.304985440135023</v>
+        <v>3.44530936089808</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08469429777134803</v>
+        <v>0.08358467706029399</v>
       </c>
       <c r="C58">
-        <v>15417.84248861334</v>
+        <v>16277.92139977583</v>
       </c>
       <c r="D58">
-        <v>29774.30248861334</v>
+        <v>30634.38139977583</v>
       </c>
       <c r="E58">
         <v>9360.260000000002</v>
@@ -6049,37 +6049,37 @@
         <v>3659.1</v>
       </c>
       <c r="M58">
-        <v>1127.275492855691</v>
+        <v>1081.362716855691</v>
       </c>
       <c r="N58">
-        <v>2531.824507144309</v>
+        <v>2577.737283144309</v>
       </c>
       <c r="O58">
-        <v>632.9561267860772</v>
+        <v>644.4343207860773</v>
       </c>
       <c r="P58">
-        <v>1898.868380358232</v>
+        <v>1933.302962358232</v>
       </c>
       <c r="Q58">
-        <v>3823.168380358231</v>
+        <v>3857.602962358232</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1315520881206448</v>
+        <v>0.1315120410500674</v>
       </c>
       <c r="T58">
         <v>1.670687215803926</v>
       </c>
       <c r="U58">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.245967842989755</v>
+        <v>3.383785979453471</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08460538949290691</v>
+        <v>0.08347632000485011</v>
       </c>
       <c r="C59">
-        <v>15170.72435257579</v>
+        <v>16050.69084743412</v>
       </c>
       <c r="D59">
-        <v>29842.51935257579</v>
+        <v>30722.48584743412</v>
       </c>
       <c r="E59">
         <v>9675.595000000001</v>
@@ -6131,37 +6131,37 @@
         <v>3659.1</v>
       </c>
       <c r="M59">
-        <v>1147.405412370971</v>
+        <v>1100.672765370971</v>
       </c>
       <c r="N59">
-        <v>2511.694587629029</v>
+        <v>2558.427234629029</v>
       </c>
       <c r="O59">
-        <v>627.9236469072573</v>
+        <v>639.6068086572573</v>
       </c>
       <c r="P59">
-        <v>1883.770940721772</v>
+        <v>1918.820425971772</v>
       </c>
       <c r="Q59">
-        <v>3808.070940721772</v>
+        <v>3843.120425971772</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1332912462085432</v>
+        <v>0.1332503869339925</v>
       </c>
       <c r="T59">
         <v>1.704570812663118</v>
       </c>
       <c r="U59">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.189021038726778</v>
+        <v>3.32442131314727</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.0845164812144658</v>
+        <v>0.08336796294940624</v>
       </c>
       <c r="C60">
-        <v>14923.91952207352</v>
+        <v>15823.96853337685</v>
       </c>
       <c r="D60">
-        <v>29911.04952207352</v>
+        <v>30811.09853337685</v>
       </c>
       <c r="E60">
         <v>9990.93</v>
@@ -6213,37 +6213,37 @@
         <v>3659.1</v>
       </c>
       <c r="M60">
-        <v>1167.535331886251</v>
+        <v>1119.982813886251</v>
       </c>
       <c r="N60">
-        <v>2491.564668113749</v>
+        <v>2539.117186113749</v>
       </c>
       <c r="O60">
-        <v>622.8911670284372</v>
+        <v>634.7792965284373</v>
       </c>
       <c r="P60">
-        <v>1868.673501085311</v>
+        <v>1904.337889585312</v>
       </c>
       <c r="Q60">
-        <v>3792.973501085311</v>
+        <v>3828.637889585311</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1351132213482463</v>
+        <v>0.1350715111933427</v>
       </c>
       <c r="T60">
         <v>1.740067914134653</v>
       </c>
       <c r="U60">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.134037917369419</v>
+        <v>3.267103704299904</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08442757293602467</v>
+        <v>0.08325960589396238</v>
       </c>
       <c r="C61">
-        <v>14677.43016049299</v>
+        <v>15597.75886805117</v>
       </c>
       <c r="D61">
-        <v>29979.89516049298</v>
+        <v>30900.22386805117</v>
       </c>
       <c r="E61">
         <v>10306.265</v>
@@ -6295,37 +6295,37 @@
         <v>3659.1</v>
       </c>
       <c r="M61">
-        <v>1187.665251401531</v>
+        <v>1139.292862401531</v>
       </c>
       <c r="N61">
-        <v>2471.434748598469</v>
+        <v>2519.807137598469</v>
       </c>
       <c r="O61">
-        <v>617.8586871496173</v>
+        <v>629.9517843996173</v>
       </c>
       <c r="P61">
-        <v>1853.576061448852</v>
+        <v>1889.855353198852</v>
       </c>
       <c r="Q61">
-        <v>3777.876061448851</v>
+        <v>3814.155353198852</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1370240733240325</v>
+        <v>0.1369814707824172</v>
       </c>
       <c r="T61">
         <v>1.777296581531629</v>
       </c>
       <c r="U61">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.080918630634345</v>
+        <v>3.211729065243973</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08433866465758355</v>
+        <v>0.08315124883851852</v>
       </c>
       <c r="C62">
-        <v>14431.25845118422</v>
+        <v>15372.06631308357</v>
       </c>
       <c r="D62">
-        <v>30049.05845118422</v>
+        <v>30989.86631308356</v>
       </c>
       <c r="E62">
         <v>10621.6</v>
@@ -6377,37 +6377,37 @@
         <v>3659.1</v>
       </c>
       <c r="M62">
-        <v>1207.795170916811</v>
+        <v>1158.602910916811</v>
       </c>
       <c r="N62">
-        <v>2451.304829083188</v>
+        <v>2500.497089083189</v>
       </c>
       <c r="O62">
-        <v>612.8262072707971</v>
+        <v>625.1242722707972</v>
       </c>
       <c r="P62">
-        <v>1838.478621812391</v>
+        <v>1875.372816812392</v>
       </c>
       <c r="Q62">
-        <v>3762.778621812391</v>
+        <v>3799.672816812391</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.139030467898608</v>
+        <v>0.1389869283509454</v>
       </c>
       <c r="T62">
         <v>1.816386682298454</v>
       </c>
       <c r="U62">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.029569986790439</v>
+        <v>3.158200247489907</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08543925637914243</v>
+        <v>0.08304289178307464</v>
       </c>
       <c r="C63">
-        <v>13281.60545450721</v>
+        <v>15146.8953820244</v>
       </c>
       <c r="D63">
-        <v>29214.74045450722</v>
+        <v>31080.03038202439</v>
       </c>
       <c r="E63">
         <v>10936.935</v>
@@ -6459,45 +6459,45 @@
         <v>3659.1</v>
       </c>
       <c r="M63">
-        <v>1277.937221432092</v>
+        <v>1177.912959432092</v>
       </c>
       <c r="N63">
-        <v>2381.162778567908</v>
+        <v>2481.187040567908</v>
       </c>
       <c r="O63">
-        <v>595.2906946419771</v>
+        <v>620.2967601419771</v>
       </c>
       <c r="P63">
-        <v>1785.872083925931</v>
+        <v>1860.890280425931</v>
       </c>
       <c r="Q63">
-        <v>3710.172083925931</v>
+        <v>3785.190280425931</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1411397545026489</v>
+        <v>0.1410952298973469</v>
       </c>
       <c r="T63">
         <v>1.857481403617424</v>
       </c>
       <c r="U63">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.863286191710976</v>
+        <v>3.106426472940892</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08536984810070131</v>
+        <v>0.08293453472763077</v>
       </c>
       <c r="C64">
-        <v>13017.51515059226</v>
+        <v>14922.25064110542</v>
       </c>
       <c r="D64">
-        <v>29265.98515059226</v>
+        <v>31170.72064110542</v>
       </c>
       <c r="E64">
         <v>11252.27</v>
@@ -6541,45 +6541,45 @@
         <v>3659.1</v>
       </c>
       <c r="M64">
-        <v>1298.887011947372</v>
+        <v>1197.223007947372</v>
       </c>
       <c r="N64">
-        <v>2360.212988052628</v>
+        <v>2461.876992052628</v>
       </c>
       <c r="O64">
-        <v>590.053247013157</v>
+        <v>615.4692480131571</v>
       </c>
       <c r="P64">
-        <v>1770.159741039471</v>
+        <v>1846.407744039471</v>
       </c>
       <c r="Q64">
-        <v>3694.459741039471</v>
+        <v>3770.707744039471</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.143360056191113</v>
+        <v>0.1433144946830327</v>
       </c>
       <c r="T64">
         <v>1.900739005005813</v>
       </c>
       <c r="U64">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.817104156360799</v>
+        <v>3.056322820151523</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08530043982226018</v>
+        <v>0.08282617767218689</v>
       </c>
       <c r="C65">
-        <v>12753.60493612189</v>
+        <v>14698.13671001071</v>
       </c>
       <c r="D65">
-        <v>29317.40993612189</v>
+        <v>31261.94171001071</v>
       </c>
       <c r="E65">
         <v>11567.605</v>
@@ -6623,45 +6623,45 @@
         <v>3659.1</v>
       </c>
       <c r="M65">
-        <v>1319.836802462652</v>
+        <v>1216.533056462652</v>
       </c>
       <c r="N65">
-        <v>2339.263197537348</v>
+        <v>2442.566943537348</v>
       </c>
       <c r="O65">
-        <v>584.815799384337</v>
+        <v>610.6417358843371</v>
       </c>
       <c r="P65">
-        <v>1754.447398153011</v>
+        <v>1831.925207653011</v>
       </c>
       <c r="Q65">
-        <v>3678.747398153011</v>
+        <v>3756.225207653011</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1457003741870617</v>
+        <v>0.1456537197274042</v>
       </c>
       <c r="T65">
         <v>1.946334855117898</v>
       </c>
       <c r="U65">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.772388217370946</v>
+        <v>3.007809759514197</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08523103154381906</v>
+        <v>0.08391782061674302</v>
       </c>
       <c r="C66">
-        <v>12489.8757621008</v>
+        <v>13487.50188571099</v>
       </c>
       <c r="D66">
-        <v>29369.0157621008</v>
+        <v>30366.64188571099</v>
       </c>
       <c r="E66">
         <v>11882.94</v>
@@ -6705,37 +6705,37 @@
         <v>3659.1</v>
       </c>
       <c r="M66">
-        <v>1340.786592977932</v>
+        <v>1286.296704977932</v>
       </c>
       <c r="N66">
-        <v>2318.313407022068</v>
+        <v>2372.803295022068</v>
       </c>
       <c r="O66">
-        <v>579.578351755517</v>
+        <v>593.2008237555169</v>
       </c>
       <c r="P66">
-        <v>1738.735055266551</v>
+        <v>1779.602471266551</v>
       </c>
       <c r="Q66">
-        <v>3663.035055266551</v>
+        <v>3703.90247126655</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1481707098494519</v>
+        <v>0.1481229017186852</v>
       </c>
       <c r="T66">
         <v>1.994463808013989</v>
       </c>
       <c r="U66">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.729069651474525</v>
+        <v>2.844678048104598</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08516162326537793</v>
+        <v>0.08382821356129916</v>
       </c>
       <c r="C67">
-        <v>12226.32858624144</v>
+        <v>13243.72074292046</v>
       </c>
       <c r="D67">
-        <v>29420.80358624144</v>
+        <v>30438.19574292047</v>
       </c>
       <c r="E67">
         <v>12198.275</v>
@@ -6787,37 +6787,37 @@
         <v>3659.1</v>
       </c>
       <c r="M67">
-        <v>1361.736383493212</v>
+        <v>1306.395090993212</v>
       </c>
       <c r="N67">
-        <v>2297.363616506787</v>
+        <v>2352.704909006788</v>
       </c>
       <c r="O67">
-        <v>574.3409041266968</v>
+        <v>588.1762272516969</v>
       </c>
       <c r="P67">
-        <v>1723.022712380091</v>
+        <v>1764.528681755091</v>
       </c>
       <c r="Q67">
-        <v>3647.32271238009</v>
+        <v>3688.828681755091</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.150782207549693</v>
+        <v>0.1507331798237537</v>
       </c>
       <c r="T67">
         <v>2.045342986789856</v>
       </c>
       <c r="U67">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.687083964528762</v>
+        <v>2.800913770441451</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08509221498693681</v>
+        <v>0.08373860650585528</v>
       </c>
       <c r="C68">
-        <v>11962.96437302336</v>
+        <v>13000.27760571534</v>
       </c>
       <c r="D68">
-        <v>29472.77437302336</v>
+        <v>30510.08760571534</v>
       </c>
       <c r="E68">
         <v>12513.61</v>
@@ -6869,37 +6869,37 @@
         <v>3659.1</v>
       </c>
       <c r="M68">
-        <v>1382.686174008492</v>
+        <v>1326.493477008492</v>
       </c>
       <c r="N68">
-        <v>2276.413825991508</v>
+        <v>2332.606522991508</v>
       </c>
       <c r="O68">
-        <v>569.1034564978769</v>
+        <v>583.1516307478769</v>
       </c>
       <c r="P68">
-        <v>1707.310369493631</v>
+        <v>1749.454892243631</v>
       </c>
       <c r="Q68">
-        <v>3631.610369493631</v>
+        <v>3673.75489224363</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1535473227617131</v>
+        <v>0.1534970036997086</v>
       </c>
       <c r="T68">
         <v>2.099215058434892</v>
       </c>
       <c r="U68">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.646370571126812</v>
+        <v>2.758475683010519</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08502280670849569</v>
+        <v>0.0836489994504114</v>
       </c>
       <c r="C69">
-        <v>11699.78409375303</v>
+        <v>12757.17487476818</v>
       </c>
       <c r="D69">
-        <v>29524.92909375303</v>
+        <v>30582.31987476817</v>
       </c>
       <c r="E69">
         <v>12828.945</v>
@@ -6951,37 +6951,37 @@
         <v>3659.1</v>
       </c>
       <c r="M69">
-        <v>1403.635964523772</v>
+        <v>1346.591863023773</v>
       </c>
       <c r="N69">
-        <v>2255.464035476228</v>
+        <v>2312.508136976227</v>
       </c>
       <c r="O69">
-        <v>563.8660088690569</v>
+        <v>578.1270342440569</v>
       </c>
       <c r="P69">
-        <v>1691.598026607171</v>
+        <v>1734.381102732171</v>
       </c>
       <c r="Q69">
-        <v>3615.89802660717</v>
+        <v>3658.68110273217</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1564800207138555</v>
+        <v>0.156428332052994</v>
       </c>
       <c r="T69">
         <v>2.156352104119021</v>
       </c>
       <c r="U69">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.606872502901039</v>
+        <v>2.717304404159616</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.08495339843005457</v>
+        <v>0.08355939239496754</v>
       </c>
       <c r="C70">
-        <v>11436.78872662434</v>
+        <v>12514.41497353978</v>
       </c>
       <c r="D70">
-        <v>29577.26872662434</v>
+        <v>30654.89497353978</v>
       </c>
       <c r="E70">
         <v>13144.28</v>
@@ -7033,37 +7033,37 @@
         <v>3659.1</v>
       </c>
       <c r="M70">
-        <v>1424.585755039053</v>
+        <v>1366.690249039053</v>
       </c>
       <c r="N70">
-        <v>2234.514244960947</v>
+        <v>2292.409750960947</v>
       </c>
       <c r="O70">
-        <v>558.6285612402368</v>
+        <v>573.1024377402367</v>
       </c>
       <c r="P70">
-        <v>1675.88568372071</v>
+        <v>1719.30731322071</v>
       </c>
       <c r="Q70">
-        <v>3600.18568372071</v>
+        <v>3643.60731322071</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1595960122880068</v>
+        <v>0.1595428684283599</v>
       </c>
       <c r="T70">
         <v>2.217060215158408</v>
       </c>
       <c r="U70">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.568536142564258</v>
+        <v>2.677344045274916</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08488399015161344</v>
+        <v>0.08346978533952366</v>
       </c>
       <c r="C71">
-        <v>11173.97925677984</v>
+        <v>12272.0003485502</v>
       </c>
       <c r="D71">
-        <v>29629.79425677984</v>
+        <v>30727.8153485502</v>
       </c>
       <c r="E71">
         <v>13459.615</v>
@@ -7115,37 +7115,37 @@
         <v>3659.1</v>
       </c>
       <c r="M71">
-        <v>1445.535545554333</v>
+        <v>1386.788635054333</v>
       </c>
       <c r="N71">
-        <v>2213.564454445667</v>
+        <v>2272.311364945667</v>
       </c>
       <c r="O71">
-        <v>553.3911136114168</v>
+        <v>568.0778412364167</v>
       </c>
       <c r="P71">
-        <v>1660.17334083425</v>
+        <v>1704.23352370925</v>
       </c>
       <c r="Q71">
-        <v>3584.47334083425</v>
+        <v>3628.53352370925</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1629130355766195</v>
+        <v>0.1628583426343944</v>
       </c>
       <c r="T71">
         <v>2.281684978522916</v>
       </c>
       <c r="U71">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.53131098107782</v>
+        <v>2.638541957662236</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08623208187317233</v>
+        <v>0.08338017828407979</v>
       </c>
       <c r="C72">
-        <v>9870.723810972624</v>
+        <v>12029.93346965364</v>
       </c>
       <c r="D72">
-        <v>28641.87381097263</v>
+        <v>30801.08346965363</v>
       </c>
       <c r="E72">
         <v>13774.95</v>
@@ -7197,45 +7197,45 @@
         <v>3659.1</v>
       </c>
       <c r="M72">
-        <v>1526.083651069613</v>
+        <v>1406.887021069613</v>
       </c>
       <c r="N72">
-        <v>2133.016348930387</v>
+        <v>2252.212978930387</v>
       </c>
       <c r="O72">
-        <v>533.2540872325967</v>
+        <v>563.0532447325967</v>
       </c>
       <c r="P72">
-        <v>1599.76226169779</v>
+        <v>1689.15973419779</v>
       </c>
       <c r="Q72">
-        <v>3524.06226169779</v>
+        <v>3613.45973419779</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1664511937511398</v>
+        <v>0.1663948484541647</v>
       </c>
       <c r="T72">
         <v>2.350618059445059</v>
       </c>
       <c r="U72">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.397706048050106</v>
+        <v>2.600848501124204</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.08618292359473122</v>
+        <v>0.08329057122863592</v>
       </c>
       <c r="C73">
-        <v>9590.254667194553</v>
+        <v>11788.21683031729</v>
       </c>
       <c r="D73">
-        <v>28676.73966719455</v>
+        <v>30874.70183031729</v>
       </c>
       <c r="E73">
         <v>14090.285</v>
@@ -7279,45 +7279,45 @@
         <v>3659.1</v>
       </c>
       <c r="M73">
-        <v>1547.884846084893</v>
+        <v>1426.985407084893</v>
       </c>
       <c r="N73">
-        <v>2111.215153915106</v>
+        <v>2232.114592915107</v>
       </c>
       <c r="O73">
-        <v>527.8037884787766</v>
+        <v>558.0286482287767</v>
       </c>
       <c r="P73">
-        <v>1583.41136543633</v>
+        <v>1674.08594468633</v>
       </c>
       <c r="Q73">
-        <v>3507.711365436329</v>
+        <v>3598.38594468633</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1702333628342476</v>
+        <v>0.1701752512270225</v>
       </c>
       <c r="T73">
         <v>2.424305145948038</v>
       </c>
       <c r="U73">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.363935540331091</v>
+        <v>2.564216832094286</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.08613376531629009</v>
+        <v>0.08320096417319206</v>
       </c>
       <c r="C74">
-        <v>9309.870511537723</v>
+        <v>11546.85294790429</v>
       </c>
       <c r="D74">
-        <v>28711.69051153772</v>
+        <v>30948.67294790429</v>
       </c>
       <c r="E74">
         <v>14405.62</v>
@@ -7361,45 +7361,45 @@
         <v>3659.1</v>
       </c>
       <c r="M74">
-        <v>1569.686041100173</v>
+        <v>1447.083793100174</v>
       </c>
       <c r="N74">
-        <v>2089.413958899826</v>
+        <v>2212.016206899826</v>
       </c>
       <c r="O74">
-        <v>522.3534897249566</v>
+        <v>553.0040517249565</v>
       </c>
       <c r="P74">
-        <v>1567.06046917487</v>
+        <v>1659.01215517487</v>
       </c>
       <c r="Q74">
-        <v>3491.36046917487</v>
+        <v>3583.312155174869</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1742856868518631</v>
+        <v>0.1742256827693701</v>
       </c>
       <c r="T74">
         <v>2.503255595772659</v>
       </c>
       <c r="U74">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.331103102270937</v>
+        <v>2.528602709426309</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.08608460703784897</v>
+        <v>0.08502760711774818</v>
       </c>
       <c r="C75">
-        <v>9029.571655128635</v>
+        <v>9790.385560859282</v>
       </c>
       <c r="D75">
-        <v>28746.72665512863</v>
+        <v>29507.54056085928</v>
       </c>
       <c r="E75">
         <v>14720.955</v>
@@ -7443,37 +7443,37 @@
         <v>3659.1</v>
       </c>
       <c r="M75">
-        <v>1591.487236115454</v>
+        <v>1547.750271615453</v>
       </c>
       <c r="N75">
-        <v>2067.612763884546</v>
+        <v>2111.349728384546</v>
       </c>
       <c r="O75">
-        <v>516.9031909711366</v>
+        <v>527.8374320961366</v>
       </c>
       <c r="P75">
-        <v>1550.70957291341</v>
+        <v>1583.51229628841</v>
       </c>
       <c r="Q75">
-        <v>3475.00957291341</v>
+        <v>3507.812296288409</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1786381830189317</v>
+        <v>0.1785761462778176</v>
       </c>
       <c r="T75">
         <v>2.588054227065771</v>
       </c>
       <c r="U75">
-        <v>0.06913661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.299170183061746</v>
+        <v>2.364141080835243</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.08603544875940784</v>
+        <v>0.08496425006230429</v>
       </c>
       <c r="C76">
-        <v>8749.358410614295</v>
+        <v>9522.785698908723</v>
       </c>
       <c r="D76">
-        <v>28781.8484106143</v>
+        <v>29555.27569890872</v>
       </c>
       <c r="E76">
         <v>15036.29</v>
@@ -7525,37 +7525,37 @@
         <v>3659.1</v>
       </c>
       <c r="M76">
-        <v>1613.288431130734</v>
+        <v>1568.952330130734</v>
       </c>
       <c r="N76">
-        <v>2045.811568869266</v>
+        <v>2090.147669869266</v>
       </c>
       <c r="O76">
-        <v>511.4528922173164</v>
+        <v>522.5369174673165</v>
       </c>
       <c r="P76">
-        <v>1534.358676651949</v>
+        <v>1567.610752401949</v>
       </c>
       <c r="Q76">
-        <v>3458.658676651949</v>
+        <v>3491.910752401949</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.183325486583467</v>
+        <v>0.1832612608253765</v>
       </c>
       <c r="T76">
         <v>2.679375829996814</v>
       </c>
       <c r="U76">
-        <v>0.06913661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.268100315723073</v>
+        <v>2.332193228391524</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.08863004048096672</v>
+        <v>0.08490089300686043</v>
       </c>
       <c r="C77">
-        <v>6690.454065856658</v>
+        <v>9255.340532033137</v>
       </c>
       <c r="D77">
-        <v>27038.27906585666</v>
+        <v>29603.16553203314</v>
       </c>
       <c r="E77">
         <v>15351.625</v>
@@ -7607,45 +7607,45 @@
         <v>3659.1</v>
       </c>
       <c r="M77">
-        <v>1746.245213646014</v>
+        <v>1590.154388646014</v>
       </c>
       <c r="N77">
-        <v>1912.854786353986</v>
+        <v>2068.945611353986</v>
       </c>
       <c r="O77">
-        <v>478.2136965884965</v>
+        <v>517.2364028384966</v>
       </c>
       <c r="P77">
-        <v>1434.641089765489</v>
+        <v>1551.70920851549</v>
       </c>
       <c r="Q77">
-        <v>3358.941089765489</v>
+        <v>3476.009208515489</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1883877744331652</v>
+        <v>0.18832118453674</v>
       </c>
       <c r="T77">
         <v>2.778003161162341</v>
       </c>
       <c r="U77">
-        <v>0.07383661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V77">
         <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.05537746249690056</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.0954101814602</v>
+        <v>2.301097318679637</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.08861613220252559</v>
+        <v>0.08483753595141655</v>
       </c>
       <c r="C78">
-        <v>6383.90210847335</v>
+        <v>8988.050813432608</v>
       </c>
       <c r="D78">
-        <v>27047.06210847335</v>
+        <v>29651.2108134326</v>
       </c>
       <c r="E78">
         <v>15666.96</v>
@@ -7689,45 +7689,45 @@
         <v>3659.1</v>
       </c>
       <c r="M78">
-        <v>1769.528483161294</v>
+        <v>1611.356447161294</v>
       </c>
       <c r="N78">
-        <v>1889.571516838706</v>
+        <v>2047.743552838706</v>
       </c>
       <c r="O78">
-        <v>472.3928792096764</v>
+        <v>511.9358882096765</v>
       </c>
       <c r="P78">
-        <v>1417.178637629029</v>
+        <v>1535.807664629029</v>
       </c>
       <c r="Q78">
-        <v>3341.478637629029</v>
+        <v>3460.107664629029</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1938719196036715</v>
+        <v>0.1938027685573839</v>
       </c>
       <c r="T78">
         <v>2.884849436591662</v>
       </c>
       <c r="U78">
-        <v>0.07383661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.05537746249690056</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.067838994862039</v>
+        <v>2.270819722381221</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.08860222392408448</v>
+        <v>0.0863911788959727</v>
       </c>
       <c r="C79">
-        <v>6077.355859064577</v>
+        <v>7537.804344221564</v>
       </c>
       <c r="D79">
-        <v>27055.85085906458</v>
+        <v>28516.29934422157</v>
       </c>
       <c r="E79">
         <v>15982.295</v>
@@ -7771,37 +7771,37 @@
         <v>3659.1</v>
       </c>
       <c r="M79">
-        <v>1792.811752676575</v>
+        <v>1700.544731676575</v>
       </c>
       <c r="N79">
-        <v>1866.288247323425</v>
+        <v>1958.555268323425</v>
       </c>
       <c r="O79">
-        <v>466.5720618308563</v>
+        <v>489.6388170808563</v>
       </c>
       <c r="P79">
-        <v>1399.716185492569</v>
+        <v>1468.916451242569</v>
       </c>
       <c r="Q79">
-        <v>3324.016185492569</v>
+        <v>3393.216451242569</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1998329469629176</v>
+        <v>0.1997610120580837</v>
       </c>
       <c r="T79">
         <v>3.000986692493098</v>
       </c>
       <c r="U79">
-        <v>0.07383661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V79">
         <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.05537746249690056</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.040983942980714</v>
+        <v>2.151722287476953</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.08858831564564335</v>
+        <v>0.08634882184052883</v>
       </c>
       <c r="C80">
-        <v>5770.815323196472</v>
+        <v>7252.257299026445</v>
       </c>
       <c r="D80">
-        <v>27064.64532319647</v>
+        <v>28546.08729902645</v>
       </c>
       <c r="E80">
         <v>16297.63</v>
@@ -7853,37 +7853,37 @@
         <v>3659.1</v>
       </c>
       <c r="M80">
-        <v>1816.095022191855</v>
+        <v>1722.629728191855</v>
       </c>
       <c r="N80">
-        <v>1843.004977808145</v>
+        <v>1936.470271808145</v>
       </c>
       <c r="O80">
-        <v>460.7512444520363</v>
+        <v>484.1175679520363</v>
       </c>
       <c r="P80">
-        <v>1382.253733356109</v>
+        <v>1452.352703856109</v>
       </c>
       <c r="Q80">
-        <v>3306.553733356109</v>
+        <v>3376.652703856108</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2063358859002769</v>
+        <v>0.2062609140588472</v>
       </c>
       <c r="T80">
         <v>3.127681880749209</v>
       </c>
       <c r="U80">
-        <v>0.07383661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.05537746249690056</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.014817482173269</v>
+        <v>2.124136104304172</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09408465736720223</v>
+        <v>0.08630646478508497</v>
       </c>
       <c r="C81">
-        <v>2374.656157089365</v>
+        <v>6966.772551544054</v>
       </c>
       <c r="D81">
-        <v>23983.82115708937</v>
+        <v>28575.93755154406</v>
       </c>
       <c r="E81">
         <v>16612.965</v>
@@ -7935,45 +7935,45 @@
         <v>3659.1</v>
       </c>
       <c r="M81">
-        <v>2071.054916207135</v>
+        <v>1744.714724707135</v>
       </c>
       <c r="N81">
-        <v>1588.045083792865</v>
+        <v>1914.385275292865</v>
       </c>
       <c r="O81">
-        <v>397.0112709482163</v>
+        <v>478.5963188232163</v>
       </c>
       <c r="P81">
-        <v>1191.033812844649</v>
+        <v>1435.788956469649</v>
       </c>
       <c r="Q81">
-        <v>3115.333812844648</v>
+        <v>3360.088956469649</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.21345815235548</v>
+        <v>0.2133798543453977</v>
       </c>
       <c r="T81">
         <v>3.266443277410666</v>
       </c>
       <c r="U81">
-        <v>0.08313661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V81">
         <v>0.25</v>
       </c>
       <c r="W81">
-        <v>0.06235246249690056</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.766780770208238</v>
+        <v>2.097248305515511</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.09696049908876113</v>
+        <v>0.08626410772964108</v>
       </c>
       <c r="C82">
-        <v>711.1389705493384</v>
+        <v>6681.350297410569</v>
       </c>
       <c r="D82">
-        <v>22635.63897054934</v>
+        <v>28605.85029741057</v>
       </c>
       <c r="E82">
         <v>16928.3</v>
@@ -8017,45 +8017,45 @@
         <v>3659.1</v>
       </c>
       <c r="M82">
-        <v>2215.836761222415</v>
+        <v>1766.799721222415</v>
       </c>
       <c r="N82">
-        <v>1443.263238777585</v>
+        <v>1892.300278777585</v>
       </c>
       <c r="O82">
-        <v>360.8158096943962</v>
+        <v>473.0750696943962</v>
       </c>
       <c r="P82">
-        <v>1082.447429083189</v>
+        <v>1419.225209083188</v>
       </c>
       <c r="Q82">
-        <v>3006.747429083188</v>
+        <v>3343.525209083188</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2212926454562034</v>
+        <v>0.2212106886606032</v>
       </c>
       <c r="T82">
         <v>3.419080813738267</v>
       </c>
       <c r="U82">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V82">
         <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.651340055384485</v>
+        <v>2.071032701696567</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09705159081032</v>
+        <v>0.08622175067419721</v>
       </c>
       <c r="C83">
-        <v>355.5726471930902</v>
+        <v>6395.99073308213</v>
       </c>
       <c r="D83">
-        <v>22595.40764719309</v>
+        <v>28635.82573308213</v>
       </c>
       <c r="E83">
         <v>17243.635</v>
@@ -8099,45 +8099,45 @@
         <v>3659.1</v>
       </c>
       <c r="M83">
-        <v>2243.534720737695</v>
+        <v>1788.884717737695</v>
       </c>
       <c r="N83">
-        <v>1415.565279262305</v>
+        <v>1870.215282262305</v>
       </c>
       <c r="O83">
-        <v>353.8913198155761</v>
+        <v>467.5538205655761</v>
       </c>
       <c r="P83">
-        <v>1061.673959446729</v>
+        <v>1402.661461696728</v>
       </c>
       <c r="Q83">
-        <v>2985.973959446728</v>
+        <v>3326.961461696728</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2299518220412134</v>
+        <v>0.2298658213247777</v>
       </c>
       <c r="T83">
         <v>3.587785459152984</v>
       </c>
       <c r="U83">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V83">
         <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.630953141120479</v>
+        <v>2.04546439673735</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09714268253187887</v>
+        <v>0.08617939361875335</v>
       </c>
       <c r="C84">
-        <v>0.1490799346611311</v>
+        <v>6110.694055839249</v>
       </c>
       <c r="D84">
-        <v>22555.31907993466</v>
+        <v>28665.86405583925</v>
       </c>
       <c r="E84">
         <v>17558.97</v>
@@ -8181,45 +8181,45 @@
         <v>3659.1</v>
       </c>
       <c r="M84">
-        <v>2271.232680252976</v>
+        <v>1810.969714252976</v>
       </c>
       <c r="N84">
-        <v>1387.867319747024</v>
+        <v>1848.130285747024</v>
       </c>
       <c r="O84">
-        <v>346.9668299367561</v>
+        <v>462.0325714367561</v>
       </c>
       <c r="P84">
-        <v>1040.900489810268</v>
+        <v>1386.097714310268</v>
       </c>
       <c r="Q84">
-        <v>2965.200489810268</v>
+        <v>3310.397714310268</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2395731293578912</v>
+        <v>0.2394826353960827</v>
       </c>
       <c r="T84">
         <v>3.775235065169336</v>
       </c>
       <c r="U84">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V84">
         <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.61106346866779</v>
+        <v>2.020519708972261</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09723377425343775</v>
+        <v>0.09099253656330947</v>
       </c>
       <c r="C85">
-        <v>-355.132489709973</v>
+        <v>2742.357126268784</v>
       </c>
       <c r="D85">
-        <v>22515.37251029003</v>
+        <v>25612.86212626879</v>
       </c>
       <c r="E85">
         <v>17874.305</v>
@@ -8263,45 +8263,45 @@
         <v>3659.1</v>
       </c>
       <c r="M85">
-        <v>2298.930639768256</v>
+        <v>2037.202589768256</v>
       </c>
       <c r="N85">
-        <v>1360.169360231744</v>
+        <v>1621.897410231744</v>
       </c>
       <c r="O85">
-        <v>340.042340057936</v>
+        <v>405.4743525579361</v>
       </c>
       <c r="P85">
-        <v>1020.127020173808</v>
+        <v>1216.423057673808</v>
       </c>
       <c r="Q85">
-        <v>2944.427020173808</v>
+        <v>3140.723057673808</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2503263551824135</v>
+        <v>0.2502308393581295</v>
       </c>
       <c r="T85">
         <v>3.984737566011143</v>
       </c>
       <c r="U85">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V85">
         <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690056</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.591653065430828</v>
+        <v>1.796139479881697</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.09732486597499664</v>
+        <v>0.09100867950786559</v>
       </c>
       <c r="C86">
-        <v>-710.2728148610731</v>
+        <v>2417.876382183164</v>
       </c>
       <c r="D86">
-        <v>22475.56718513893</v>
+        <v>25603.71638218316</v>
       </c>
       <c r="E86">
         <v>18189.64</v>
@@ -8345,45 +8345,45 @@
         <v>3659.1</v>
       </c>
       <c r="M86">
-        <v>2326.628599283536</v>
+        <v>2061.747199283535</v>
       </c>
       <c r="N86">
-        <v>1332.471400716464</v>
+        <v>1597.352800716465</v>
       </c>
       <c r="O86">
-        <v>333.1178501791161</v>
+        <v>399.3382001791161</v>
       </c>
       <c r="P86">
-        <v>999.3535505373483</v>
+        <v>1198.014600537349</v>
       </c>
       <c r="Q86">
-        <v>2923.653550537348</v>
+        <v>3122.314600537348</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2624237342350009</v>
+        <v>0.262322568815432</v>
       </c>
       <c r="T86">
         <v>4.220427879458172</v>
       </c>
       <c r="U86">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V86">
         <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690056</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.57270481465189</v>
+        <v>1.774756867025963</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.09741595769655553</v>
+        <v>0.09102482245242172</v>
       </c>
       <c r="C87">
-        <v>-1065.272643322514</v>
+        <v>2093.402167221662</v>
       </c>
       <c r="D87">
-        <v>22435.90235667748</v>
+        <v>25594.57716722166</v>
       </c>
       <c r="E87">
         <v>18504.975</v>
@@ -8427,45 +8427,45 @@
         <v>3659.1</v>
       </c>
       <c r="M87">
-        <v>2354.326558798816</v>
+        <v>2086.291808798816</v>
       </c>
       <c r="N87">
-        <v>1304.773441201184</v>
+        <v>1572.808191201184</v>
       </c>
       <c r="O87">
-        <v>326.193360300296</v>
+        <v>393.2020478002961</v>
       </c>
       <c r="P87">
-        <v>978.5800809008881</v>
+        <v>1179.606143400888</v>
       </c>
       <c r="Q87">
-        <v>2902.880080900888</v>
+        <v>3103.906143400888</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2761340971612669</v>
+        <v>0.2760265288670416</v>
       </c>
       <c r="T87">
         <v>4.487543568031475</v>
       </c>
       <c r="U87">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V87">
         <v>0.25</v>
       </c>
       <c r="W87">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690056</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.554202405067751</v>
+        <v>1.753877374472716</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.09750704941811439</v>
+        <v>0.09355646539697784</v>
       </c>
       <c r="C88">
-        <v>-1420.132717628538</v>
+        <v>421.2596613547248</v>
       </c>
       <c r="D88">
-        <v>22396.37728237146</v>
+        <v>24237.76966135473</v>
       </c>
       <c r="E88">
         <v>18820.31</v>
@@ -8509,37 +8509,37 @@
         <v>3659.1</v>
       </c>
       <c r="M88">
-        <v>2382.024518314096</v>
+        <v>2216.599777314096</v>
       </c>
       <c r="N88">
-        <v>1277.075481685904</v>
+        <v>1442.500222685904</v>
       </c>
       <c r="O88">
-        <v>319.268870421476</v>
+        <v>360.6250556714759</v>
       </c>
       <c r="P88">
-        <v>957.8066112644279</v>
+        <v>1081.875167014428</v>
       </c>
       <c r="Q88">
-        <v>2882.106611264428</v>
+        <v>3006.175167014428</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2918030833627135</v>
+        <v>0.2916881974974526</v>
       </c>
       <c r="T88">
         <v>4.792818640686677</v>
       </c>
       <c r="U88">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V88">
         <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.53613028407859</v>
+        <v>1.65077161761417</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.09759814113967327</v>
+        <v>0.09360185834153398</v>
       </c>
       <c r="C89">
-        <v>-1774.853775090185</v>
+        <v>82.90832323369978</v>
       </c>
       <c r="D89">
-        <v>22356.99122490982</v>
+        <v>24214.7533232337</v>
       </c>
       <c r="E89">
         <v>19135.645</v>
@@ -8591,37 +8591,37 @@
         <v>3659.1</v>
       </c>
       <c r="M89">
-        <v>2409.722477829376</v>
+        <v>2242.374193329376</v>
       </c>
       <c r="N89">
-        <v>1249.377522170624</v>
+        <v>1416.725806670624</v>
       </c>
       <c r="O89">
-        <v>312.3443805426559</v>
+        <v>354.1814516676559</v>
       </c>
       <c r="P89">
-        <v>937.0331416279678</v>
+        <v>1062.544355002968</v>
       </c>
       <c r="Q89">
-        <v>2861.333141627968</v>
+        <v>2986.844355002967</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3098826828259213</v>
+        <v>0.3097593536094653</v>
       </c>
       <c r="T89">
         <v>5.145059109134986</v>
       </c>
       <c r="U89">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V89">
         <v>0.25</v>
       </c>
       <c r="W89">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.518473614146653</v>
+        <v>1.631797231204812</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.09768923286123216</v>
+        <v>0.09364725128609011</v>
       </c>
       <c r="C90">
-        <v>-2129.43654784104</v>
+        <v>-255.3993434398726</v>
       </c>
       <c r="D90">
-        <v>22317.74345215896</v>
+        <v>24191.78065656013</v>
       </c>
       <c r="E90">
         <v>19450.98</v>
@@ -8673,37 +8673,37 @@
         <v>3659.1</v>
       </c>
       <c r="M90">
-        <v>2437.420437344656</v>
+        <v>2268.148609344657</v>
       </c>
       <c r="N90">
-        <v>1221.679562655343</v>
+        <v>1390.951390655343</v>
       </c>
       <c r="O90">
-        <v>305.4198906638359</v>
+        <v>347.7378476638359</v>
       </c>
       <c r="P90">
-        <v>916.2596719915076</v>
+        <v>1043.213542991507</v>
       </c>
       <c r="Q90">
-        <v>2840.559671991507</v>
+        <v>2967.513542991507</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3309755488663303</v>
+        <v>0.3308423690734801</v>
       </c>
       <c r="T90">
         <v>5.556006322324683</v>
       </c>
       <c r="U90">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V90">
         <v>0.25</v>
       </c>
       <c r="W90">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.501218232167713</v>
+        <v>1.613254080850212</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.108660574582791</v>
+        <v>0.09369264423064624</v>
       </c>
       <c r="C91">
-        <v>-6339.9887247892</v>
+        <v>-593.6634628421925</v>
       </c>
       <c r="D91">
-        <v>18422.5262752108</v>
+        <v>24168.85153715781</v>
       </c>
       <c r="E91">
         <v>19766.315</v>
@@ -8755,45 +8755,45 @@
         <v>3659.1</v>
       </c>
       <c r="M91">
-        <v>2922.574881359937</v>
+        <v>2293.923025359937</v>
       </c>
       <c r="N91">
-        <v>736.5251186400633</v>
+        <v>1365.176974640063</v>
       </c>
       <c r="O91">
-        <v>184.1312796600158</v>
+        <v>341.2942436600158</v>
       </c>
       <c r="P91">
-        <v>552.3938389800475</v>
+        <v>1023.882730980047</v>
       </c>
       <c r="Q91">
-        <v>2476.693838980047</v>
+        <v>2948.182730980047</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3559034814595411</v>
+        <v>0.3557586600764067</v>
       </c>
       <c r="T91">
         <v>6.041671210639778</v>
       </c>
       <c r="U91">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V91">
         <v>0.25</v>
       </c>
       <c r="W91">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.252012402945632</v>
+        <v>1.59512763050358</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1332952974779559</v>
+        <v>0.09373803717520236</v>
       </c>
       <c r="C92">
-        <v>-11842.27482845342</v>
+        <v>-931.8841586791277</v>
       </c>
       <c r="D92">
-        <v>13235.57517154658</v>
+        <v>24145.96584132087</v>
       </c>
       <c r="E92">
         <v>20081.65</v>
@@ -8837,45 +8837,45 @@
         <v>3659.1</v>
       </c>
       <c r="M92">
-        <v>3883.443706375217</v>
+        <v>2319.697441375217</v>
       </c>
       <c r="N92">
-        <v>-224.3437063752167</v>
+        <v>1339.402558624783</v>
       </c>
       <c r="O92">
-        <v>-56.08592659380417</v>
+        <v>334.8506396561957</v>
       </c>
       <c r="P92">
-        <v>-168.2577797814125</v>
+        <v>1004.551918968587</v>
       </c>
       <c r="Q92">
-        <v>1756.042220218587</v>
+        <v>2928.851918968587</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.391519671665342</v>
+        <v>0.3856582092799186</v>
       </c>
       <c r="T92">
-        <v>6.735572839819431</v>
+        <v>6.624469076617892</v>
       </c>
       <c r="U92">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V92">
-        <v>0.2355576826048151</v>
+        <v>0.25</v>
       </c>
       <c r="W92">
-        <v>0.1046037003460241</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.9422307304192603</v>
+        <v>1.577403990164651</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1342056636445813</v>
+        <v>0.09378343011975851</v>
       </c>
       <c r="C93">
-        <v>-12293.90448804043</v>
+        <v>-1270.061554188454</v>
       </c>
       <c r="D93">
-        <v>13099.28051195957</v>
+        <v>24123.12344581155</v>
       </c>
       <c r="E93">
         <v>20396.985</v>
@@ -8919,45 +8919,45 @@
         <v>3659.1</v>
       </c>
       <c r="M93">
-        <v>3926.593080890497</v>
+        <v>2345.471857390497</v>
       </c>
       <c r="N93">
-        <v>-267.4930808904969</v>
+        <v>1313.628142609502</v>
       </c>
       <c r="O93">
-        <v>-66.87327022262423</v>
+        <v>328.4070356523756</v>
       </c>
       <c r="P93">
-        <v>-200.6198106678727</v>
+        <v>985.2211069571268</v>
       </c>
       <c r="Q93">
-        <v>1723.680189332127</v>
+        <v>2909.521106957126</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4299329685170467</v>
+        <v>0.4222021027508777</v>
       </c>
       <c r="T93">
-        <v>7.48396982202159</v>
+        <v>7.336777579480032</v>
       </c>
       <c r="U93">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V93">
-        <v>0.2329691366421248</v>
+        <v>0.25</v>
       </c>
       <c r="W93">
-        <v>0.1049579082176341</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.9318765465684993</v>
+        <v>1.560069880382622</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1351160298112066</v>
+        <v>0.09382882306431463</v>
       </c>
       <c r="C94">
-        <v>-12742.75574274219</v>
+        <v>-1608.195772142008</v>
       </c>
       <c r="D94">
-        <v>12965.76425725781</v>
+        <v>24100.32422785799</v>
       </c>
       <c r="E94">
         <v>20712.32</v>
@@ -9001,45 +9001,45 @@
         <v>3659.1</v>
       </c>
       <c r="M94">
-        <v>3969.742455405777</v>
+        <v>2371.246273405777</v>
       </c>
       <c r="N94">
-        <v>-310.6424554057771</v>
+        <v>1287.853726594223</v>
       </c>
       <c r="O94">
-        <v>-77.66061385144428</v>
+        <v>321.9634316485557</v>
       </c>
       <c r="P94">
-        <v>-232.9818415543328</v>
+        <v>965.8902949456671</v>
       </c>
       <c r="Q94">
-        <v>1691.318158445667</v>
+        <v>2890.190294945667</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4779495895816778</v>
+        <v>0.4678819695895765</v>
       </c>
       <c r="T94">
-        <v>8.419466049774293</v>
+        <v>8.227163208057707</v>
       </c>
       <c r="U94">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V94">
-        <v>0.2304368634177539</v>
+        <v>0.25</v>
       </c>
       <c r="W94">
-        <v>0.1053044159181222</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.9217474536710155</v>
+        <v>1.543112599074116</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1360263959778319</v>
+        <v>0.09387421600887075</v>
       </c>
       <c r="C95">
-        <v>-13188.91269319611</v>
+        <v>-1946.28693484798</v>
       </c>
       <c r="D95">
-        <v>12834.94230680389</v>
+        <v>24077.56806515202</v>
       </c>
       <c r="E95">
         <v>21027.655</v>
@@ -9083,45 +9083,45 @@
         <v>3659.1</v>
       </c>
       <c r="M95">
-        <v>4012.891829921057</v>
+        <v>2397.020689421058</v>
       </c>
       <c r="N95">
-        <v>-353.7918299210573</v>
+        <v>1262.079310578942</v>
       </c>
       <c r="O95">
-        <v>-88.44795748026434</v>
+        <v>315.5198276447355</v>
       </c>
       <c r="P95">
-        <v>-265.343872440793</v>
+        <v>946.5594829342066</v>
       </c>
       <c r="Q95">
-        <v>1658.956127559207</v>
+        <v>2870.859482934206</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5396852452362031</v>
+        <v>0.5266132269536178</v>
       </c>
       <c r="T95">
-        <v>9.622246914027762</v>
+        <v>9.371944730514718</v>
       </c>
       <c r="U95">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V95">
-        <v>0.2279590476820791</v>
+        <v>0.25</v>
       </c>
       <c r="W95">
-        <v>0.1056434718401051</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.9118361907283165</v>
+        <v>1.52651999048192</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1369367621444573</v>
+        <v>0.09391960895342688</v>
       </c>
       <c r="C96">
-        <v>-13632.45607971068</v>
+        <v>-2284.335164153017</v>
       </c>
       <c r="D96">
-        <v>12706.73392028933</v>
+        <v>24054.85483584699</v>
       </c>
       <c r="E96">
         <v>21342.99</v>
@@ -9165,45 +9165,45 @@
         <v>3659.1</v>
       </c>
       <c r="M96">
-        <v>4056.041204436337</v>
+        <v>2422.795105436338</v>
       </c>
       <c r="N96">
-        <v>-396.9412044363376</v>
+        <v>1236.304894563662</v>
       </c>
       <c r="O96">
-        <v>-99.23530110908439</v>
+        <v>309.0762236409155</v>
       </c>
       <c r="P96">
-        <v>-297.7059033272532</v>
+        <v>927.2286709227465</v>
       </c>
       <c r="Q96">
-        <v>1626.594096672747</v>
+        <v>2851.528670922746</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6219994527755704</v>
+        <v>0.6049215701056729</v>
       </c>
       <c r="T96">
-        <v>11.22595473303239</v>
+        <v>10.89832009379073</v>
       </c>
       <c r="U96">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V96">
-        <v>0.2255339514301421</v>
+        <v>0.25</v>
       </c>
       <c r="W96">
-        <v>0.1059753138063011</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.9021358057205684</v>
+        <v>1.510280416115092</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1378471283110826</v>
+        <v>0.104082501897983</v>
       </c>
       <c r="C97">
-        <v>-14073.46344843735</v>
+        <v>-6794.186640495493</v>
       </c>
       <c r="D97">
-        <v>12581.06155156265</v>
+        <v>19860.33835950451</v>
       </c>
       <c r="E97">
         <v>21658.325</v>
@@ -9247,45 +9247,45 @@
         <v>3659.1</v>
       </c>
       <c r="M97">
-        <v>4099.190578951618</v>
+        <v>2873.956436451618</v>
       </c>
       <c r="N97">
-        <v>-440.0905789516178</v>
+        <v>785.1435635483822</v>
       </c>
       <c r="O97">
-        <v>-110.0226447379044</v>
+        <v>196.2858908870955</v>
       </c>
       <c r="P97">
-        <v>-330.0679342137133</v>
+        <v>588.8576726612866</v>
       </c>
       <c r="Q97">
-        <v>1594.232065786287</v>
+        <v>2513.157672661287</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.737239343330685</v>
+        <v>0.7145532505185503</v>
       </c>
       <c r="T97">
-        <v>13.47114567963888</v>
+        <v>13.03524560237716</v>
       </c>
       <c r="U97">
-        <v>0.1368366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V97">
-        <v>0.2231599098361406</v>
+        <v>0.25</v>
       </c>
       <c r="W97">
-        <v>0.1063001696258404</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.8926396393445624</v>
+        <v>1.273192576474045</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.138757494477708</v>
+        <v>0.1042343948425391</v>
       </c>
       <c r="C98">
-        <v>-14512.00930777823</v>
+        <v>-7161.146120930942</v>
       </c>
       <c r="D98">
-        <v>12457.85069222177</v>
+        <v>19808.71387906906</v>
       </c>
       <c r="E98">
         <v>21973.66</v>
@@ -9329,45 +9329,45 @@
         <v>3659.1</v>
       </c>
       <c r="M98">
-        <v>4142.339953466898</v>
+        <v>2904.208609466898</v>
       </c>
       <c r="N98">
-        <v>-483.239953466898</v>
+        <v>754.8913905331019</v>
       </c>
       <c r="O98">
-        <v>-120.8099883667245</v>
+        <v>188.7228476332755</v>
       </c>
       <c r="P98">
-        <v>-362.4299651001735</v>
+        <v>566.1685428998264</v>
       </c>
       <c r="Q98">
-        <v>1561.870034899826</v>
+        <v>2490.468542899826</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.9100991791633541</v>
+        <v>0.8790007711378642</v>
       </c>
       <c r="T98">
-        <v>16.83893209954856</v>
+        <v>16.24063386525675</v>
       </c>
       <c r="U98">
-        <v>0.1368366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V98">
-        <v>0.2208353274420141</v>
+        <v>0.25</v>
       </c>
       <c r="W98">
-        <v>0.106618257615806</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.8833413097680565</v>
+        <v>1.25993015380244</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1396678606443333</v>
+        <v>0.1268025012303168</v>
       </c>
       <c r="C99">
-        <v>-14948.16527569227</v>
+        <v>-12995.3867773968</v>
       </c>
       <c r="D99">
-        <v>12337.02972430773</v>
+        <v>14289.8082226032</v>
       </c>
       <c r="E99">
         <v>22288.995</v>
@@ -9411,37 +9411,37 @@
         <v>3659.1</v>
       </c>
       <c r="M99">
-        <v>4185.489327982177</v>
+        <v>3809.263139482178</v>
       </c>
       <c r="N99">
-        <v>-526.3893279821773</v>
+        <v>-150.1631394821784</v>
       </c>
       <c r="O99">
-        <v>-131.5973319955443</v>
+        <v>-37.5407848705446</v>
       </c>
       <c r="P99">
-        <v>-394.791995986633</v>
+        <v>-112.6223546116338</v>
       </c>
       <c r="Q99">
-        <v>1529.508004013367</v>
+        <v>1811.677645388366</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.198198905551139</v>
+        <v>1.167053591750588</v>
       </c>
       <c r="T99">
-        <v>22.45190946606474</v>
+        <v>21.85531949143179</v>
       </c>
       <c r="U99">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V99">
-        <v>0.2185586745817872</v>
+        <v>0.2401448696254552</v>
       </c>
       <c r="W99">
-        <v>0.1069297870905145</v>
+        <v>0.09462978709051455</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.874234698327149</v>
+        <v>0.9605794785018209</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1405782268109586</v>
+        <v>0.1275898673969421</v>
       </c>
       <c r="C100">
-        <v>-15382.00021851207</v>
+        <v>-13448.28541309066</v>
       </c>
       <c r="D100">
-        <v>12218.52978148792</v>
+        <v>14152.24458690934</v>
       </c>
       <c r="E100">
         <v>22604.33</v>
@@ -9493,37 +9493,37 @@
         <v>3659.1</v>
       </c>
       <c r="M100">
-        <v>4228.638702497457</v>
+        <v>3848.533893497458</v>
       </c>
       <c r="N100">
-        <v>-569.5387024974575</v>
+        <v>-189.4338934974585</v>
       </c>
       <c r="O100">
-        <v>-142.3846756243644</v>
+        <v>-47.35847337436462</v>
       </c>
       <c r="P100">
-        <v>-427.1540268730931</v>
+        <v>-142.0754201230939</v>
       </c>
       <c r="Q100">
-        <v>1497.145973126906</v>
+        <v>1782.224579876906</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.774398358326708</v>
+        <v>1.727680387625881</v>
       </c>
       <c r="T100">
-        <v>33.67786419909712</v>
+        <v>32.78297923714769</v>
       </c>
       <c r="U100">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V100">
-        <v>0.2163284840248302</v>
+        <v>0.2376944117721343</v>
       </c>
       <c r="W100">
-        <v>0.1072349588208413</v>
+        <v>0.09493495882084128</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8653139360993208</v>
+        <v>0.9507776470885371</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.141488592977584</v>
+        <v>0.1283772335635674</v>
       </c>
       <c r="C101">
-        <v>-15813.58038183657</v>
+        <v>-13898.56073609097</v>
       </c>
       <c r="D101">
-        <v>12102.28461816343</v>
+        <v>14017.30426390903</v>
       </c>
       <c r="E101">
         <v>22919.665</v>
@@ -9575,37 +9575,37 @@
         <v>3659.1</v>
       </c>
       <c r="M101">
-        <v>4271.788077012739</v>
+        <v>3887.804647512739</v>
       </c>
       <c r="N101">
-        <v>-612.6880770127386</v>
+        <v>-228.704647512739</v>
       </c>
       <c r="O101">
-        <v>-153.1720192531847</v>
+        <v>-57.17616187818476</v>
       </c>
       <c r="P101">
-        <v>-459.516057759554</v>
+        <v>-171.5284856345543</v>
       </c>
       <c r="Q101">
-        <v>1464.783942240446</v>
+        <v>1752.771514365445</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.502996716653417</v>
+        <v>3.409560775251763</v>
       </c>
       <c r="T101">
-        <v>67.35572839819424</v>
+        <v>65.56595847429537</v>
       </c>
       <c r="U101">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V101">
-        <v>0.2141433478225591</v>
+        <v>0.2352934581178703</v>
       </c>
       <c r="W101">
-        <v>0.1075339654657068</v>
+        <v>0.09523396546570687</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.8565733912902366</v>
+        <v>0.941173832471481</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/france/france_rubber_tires.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08965267216515078</v>
+        <v>0.08950681510970691</v>
       </c>
       <c r="C2">
-        <v>29697.731589053</v>
+        <v>29470.48262138197</v>
       </c>
       <c r="D2">
-        <v>26395.43158905301</v>
+        <v>26483.51762138197</v>
       </c>
       <c r="E2">
-        <v>-8298.5</v>
+        <v>-7983.165</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>315.335</v>
       </c>
       <c r="G2">
         <v>3302.3</v>
@@ -1457,28 +1457,28 @@
         <v>3659.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>17.73337351528019</v>
       </c>
       <c r="N2">
-        <v>3659.1</v>
+        <v>3641.36662648472</v>
       </c>
       <c r="O2">
-        <v>914.775</v>
+        <v>910.3416566211799</v>
       </c>
       <c r="P2">
-        <v>2744.325</v>
+        <v>2731.02496986354</v>
       </c>
       <c r="Q2">
-        <v>4668.625</v>
+        <v>4655.324969863539</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08965267216515078</v>
+        <v>0.08998488937852314</v>
       </c>
       <c r="T2">
-        <v>0.8547702034345666</v>
+        <v>0.8612457352787678</v>
       </c>
       <c r="U2">
         <v>0.05623661666253409</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>206.3397580188051</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08950681510970691</v>
+        <v>0.08936095805426304</v>
       </c>
       <c r="C3">
-        <v>29470.48262138197</v>
+        <v>29243.82353831747</v>
       </c>
       <c r="D3">
-        <v>26483.51762138197</v>
+        <v>26572.19353831746</v>
       </c>
       <c r="E3">
-        <v>-7983.165</v>
+        <v>-7667.83</v>
       </c>
       <c r="F3">
-        <v>315.335</v>
+        <v>630.67</v>
       </c>
       <c r="G3">
         <v>3302.3</v>
@@ -1539,28 +1539,28 @@
         <v>3659.1</v>
       </c>
       <c r="M3">
-        <v>17.73337351528019</v>
+        <v>35.46674703056037</v>
       </c>
       <c r="N3">
-        <v>3641.36662648472</v>
+        <v>3623.63325296944</v>
       </c>
       <c r="O3">
-        <v>910.3416566211799</v>
+        <v>905.9083132423599</v>
       </c>
       <c r="P3">
-        <v>2731.02496986354</v>
+        <v>2717.72493972708</v>
       </c>
       <c r="Q3">
-        <v>4655.324969863539</v>
+        <v>4642.02493972708</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08998488937852314</v>
+        <v>0.09032388653502554</v>
       </c>
       <c r="T3">
-        <v>0.8612457352787678</v>
+        <v>0.8678534208340752</v>
       </c>
       <c r="U3">
         <v>0.05623661666253409</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>206.3397580188051</v>
+        <v>103.1698790094025</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08936095805426304</v>
+        <v>0.08921510099881916</v>
       </c>
       <c r="C4">
-        <v>29243.82353831747</v>
+        <v>29017.76028517553</v>
       </c>
       <c r="D4">
-        <v>26572.19353831746</v>
+        <v>26661.46528517553</v>
       </c>
       <c r="E4">
-        <v>-7667.83</v>
+        <v>-7352.495</v>
       </c>
       <c r="F4">
-        <v>630.67</v>
+        <v>946.005</v>
       </c>
       <c r="G4">
         <v>3302.3</v>
@@ -1621,28 +1621,28 @@
         <v>3659.1</v>
       </c>
       <c r="M4">
-        <v>35.46674703056037</v>
+        <v>53.20012054584056</v>
       </c>
       <c r="N4">
-        <v>3623.63325296944</v>
+        <v>3605.899879454159</v>
       </c>
       <c r="O4">
-        <v>905.9083132423599</v>
+        <v>901.4749698635399</v>
       </c>
       <c r="P4">
-        <v>2717.72493972708</v>
+        <v>2704.42490959062</v>
       </c>
       <c r="Q4">
-        <v>4642.02493972708</v>
+        <v>4628.724909590619</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09032388653502554</v>
+        <v>0.09066987332362077</v>
       </c>
       <c r="T4">
-        <v>0.8678534208340752</v>
+        <v>0.8745973473286672</v>
       </c>
       <c r="U4">
         <v>0.05623661666253409</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>103.1698790094025</v>
+        <v>68.77991933960169</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08921510099881916</v>
+        <v>0.0890692439433753</v>
       </c>
       <c r="C5">
-        <v>29017.76028517553</v>
+        <v>28792.29888743683</v>
       </c>
       <c r="D5">
-        <v>26661.46528517553</v>
+        <v>26751.33888743684</v>
       </c>
       <c r="E5">
-        <v>-7352.495</v>
+        <v>-7037.16</v>
       </c>
       <c r="F5">
-        <v>946.005</v>
+        <v>1261.34</v>
       </c>
       <c r="G5">
         <v>3302.3</v>
@@ -1703,28 +1703,28 @@
         <v>3659.1</v>
       </c>
       <c r="M5">
-        <v>53.20012054584056</v>
+        <v>70.93349406112074</v>
       </c>
       <c r="N5">
-        <v>3605.899879454159</v>
+        <v>3588.166505938879</v>
       </c>
       <c r="O5">
-        <v>901.4749698635399</v>
+        <v>897.0416264847198</v>
       </c>
       <c r="P5">
-        <v>2704.42490959062</v>
+        <v>2691.124879454159</v>
       </c>
       <c r="Q5">
-        <v>4628.724909590619</v>
+        <v>4615.424879454159</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09066987332362077</v>
+        <v>0.09102306817031175</v>
       </c>
       <c r="T5">
-        <v>0.8745973473286672</v>
+        <v>0.8814817722918967</v>
       </c>
       <c r="U5">
         <v>0.05623661666253409</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.77991933960169</v>
+        <v>51.58493950470127</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0890692439433753</v>
+        <v>0.08892338688793143</v>
       </c>
       <c r="C6">
-        <v>28792.29888743683</v>
+        <v>28567.44545210249</v>
       </c>
       <c r="D6">
-        <v>26751.33888743684</v>
+        <v>26841.82045210249</v>
       </c>
       <c r="E6">
-        <v>-7037.16</v>
+        <v>-6721.825</v>
       </c>
       <c r="F6">
-        <v>1261.34</v>
+        <v>1576.675</v>
       </c>
       <c r="G6">
         <v>3302.3</v>
@@ -1785,28 +1785,28 @@
         <v>3659.1</v>
       </c>
       <c r="M6">
-        <v>70.93349406112074</v>
+        <v>88.66686757640095</v>
       </c>
       <c r="N6">
-        <v>3588.166505938879</v>
+        <v>3570.433132423599</v>
       </c>
       <c r="O6">
-        <v>897.0416264847198</v>
+        <v>892.6082831058998</v>
       </c>
       <c r="P6">
-        <v>2691.124879454159</v>
+        <v>2677.824849317699</v>
       </c>
       <c r="Q6">
-        <v>4615.424879454159</v>
+        <v>4602.124849317699</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09102306817031175</v>
+        <v>0.09138369869798568</v>
       </c>
       <c r="T6">
-        <v>0.8814817722918967</v>
+        <v>0.88851113251751</v>
       </c>
       <c r="U6">
         <v>0.05623661666253409</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.58493950470127</v>
+        <v>41.26795160376101</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08892338688793143</v>
+        <v>0.08877752983248755</v>
       </c>
       <c r="C7">
-        <v>28567.44545210249</v>
+        <v>28343.20616907731</v>
       </c>
       <c r="D7">
-        <v>26841.82045210249</v>
+        <v>26932.91616907731</v>
       </c>
       <c r="E7">
-        <v>-6721.825</v>
+        <v>-6406.49</v>
       </c>
       <c r="F7">
-        <v>1576.675</v>
+        <v>1892.01</v>
       </c>
       <c r="G7">
         <v>3302.3</v>
@@ -1867,28 +1867,28 @@
         <v>3659.1</v>
       </c>
       <c r="M7">
-        <v>88.66686757640095</v>
+        <v>106.4002410916811</v>
       </c>
       <c r="N7">
-        <v>3570.433132423599</v>
+        <v>3552.699758908319</v>
       </c>
       <c r="O7">
-        <v>892.6082831058998</v>
+        <v>888.1749397270797</v>
       </c>
       <c r="P7">
-        <v>2677.824849317699</v>
+        <v>2664.524819181239</v>
       </c>
       <c r="Q7">
-        <v>4602.124849317699</v>
+        <v>4588.824819181239</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09138369869798568</v>
+        <v>0.09175200221561013</v>
       </c>
       <c r="T7">
-        <v>0.88851113251751</v>
+        <v>0.8956900535989872</v>
       </c>
       <c r="U7">
         <v>0.05623661666253409</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.26795160376101</v>
+        <v>34.38995966980084</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08877752983248755</v>
+        <v>0.08863167277704369</v>
       </c>
       <c r="C8">
-        <v>28343.20616907732</v>
+        <v>28119.58731258136</v>
       </c>
       <c r="D8">
-        <v>26932.91616907731</v>
+        <v>27024.63231258137</v>
       </c>
       <c r="E8">
-        <v>-6406.49</v>
+        <v>-6091.155000000001</v>
       </c>
       <c r="F8">
-        <v>1892.01</v>
+        <v>2207.345</v>
       </c>
       <c r="G8">
         <v>3302.3</v>
@@ -1949,28 +1949,28 @@
         <v>3659.1</v>
       </c>
       <c r="M8">
-        <v>106.4002410916811</v>
+        <v>124.1336146069613</v>
       </c>
       <c r="N8">
-        <v>3552.699758908319</v>
+        <v>3534.966385393039</v>
       </c>
       <c r="O8">
-        <v>888.1749397270797</v>
+        <v>883.7415963482597</v>
       </c>
       <c r="P8">
-        <v>2664.524819181239</v>
+        <v>2651.224789044779</v>
       </c>
       <c r="Q8">
-        <v>4588.824819181239</v>
+        <v>4575.524789044779</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09175200221561013</v>
+        <v>0.09212822623898995</v>
       </c>
       <c r="T8">
-        <v>0.8956900535989872</v>
+        <v>0.9030233600800662</v>
       </c>
       <c r="U8">
         <v>0.05623661666253409</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.38995966980085</v>
+        <v>29.47710828840072</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08863167277704367</v>
+        <v>0.08848581572159982</v>
       </c>
       <c r="C9">
-        <v>28119.58731258137</v>
+        <v>27896.59524259059</v>
       </c>
       <c r="D9">
-        <v>27024.63231258138</v>
+        <v>27116.97524259059</v>
       </c>
       <c r="E9">
-        <v>-6091.155</v>
+        <v>-5775.82</v>
       </c>
       <c r="F9">
-        <v>2207.345</v>
+        <v>2522.68</v>
       </c>
       <c r="G9">
         <v>3302.3</v>
@@ -2031,28 +2031,28 @@
         <v>3659.1</v>
       </c>
       <c r="M9">
-        <v>124.1336146069613</v>
+        <v>141.8669881222415</v>
       </c>
       <c r="N9">
-        <v>3534.966385393039</v>
+        <v>3517.233011877759</v>
       </c>
       <c r="O9">
-        <v>883.7415963482597</v>
+        <v>879.3082529694396</v>
       </c>
       <c r="P9">
-        <v>2651.224789044779</v>
+        <v>2637.924758908319</v>
       </c>
       <c r="Q9">
-        <v>4575.524789044779</v>
+        <v>4562.224758908318</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09212822623898995</v>
+        <v>0.09251262904548671</v>
       </c>
       <c r="T9">
-        <v>0.9030233600800662</v>
+        <v>0.9105160862672558</v>
       </c>
       <c r="U9">
         <v>0.05623661666253409</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.47710828840072</v>
+        <v>25.79246975235063</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08848581572159982</v>
+        <v>0.08833995866615593</v>
       </c>
       <c r="C10">
-        <v>27896.59524259059</v>
+        <v>27674.23640630689</v>
       </c>
       <c r="D10">
-        <v>27116.97524259059</v>
+        <v>27209.95140630689</v>
       </c>
       <c r="E10">
-        <v>-5775.82</v>
+        <v>-5460.485000000001</v>
       </c>
       <c r="F10">
-        <v>2522.68</v>
+        <v>2838.015</v>
       </c>
       <c r="G10">
         <v>3302.3</v>
@@ -2113,28 +2113,28 @@
         <v>3659.1</v>
       </c>
       <c r="M10">
-        <v>141.8669881222415</v>
+        <v>159.6003616375217</v>
       </c>
       <c r="N10">
-        <v>3517.233011877759</v>
+        <v>3499.499638362478</v>
       </c>
       <c r="O10">
-        <v>879.3082529694396</v>
+        <v>874.8749095906196</v>
       </c>
       <c r="P10">
-        <v>2637.924758908319</v>
+        <v>2624.624728771859</v>
       </c>
       <c r="Q10">
-        <v>4562.224758908318</v>
+        <v>4548.924728771859</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09251262904548671</v>
+        <v>0.09290548026531306</v>
       </c>
       <c r="T10">
-        <v>0.9105160862672558</v>
+        <v>0.9181734877552624</v>
       </c>
       <c r="U10">
         <v>0.05623661666253409</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.79246975235063</v>
+        <v>22.92663977986723</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08833995866615593</v>
+        <v>0.08819410161071208</v>
       </c>
       <c r="C11">
-        <v>27674.23640630689</v>
+        <v>27452.51733965861</v>
       </c>
       <c r="D11">
-        <v>27209.95140630689</v>
+        <v>27303.56733965861</v>
       </c>
       <c r="E11">
-        <v>-5460.485000000001</v>
+        <v>-5145.15</v>
       </c>
       <c r="F11">
-        <v>2838.015</v>
+        <v>3153.35</v>
       </c>
       <c r="G11">
         <v>3302.3</v>
@@ -2195,28 +2195,28 @@
         <v>3659.1</v>
       </c>
       <c r="M11">
-        <v>159.6003616375217</v>
+        <v>177.3337351528019</v>
       </c>
       <c r="N11">
-        <v>3499.499638362478</v>
+        <v>3481.766264847198</v>
       </c>
       <c r="O11">
-        <v>874.8749095906196</v>
+        <v>870.4415662117995</v>
       </c>
       <c r="P11">
-        <v>2624.624728771859</v>
+        <v>2611.324698635398</v>
       </c>
       <c r="Q11">
-        <v>4548.924728771859</v>
+        <v>4535.624698635398</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09290548026531306</v>
+        <v>0.09330706151224669</v>
       </c>
       <c r="T11">
-        <v>0.9181734877552624</v>
+        <v>0.9260010537207803</v>
       </c>
       <c r="U11">
         <v>0.05623661666253409</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.92663977986723</v>
+        <v>20.6339758018805</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08819410161071208</v>
+        <v>0.0880482445552682</v>
       </c>
       <c r="C12">
-        <v>27452.5173396586</v>
+        <v>27231.44466883222</v>
       </c>
       <c r="D12">
-        <v>27303.56733965861</v>
+        <v>27397.82966883222</v>
       </c>
       <c r="E12">
-        <v>-5145.15</v>
+        <v>-4829.815000000001</v>
       </c>
       <c r="F12">
-        <v>3153.35</v>
+        <v>3468.685</v>
       </c>
       <c r="G12">
         <v>3302.3</v>
@@ -2277,28 +2277,28 @@
         <v>3659.1</v>
       </c>
       <c r="M12">
-        <v>177.3337351528019</v>
+        <v>195.0671086680821</v>
       </c>
       <c r="N12">
-        <v>3481.766264847198</v>
+        <v>3464.032891331918</v>
       </c>
       <c r="O12">
-        <v>870.4415662117995</v>
+        <v>866.0082228329794</v>
       </c>
       <c r="P12">
-        <v>2611.324698635398</v>
+        <v>2598.024668498938</v>
       </c>
       <c r="Q12">
-        <v>4535.624698635398</v>
+        <v>4522.324668498938</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09330706151224669</v>
+        <v>0.0937176670568642</v>
       </c>
       <c r="T12">
-        <v>0.9260010537207803</v>
+        <v>0.9340045200450742</v>
       </c>
       <c r="U12">
         <v>0.05623661666253409</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.6339758018805</v>
+        <v>18.75815981989137</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0880482445552682</v>
+        <v>0.08790238749982433</v>
       </c>
       <c r="C13">
-        <v>27231.44466883222</v>
+        <v>27011.02511183566</v>
       </c>
       <c r="D13">
-        <v>27397.82966883222</v>
+        <v>27492.74511183566</v>
       </c>
       <c r="E13">
-        <v>-4829.815000000001</v>
+        <v>-4514.48</v>
       </c>
       <c r="F13">
-        <v>3468.685</v>
+        <v>3784.02</v>
       </c>
       <c r="G13">
         <v>3302.3</v>
@@ -2359,28 +2359,28 @@
         <v>3659.1</v>
       </c>
       <c r="M13">
-        <v>195.0671086680821</v>
+        <v>212.8004821833622</v>
       </c>
       <c r="N13">
-        <v>3464.032891331918</v>
+        <v>3446.299517816637</v>
       </c>
       <c r="O13">
-        <v>866.0082228329794</v>
+        <v>861.5748794541594</v>
       </c>
       <c r="P13">
-        <v>2598.024668498938</v>
+        <v>2584.724638362478</v>
       </c>
       <c r="Q13">
-        <v>4522.324668498938</v>
+        <v>4509.024638362478</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0937176670568642</v>
+        <v>0.09413760454567757</v>
       </c>
       <c r="T13">
-        <v>0.9340045200450742</v>
+        <v>0.9421898833312836</v>
       </c>
       <c r="U13">
         <v>0.05623661666253409</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.75815981989137</v>
+        <v>17.19497983490042</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08790238749982433</v>
+        <v>0.08775653044438046</v>
       </c>
       <c r="C14">
-        <v>27011.02511183566</v>
+        <v>26791.26548009442</v>
       </c>
       <c r="D14">
-        <v>27492.74511183566</v>
+        <v>27588.32048009442</v>
       </c>
       <c r="E14">
-        <v>-4514.48</v>
+        <v>-4199.145</v>
       </c>
       <c r="F14">
-        <v>3784.02</v>
+        <v>4099.355</v>
       </c>
       <c r="G14">
         <v>3302.3</v>
@@ -2441,28 +2441,28 @@
         <v>3659.1</v>
       </c>
       <c r="M14">
-        <v>212.8004821833622</v>
+        <v>230.5338556986424</v>
       </c>
       <c r="N14">
-        <v>3446.299517816637</v>
+        <v>3428.566144301357</v>
       </c>
       <c r="O14">
-        <v>861.5748794541594</v>
+        <v>857.1415360753393</v>
       </c>
       <c r="P14">
-        <v>2584.724638362478</v>
+        <v>2571.424608226018</v>
       </c>
       <c r="Q14">
-        <v>4509.024638362478</v>
+        <v>4495.724608226017</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09413760454567757</v>
+        <v>0.09456719576986596</v>
       </c>
       <c r="T14">
-        <v>0.9421898833312836</v>
+        <v>0.9505634158884404</v>
       </c>
       <c r="U14">
         <v>0.05623661666253409</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.19497983490042</v>
+        <v>15.87228907836962</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08775653044438046</v>
+        <v>0.08761067338893659</v>
       </c>
       <c r="C15">
-        <v>26791.26548009442</v>
+        <v>26572.17268008092</v>
       </c>
       <c r="D15">
-        <v>27588.32048009442</v>
+        <v>27684.56268008092</v>
       </c>
       <c r="E15">
-        <v>-4199.145</v>
+        <v>-3883.809999999999</v>
       </c>
       <c r="F15">
-        <v>4099.355</v>
+        <v>4414.690000000001</v>
       </c>
       <c r="G15">
         <v>3302.3</v>
@@ -2523,28 +2523,28 @@
         <v>3659.1</v>
       </c>
       <c r="M15">
-        <v>230.5338556986424</v>
+        <v>248.2672292139226</v>
       </c>
       <c r="N15">
-        <v>3428.566144301357</v>
+        <v>3410.832770786077</v>
       </c>
       <c r="O15">
-        <v>857.1415360753393</v>
+        <v>852.7081926965193</v>
       </c>
       <c r="P15">
-        <v>2571.424608226018</v>
+        <v>2558.124578089558</v>
       </c>
       <c r="Q15">
-        <v>4495.724608226017</v>
+        <v>4482.424578089558</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09456719576986596</v>
+        <v>0.09500677748764012</v>
       </c>
       <c r="T15">
-        <v>0.9505634158884404</v>
+        <v>0.9591316817608799</v>
       </c>
       <c r="U15">
         <v>0.05623661666253409</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.87228907836962</v>
+        <v>14.73855414420036</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08761067338893659</v>
+        <v>0.08746481633349271</v>
       </c>
       <c r="C16">
-        <v>26572.17268008092</v>
+        <v>26353.75371497826</v>
       </c>
       <c r="D16">
-        <v>27684.56268008092</v>
+        <v>27781.47871497826</v>
       </c>
       <c r="E16">
-        <v>-3883.809999999999</v>
+        <v>-3568.474999999999</v>
       </c>
       <c r="F16">
-        <v>4414.690000000001</v>
+        <v>4730.025000000001</v>
       </c>
       <c r="G16">
         <v>3302.3</v>
@@ -2605,28 +2605,28 @@
         <v>3659.1</v>
       </c>
       <c r="M16">
-        <v>248.2672292139226</v>
+        <v>266.0006027292028</v>
       </c>
       <c r="N16">
-        <v>3410.832770786077</v>
+        <v>3393.099397270797</v>
       </c>
       <c r="O16">
-        <v>852.7081926965193</v>
+        <v>848.2748493176992</v>
       </c>
       <c r="P16">
-        <v>2558.124578089558</v>
+        <v>2544.824547953098</v>
       </c>
       <c r="Q16">
-        <v>4482.424578089558</v>
+        <v>4469.124547953097</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09500677748764012</v>
+        <v>0.09545670230465603</v>
       </c>
       <c r="T16">
-        <v>0.9591316817608799</v>
+        <v>0.9679015538891416</v>
       </c>
       <c r="U16">
         <v>0.05623661666253409</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.73855414420036</v>
+        <v>13.75598386792034</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08746481633349271</v>
+        <v>0.08731895927804884</v>
       </c>
       <c r="C17">
-        <v>26353.75371497827</v>
+        <v>26136.01568637889</v>
       </c>
       <c r="D17">
-        <v>27781.47871497826</v>
+        <v>27879.07568637889</v>
       </c>
       <c r="E17">
-        <v>-3568.475</v>
+        <v>-3253.14</v>
       </c>
       <c r="F17">
-        <v>4730.025</v>
+        <v>5045.36</v>
       </c>
       <c r="G17">
         <v>3302.3</v>
@@ -2687,28 +2687,28 @@
         <v>3659.1</v>
       </c>
       <c r="M17">
-        <v>266.0006027292028</v>
+        <v>283.733976244483</v>
       </c>
       <c r="N17">
-        <v>3393.099397270797</v>
+        <v>3375.366023755517</v>
       </c>
       <c r="O17">
-        <v>848.2748493176992</v>
+        <v>843.8415059388792</v>
       </c>
       <c r="P17">
-        <v>2544.824547953098</v>
+        <v>2531.524517816638</v>
       </c>
       <c r="Q17">
-        <v>4469.124547953097</v>
+        <v>4455.824517816638</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09545670230465603</v>
+        <v>0.09591733961731518</v>
       </c>
       <c r="T17">
-        <v>0.9679015538891416</v>
+        <v>0.9768802324966475</v>
       </c>
       <c r="U17">
         <v>0.05623661666253409</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.75598386792034</v>
+        <v>12.89623487617532</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08731895927804884</v>
+        <v>0.08717310222260496</v>
       </c>
       <c r="C18">
-        <v>26136.01568637889</v>
+        <v>25918.96579601929</v>
       </c>
       <c r="D18">
-        <v>27879.07568637889</v>
+        <v>27977.36079601929</v>
       </c>
       <c r="E18">
-        <v>-3253.14</v>
+        <v>-2937.804999999999</v>
       </c>
       <c r="F18">
-        <v>5045.36</v>
+        <v>5360.695000000001</v>
       </c>
       <c r="G18">
         <v>3302.3</v>
@@ -2769,28 +2769,28 @@
         <v>3659.1</v>
       </c>
       <c r="M18">
-        <v>283.733976244483</v>
+        <v>301.4673497597632</v>
       </c>
       <c r="N18">
-        <v>3375.366023755517</v>
+        <v>3357.632650240237</v>
       </c>
       <c r="O18">
-        <v>843.8415059388792</v>
+        <v>839.4081625600592</v>
       </c>
       <c r="P18">
-        <v>2531.524517816638</v>
+        <v>2518.224487680177</v>
       </c>
       <c r="Q18">
-        <v>4455.824517816638</v>
+        <v>4442.524487680177</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09591733961731518</v>
+        <v>0.09638907662425528</v>
       </c>
       <c r="T18">
-        <v>0.9768802324966475</v>
+        <v>0.9860752648055392</v>
       </c>
       <c r="U18">
         <v>0.05623661666253409</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.89623487617532</v>
+        <v>12.13763282463559</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08717310222260496</v>
+        <v>0.08702724516716108</v>
       </c>
       <c r="C19">
-        <v>25918.96579601929</v>
+        <v>25702.61134755148</v>
       </c>
       <c r="D19">
-        <v>27977.36079601929</v>
+        <v>28076.34134755148</v>
       </c>
       <c r="E19">
-        <v>-2937.804999999999</v>
+        <v>-2622.469999999999</v>
       </c>
       <c r="F19">
-        <v>5360.695000000001</v>
+        <v>5676.030000000001</v>
       </c>
       <c r="G19">
         <v>3302.3</v>
@@ -2851,28 +2851,28 @@
         <v>3659.1</v>
       </c>
       <c r="M19">
-        <v>301.4673497597632</v>
+        <v>319.2007232750434</v>
       </c>
       <c r="N19">
-        <v>3357.632650240237</v>
+        <v>3339.899276724957</v>
       </c>
       <c r="O19">
-        <v>839.4081625600592</v>
+        <v>834.9748191812391</v>
       </c>
       <c r="P19">
-        <v>2518.224487680177</v>
+        <v>2504.924457543717</v>
       </c>
       <c r="Q19">
-        <v>4442.524487680177</v>
+        <v>4429.224457543717</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09638907662425528</v>
+        <v>0.09687231941185243</v>
       </c>
       <c r="T19">
-        <v>0.9860752648055392</v>
+        <v>0.9954945661951353</v>
       </c>
       <c r="U19">
         <v>0.05623661666253409</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.13763282463559</v>
+        <v>11.46331988993361</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08702724516716109</v>
+        <v>0.08688138811171724</v>
       </c>
       <c r="C20">
-        <v>25702.61134755147</v>
+        <v>25486.95974835219</v>
       </c>
       <c r="D20">
-        <v>28076.34134755147</v>
+        <v>28176.02474835219</v>
       </c>
       <c r="E20">
-        <v>-2622.47</v>
+        <v>-2307.135</v>
       </c>
       <c r="F20">
-        <v>5676.03</v>
+        <v>5991.365</v>
       </c>
       <c r="G20">
         <v>3302.3</v>
@@ -2933,28 +2933,28 @@
         <v>3659.1</v>
       </c>
       <c r="M20">
-        <v>319.2007232750433</v>
+        <v>336.9340967903235</v>
       </c>
       <c r="N20">
-        <v>3339.899276724957</v>
+        <v>3322.165903209676</v>
       </c>
       <c r="O20">
-        <v>834.9748191812391</v>
+        <v>830.5414758024191</v>
       </c>
       <c r="P20">
-        <v>2504.924457543717</v>
+        <v>2491.624427407257</v>
       </c>
       <c r="Q20">
-        <v>4429.224457543717</v>
+        <v>4415.924427407257</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09687231941185243</v>
+        <v>0.09736749412013102</v>
       </c>
       <c r="T20">
-        <v>0.9954945661951353</v>
+        <v>1.005146442927685</v>
       </c>
       <c r="U20">
         <v>0.05623661666253409</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.46331988993361</v>
+        <v>10.85998726414764</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08688138811171724</v>
+        <v>0.08673553105627337</v>
       </c>
       <c r="C21">
-        <v>25486.95974835219</v>
+        <v>25272.01851137089</v>
       </c>
       <c r="D21">
-        <v>28176.02474835219</v>
+        <v>28276.4185113709</v>
       </c>
       <c r="E21">
-        <v>-2307.135</v>
+        <v>-1991.799999999999</v>
       </c>
       <c r="F21">
-        <v>5991.365</v>
+        <v>6306.700000000001</v>
       </c>
       <c r="G21">
         <v>3302.3</v>
@@ -3015,28 +3015,28 @@
         <v>3659.1</v>
       </c>
       <c r="M21">
-        <v>336.9340967903235</v>
+        <v>354.6674703056038</v>
       </c>
       <c r="N21">
-        <v>3322.165903209676</v>
+        <v>3304.432529694396</v>
       </c>
       <c r="O21">
-        <v>830.5414758024191</v>
+        <v>826.108132423599</v>
       </c>
       <c r="P21">
-        <v>2491.624427407257</v>
+        <v>2478.324397270797</v>
       </c>
       <c r="Q21">
-        <v>4415.924427407257</v>
+        <v>4402.624397270796</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09736749412013102</v>
+        <v>0.09787504819611656</v>
       </c>
       <c r="T21">
-        <v>1.005146442927685</v>
+        <v>1.015039616578548</v>
       </c>
       <c r="U21">
         <v>0.05623661666253409</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.85998726414764</v>
+        <v>10.31698790094025</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08673553105627337</v>
+        <v>0.08658967400082948</v>
       </c>
       <c r="C22">
-        <v>25272.01851137089</v>
+        <v>25057.7952570172</v>
       </c>
       <c r="D22">
-        <v>28276.4185113709</v>
+        <v>28377.5302570172</v>
       </c>
       <c r="E22">
-        <v>-1991.799999999999</v>
+        <v>-1676.464999999999</v>
       </c>
       <c r="F22">
-        <v>6306.700000000001</v>
+        <v>6622.035000000001</v>
       </c>
       <c r="G22">
         <v>3302.3</v>
@@ -3097,28 +3097,28 @@
         <v>3659.1</v>
       </c>
       <c r="M22">
-        <v>354.6674703056038</v>
+        <v>372.4008438208839</v>
       </c>
       <c r="N22">
-        <v>3304.432529694396</v>
+        <v>3286.699156179116</v>
       </c>
       <c r="O22">
-        <v>826.108132423599</v>
+        <v>821.674789044779</v>
       </c>
       <c r="P22">
-        <v>2478.324397270797</v>
+        <v>2465.024367134337</v>
       </c>
       <c r="Q22">
-        <v>4402.624397270796</v>
+        <v>4389.324367134337</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09787504819611656</v>
+        <v>0.09839545174238021</v>
       </c>
       <c r="T22">
-        <v>1.015039616578548</v>
+        <v>1.025183250321838</v>
       </c>
       <c r="U22">
         <v>0.05623661666253409</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.31698790094025</v>
+        <v>9.82570276280024</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08658967400082948</v>
+        <v>0.08644381694538561</v>
       </c>
       <c r="C23">
-        <v>25057.7952570172</v>
+        <v>24844.29771508911</v>
       </c>
       <c r="D23">
-        <v>28377.5302570172</v>
+        <v>28479.36771508911</v>
       </c>
       <c r="E23">
-        <v>-1676.465</v>
+        <v>-1361.13</v>
       </c>
       <c r="F23">
-        <v>6622.035</v>
+        <v>6937.37</v>
       </c>
       <c r="G23">
         <v>3302.3</v>
@@ -3179,28 +3179,28 @@
         <v>3659.1</v>
       </c>
       <c r="M23">
-        <v>372.4008438208839</v>
+        <v>390.1342173361641</v>
       </c>
       <c r="N23">
-        <v>3286.699156179116</v>
+        <v>3268.965782663836</v>
       </c>
       <c r="O23">
-        <v>821.674789044779</v>
+        <v>817.241445665959</v>
       </c>
       <c r="P23">
-        <v>2465.024367134337</v>
+        <v>2451.724336997877</v>
       </c>
       <c r="Q23">
-        <v>4389.324367134337</v>
+        <v>4376.024336997876</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09839545174238021</v>
+        <v>0.09892919896931729</v>
       </c>
       <c r="T23">
-        <v>1.025183250321838</v>
+        <v>1.035586977238032</v>
       </c>
       <c r="U23">
         <v>0.05623661666253409</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.82570276280024</v>
+        <v>9.379079909945684</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08644381694538561</v>
+        <v>0.08629795988994175</v>
       </c>
       <c r="C24">
-        <v>24844.29771508911</v>
+        <v>24631.53372674289</v>
       </c>
       <c r="D24">
-        <v>28479.36771508911</v>
+        <v>28581.93872674289</v>
       </c>
       <c r="E24">
-        <v>-1361.13</v>
+        <v>-1045.795</v>
       </c>
       <c r="F24">
-        <v>6937.37</v>
+        <v>7252.705</v>
       </c>
       <c r="G24">
         <v>3302.3</v>
@@ -3261,28 +3261,28 @@
         <v>3659.1</v>
       </c>
       <c r="M24">
-        <v>390.1342173361641</v>
+        <v>407.8675908514443</v>
       </c>
       <c r="N24">
-        <v>3268.965782663836</v>
+        <v>3251.232409148556</v>
       </c>
       <c r="O24">
-        <v>817.241445665959</v>
+        <v>812.8081022871389</v>
       </c>
       <c r="P24">
-        <v>2451.724336997877</v>
+        <v>2438.424306861417</v>
       </c>
       <c r="Q24">
-        <v>4376.024336997876</v>
+        <v>4362.724306861417</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09892919896931729</v>
+        <v>0.09947680976059041</v>
       </c>
       <c r="T24">
-        <v>1.035586977238032</v>
+        <v>1.046260930827375</v>
       </c>
       <c r="U24">
         <v>0.05623661666253409</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.379079909945684</v>
+        <v>8.971293826904567</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08629795988994175</v>
+        <v>0.08642210283449789</v>
       </c>
       <c r="C25">
-        <v>24631.53372674289</v>
+        <v>24228.85105670431</v>
       </c>
       <c r="D25">
-        <v>28581.93872674289</v>
+        <v>28494.59105670431</v>
       </c>
       <c r="E25">
-        <v>-1045.795</v>
+        <v>-730.4599999999991</v>
       </c>
       <c r="F25">
-        <v>7252.705</v>
+        <v>7568.040000000001</v>
       </c>
       <c r="G25">
         <v>3302.3</v>
@@ -3343,45 +3343,45 @@
         <v>3659.1</v>
       </c>
       <c r="M25">
-        <v>407.8675908514443</v>
+        <v>436.9530243667245</v>
       </c>
       <c r="N25">
-        <v>3251.232409148556</v>
+        <v>3222.146975633275</v>
       </c>
       <c r="O25">
-        <v>812.8081022871389</v>
+        <v>805.5367439083188</v>
       </c>
       <c r="P25">
-        <v>2438.424306861417</v>
+        <v>2416.610231724957</v>
       </c>
       <c r="Q25">
-        <v>4362.724306861417</v>
+        <v>4340.910231724956</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09947680976059041</v>
+        <v>0.1000388313621602</v>
       </c>
       <c r="T25">
-        <v>1.046260930827375</v>
+        <v>1.057215777932227</v>
       </c>
       <c r="U25">
-        <v>0.05623661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04217746249690056</v>
+        <v>0.04330246249690056</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>8.971293826904567</v>
+        <v>8.374126727474032</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08642210283449787</v>
+        <v>0.08628749577905399</v>
       </c>
       <c r="C26">
-        <v>24228.85105670432</v>
+        <v>24008.25081182852</v>
       </c>
       <c r="D26">
-        <v>28494.59105670432</v>
+        <v>28589.32581182852</v>
       </c>
       <c r="E26">
-        <v>-730.46</v>
+        <v>-415.125</v>
       </c>
       <c r="F26">
-        <v>7568.04</v>
+        <v>7883.375</v>
       </c>
       <c r="G26">
         <v>3302.3</v>
@@ -3425,28 +3425,28 @@
         <v>3659.1</v>
       </c>
       <c r="M26">
-        <v>436.9530243667245</v>
+        <v>455.1594003820047</v>
       </c>
       <c r="N26">
-        <v>3222.146975633275</v>
+        <v>3203.940599617995</v>
       </c>
       <c r="O26">
-        <v>805.5367439083188</v>
+        <v>800.9851499044988</v>
       </c>
       <c r="P26">
-        <v>2416.610231724957</v>
+        <v>2402.955449713496</v>
       </c>
       <c r="Q26">
-        <v>4340.910231724956</v>
+        <v>4327.255449713496</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1000388313621602</v>
+        <v>0.1006158402064385</v>
       </c>
       <c r="T26">
-        <v>1.057215777932227</v>
+        <v>1.068462754293208</v>
       </c>
       <c r="U26">
         <v>0.05773661666253409</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.374126727474032</v>
+        <v>8.039161658375072</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08628749577905399</v>
+        <v>0.08615288872361014</v>
       </c>
       <c r="C27">
-        <v>24008.25081182852</v>
+        <v>23788.28258943429</v>
       </c>
       <c r="D27">
-        <v>28589.32581182852</v>
+        <v>28684.69258943429</v>
       </c>
       <c r="E27">
-        <v>-415.125</v>
+        <v>-99.78999999999905</v>
       </c>
       <c r="F27">
-        <v>7883.375</v>
+        <v>8198.710000000001</v>
       </c>
       <c r="G27">
         <v>3302.3</v>
@@ -3507,28 +3507,28 @@
         <v>3659.1</v>
       </c>
       <c r="M27">
-        <v>455.1594003820047</v>
+        <v>473.3657763972849</v>
       </c>
       <c r="N27">
-        <v>3203.940599617995</v>
+        <v>3185.734223602715</v>
       </c>
       <c r="O27">
-        <v>800.9851499044988</v>
+        <v>796.4335559006788</v>
       </c>
       <c r="P27">
-        <v>2402.955449713496</v>
+        <v>2389.300667702037</v>
       </c>
       <c r="Q27">
-        <v>4327.255449713496</v>
+        <v>4313.600667702036</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1006158402064385</v>
+        <v>0.1012084438843459</v>
       </c>
       <c r="T27">
-        <v>1.068462754293208</v>
+        <v>1.08001370298827</v>
       </c>
       <c r="U27">
         <v>0.05773661666253409</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.039161658375072</v>
+        <v>7.729963133052953</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08615288872361014</v>
+        <v>0.08601828166816626</v>
       </c>
       <c r="C28">
-        <v>23788.28258943429</v>
+        <v>23568.95273549285</v>
       </c>
       <c r="D28">
-        <v>28684.69258943429</v>
+        <v>28780.69773549285</v>
       </c>
       <c r="E28">
-        <v>-99.78999999999905</v>
+        <v>215.5450000000001</v>
       </c>
       <c r="F28">
-        <v>8198.710000000001</v>
+        <v>8514.045</v>
       </c>
       <c r="G28">
         <v>3302.3</v>
@@ -3589,28 +3589,28 @@
         <v>3659.1</v>
       </c>
       <c r="M28">
-        <v>473.3657763972849</v>
+        <v>491.5721524125651</v>
       </c>
       <c r="N28">
-        <v>3185.734223602715</v>
+        <v>3167.527847587435</v>
       </c>
       <c r="O28">
-        <v>796.4335559006788</v>
+        <v>791.8819618968587</v>
       </c>
       <c r="P28">
-        <v>2389.300667702037</v>
+        <v>2375.645885690576</v>
       </c>
       <c r="Q28">
-        <v>4313.600667702036</v>
+        <v>4299.945885690576</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1012084438843459</v>
+        <v>0.1018172832794563</v>
       </c>
       <c r="T28">
-        <v>1.08001370298827</v>
+        <v>1.091881116031142</v>
       </c>
       <c r="U28">
         <v>0.05773661666253409</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.729963133052953</v>
+        <v>7.44366820219914</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08601828166816626</v>
+        <v>0.08588367461272239</v>
       </c>
       <c r="C29">
-        <v>23568.95273549285</v>
+        <v>23350.26768121826</v>
       </c>
       <c r="D29">
-        <v>28780.69773549285</v>
+        <v>28877.34768121826</v>
       </c>
       <c r="E29">
-        <v>215.5450000000001</v>
+        <v>530.880000000001</v>
       </c>
       <c r="F29">
-        <v>8514.045</v>
+        <v>8829.380000000001</v>
       </c>
       <c r="G29">
         <v>3302.3</v>
@@ -3671,28 +3671,28 @@
         <v>3659.1</v>
       </c>
       <c r="M29">
-        <v>491.5721524125651</v>
+        <v>509.7785284278453</v>
       </c>
       <c r="N29">
-        <v>3167.527847587435</v>
+        <v>3149.321471572155</v>
       </c>
       <c r="O29">
-        <v>791.8819618968587</v>
+        <v>787.3303678930387</v>
       </c>
       <c r="P29">
-        <v>2375.645885690576</v>
+        <v>2361.991103679116</v>
       </c>
       <c r="Q29">
-        <v>4299.945885690576</v>
+        <v>4286.291103679116</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1018172832794563</v>
+        <v>0.1024430348799864</v>
       </c>
       <c r="T29">
-        <v>1.091881116031142</v>
+        <v>1.104078179436315</v>
       </c>
       <c r="U29">
         <v>0.05773661666253409</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.44366820219914</v>
+        <v>7.177822909263456</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08588367461272239</v>
+        <v>0.08574906755727851</v>
       </c>
       <c r="C30">
-        <v>23350.26768121826</v>
+        <v>23132.23394450369</v>
       </c>
       <c r="D30">
-        <v>28877.34768121826</v>
+        <v>28974.64894450369</v>
       </c>
       <c r="E30">
-        <v>530.880000000001</v>
+        <v>846.215000000002</v>
       </c>
       <c r="F30">
-        <v>8829.380000000001</v>
+        <v>9144.715000000002</v>
       </c>
       <c r="G30">
         <v>3302.3</v>
@@ -3753,28 +3753,28 @@
         <v>3659.1</v>
       </c>
       <c r="M30">
-        <v>509.7785284278453</v>
+        <v>527.9849044431255</v>
       </c>
       <c r="N30">
-        <v>3149.321471572155</v>
+        <v>3131.115095556875</v>
       </c>
       <c r="O30">
-        <v>787.3303678930387</v>
+        <v>782.7787738892187</v>
       </c>
       <c r="P30">
-        <v>2361.991103679116</v>
+        <v>2348.336321667656</v>
       </c>
       <c r="Q30">
-        <v>4286.291103679116</v>
+        <v>4272.636321667656</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1024430348799864</v>
+        <v>0.1030864132861653</v>
       </c>
       <c r="T30">
-        <v>1.104078179436315</v>
+        <v>1.116618822092339</v>
       </c>
       <c r="U30">
         <v>0.05773661666253409</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.177822909263456</v>
+        <v>6.930311774461268</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0857490675572785</v>
+        <v>0.08561446050183463</v>
       </c>
       <c r="C31">
-        <v>23132.2339445037</v>
+        <v>22914.85813138656</v>
       </c>
       <c r="D31">
-        <v>28974.6489445037</v>
+        <v>29072.60813138656</v>
       </c>
       <c r="E31">
-        <v>846.2150000000001</v>
+        <v>1161.549999999999</v>
       </c>
       <c r="F31">
-        <v>9144.715</v>
+        <v>9460.049999999999</v>
       </c>
       <c r="G31">
         <v>3302.3</v>
@@ -3835,28 +3835,28 @@
         <v>3659.1</v>
       </c>
       <c r="M31">
-        <v>527.9849044431254</v>
+        <v>546.1912804584056</v>
       </c>
       <c r="N31">
-        <v>3131.115095556875</v>
+        <v>3112.908719541594</v>
       </c>
       <c r="O31">
-        <v>782.7787738892187</v>
+        <v>778.2271798853985</v>
       </c>
       <c r="P31">
-        <v>2348.336321667656</v>
+        <v>2334.681539656196</v>
       </c>
       <c r="Q31">
-        <v>4272.636321667656</v>
+        <v>4258.981539656195</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1030864132861653</v>
+        <v>0.1037481739325207</v>
       </c>
       <c r="T31">
-        <v>1.116618822092339</v>
+        <v>1.129517768824249</v>
       </c>
       <c r="U31">
         <v>0.05773661666253409</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.930311774461269</v>
+        <v>6.699301381979226</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08561446050183463</v>
+        <v>0.08587510344639077</v>
       </c>
       <c r="C32">
-        <v>22914.85813138656</v>
+        <v>22410.4388985928</v>
       </c>
       <c r="D32">
-        <v>29072.60813138656</v>
+        <v>28883.5238985928</v>
       </c>
       <c r="E32">
-        <v>1161.549999999999</v>
+        <v>1476.885</v>
       </c>
       <c r="F32">
-        <v>9460.049999999999</v>
+        <v>9775.385</v>
       </c>
       <c r="G32">
         <v>3302.3</v>
@@ -3917,45 +3917,45 @@
         <v>3659.1</v>
       </c>
       <c r="M32">
-        <v>546.1912804584056</v>
+        <v>581.0158109736858</v>
       </c>
       <c r="N32">
-        <v>3112.908719541594</v>
+        <v>3078.084189026314</v>
       </c>
       <c r="O32">
-        <v>778.2271798853985</v>
+        <v>769.5210472565785</v>
       </c>
       <c r="P32">
-        <v>2334.681539656196</v>
+        <v>2308.563141769735</v>
       </c>
       <c r="Q32">
-        <v>4258.981539656195</v>
+        <v>4232.863141769735</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1037481739325207</v>
+        <v>0.1044291160468864</v>
       </c>
       <c r="T32">
-        <v>1.129517768824249</v>
+        <v>1.142790598070127</v>
       </c>
       <c r="U32">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04330246249690056</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.699301381979226</v>
+        <v>6.297763212102537</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08587510344639077</v>
+        <v>0.08575324639094689</v>
       </c>
       <c r="C33">
-        <v>22410.4388985928</v>
+        <v>22183.19839631359</v>
       </c>
       <c r="D33">
-        <v>28883.5238985928</v>
+        <v>28971.61839631359</v>
       </c>
       <c r="E33">
-        <v>1476.885</v>
+        <v>1792.219999999999</v>
       </c>
       <c r="F33">
-        <v>9775.385</v>
+        <v>10090.72</v>
       </c>
       <c r="G33">
         <v>3302.3</v>
@@ -3999,28 +3999,28 @@
         <v>3659.1</v>
       </c>
       <c r="M33">
-        <v>581.0158109736858</v>
+        <v>599.7582564889659</v>
       </c>
       <c r="N33">
-        <v>3078.084189026314</v>
+        <v>3059.341743511034</v>
       </c>
       <c r="O33">
-        <v>769.5210472565785</v>
+        <v>764.8354358777585</v>
       </c>
       <c r="P33">
-        <v>2308.563141769735</v>
+        <v>2294.506307633275</v>
       </c>
       <c r="Q33">
-        <v>4232.863141769735</v>
+        <v>4218.806307633275</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1044291160468864</v>
+        <v>0.1051300858704981</v>
       </c>
       <c r="T33">
-        <v>1.142790598070127</v>
+        <v>1.156453804646767</v>
       </c>
       <c r="U33">
         <v>0.05943661666253409</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.297763212102537</v>
+        <v>6.100958111724333</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08575324639094689</v>
+        <v>0.08563138933550303</v>
       </c>
       <c r="C34">
-        <v>22183.19839631359</v>
+        <v>21956.49691294745</v>
       </c>
       <c r="D34">
-        <v>28971.61839631359</v>
+        <v>29060.25191294745</v>
       </c>
       <c r="E34">
-        <v>1792.219999999999</v>
+        <v>2107.555</v>
       </c>
       <c r="F34">
-        <v>10090.72</v>
+        <v>10406.055</v>
       </c>
       <c r="G34">
         <v>3302.3</v>
@@ -4081,28 +4081,28 @@
         <v>3659.1</v>
       </c>
       <c r="M34">
-        <v>599.7582564889659</v>
+        <v>618.5007020042461</v>
       </c>
       <c r="N34">
-        <v>3059.341743511034</v>
+        <v>3040.599297995754</v>
       </c>
       <c r="O34">
-        <v>764.8354358777585</v>
+        <v>760.1498244989384</v>
       </c>
       <c r="P34">
-        <v>2294.506307633275</v>
+        <v>2280.449473496815</v>
       </c>
       <c r="Q34">
-        <v>4218.806307633275</v>
+        <v>4204.749473496815</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1051300858704981</v>
+        <v>0.1058519801664565</v>
       </c>
       <c r="T34">
-        <v>1.156453804646767</v>
+        <v>1.170524868136142</v>
       </c>
       <c r="U34">
         <v>0.05943661666253409</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.100958111724333</v>
+        <v>5.916080593187232</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08563138933550303</v>
+        <v>0.08550953228005916</v>
       </c>
       <c r="C35">
-        <v>21956.49691294745</v>
+        <v>21730.33941077325</v>
       </c>
       <c r="D35">
-        <v>29060.25191294745</v>
+        <v>29149.42941077326</v>
       </c>
       <c r="E35">
-        <v>2107.555</v>
+        <v>2422.890000000001</v>
       </c>
       <c r="F35">
-        <v>10406.055</v>
+        <v>10721.39</v>
       </c>
       <c r="G35">
         <v>3302.3</v>
@@ -4163,28 +4163,28 @@
         <v>3659.1</v>
       </c>
       <c r="M35">
-        <v>618.5007020042461</v>
+        <v>637.2431475195264</v>
       </c>
       <c r="N35">
-        <v>3040.599297995754</v>
+        <v>3021.856852480474</v>
       </c>
       <c r="O35">
-        <v>760.1498244989384</v>
+        <v>755.4642131201184</v>
       </c>
       <c r="P35">
-        <v>2280.449473496815</v>
+        <v>2266.392639360355</v>
       </c>
       <c r="Q35">
-        <v>4204.749473496815</v>
+        <v>4190.692639360355</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1058519801664565</v>
+        <v>0.1065957500471409</v>
       </c>
       <c r="T35">
-        <v>1.170524868136142</v>
+        <v>1.185022327488831</v>
       </c>
       <c r="U35">
         <v>0.05943661666253409</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.916080593187232</v>
+        <v>5.742078222799372</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08550953228005916</v>
+        <v>0.08538767522461529</v>
       </c>
       <c r="C36">
-        <v>21730.33941077325</v>
+        <v>21504.73091316855</v>
       </c>
       <c r="D36">
-        <v>29149.42941077326</v>
+        <v>29239.15591316855</v>
       </c>
       <c r="E36">
-        <v>2422.890000000001</v>
+        <v>2738.225</v>
       </c>
       <c r="F36">
-        <v>10721.39</v>
+        <v>11036.725</v>
       </c>
       <c r="G36">
         <v>3302.3</v>
@@ -4245,28 +4245,28 @@
         <v>3659.1</v>
       </c>
       <c r="M36">
-        <v>637.2431475195264</v>
+        <v>655.9855930348066</v>
       </c>
       <c r="N36">
-        <v>3021.856852480474</v>
+        <v>3003.114406965193</v>
       </c>
       <c r="O36">
-        <v>755.4642131201184</v>
+        <v>750.7786017412983</v>
       </c>
       <c r="P36">
-        <v>2266.392639360355</v>
+        <v>2252.335805223895</v>
       </c>
       <c r="Q36">
-        <v>4190.692639360355</v>
+        <v>4176.635805223895</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1065957500471409</v>
+        <v>0.1073624051549232</v>
       </c>
       <c r="T36">
-        <v>1.185022327488831</v>
+        <v>1.199965862513911</v>
       </c>
       <c r="U36">
         <v>0.05943661666253409</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.742078222799372</v>
+        <v>5.578018845005103</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08538767522461529</v>
+        <v>0.0854818181691714</v>
       </c>
       <c r="C37">
-        <v>21504.73091316855</v>
+        <v>21120.02761400782</v>
       </c>
       <c r="D37">
-        <v>29239.15591316855</v>
+        <v>29169.78761400782</v>
       </c>
       <c r="E37">
-        <v>2738.225</v>
+        <v>3053.560000000001</v>
       </c>
       <c r="F37">
-        <v>11036.725</v>
+        <v>11352.06</v>
       </c>
       <c r="G37">
         <v>3302.3</v>
@@ -4327,45 +4327,45 @@
         <v>3659.1</v>
       </c>
       <c r="M37">
-        <v>655.9855930348066</v>
+        <v>683.8096865500868</v>
       </c>
       <c r="N37">
-        <v>3003.114406965193</v>
+        <v>2975.290313449913</v>
       </c>
       <c r="O37">
-        <v>750.7786017412983</v>
+        <v>743.8225783624782</v>
       </c>
       <c r="P37">
-        <v>2252.335805223895</v>
+        <v>2231.467735087434</v>
       </c>
       <c r="Q37">
-        <v>4176.635805223895</v>
+        <v>4155.767735087435</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1073624051549232</v>
+        <v>0.1081530182348238</v>
       </c>
       <c r="T37">
-        <v>1.199965862513911</v>
+        <v>1.215376383008524</v>
       </c>
       <c r="U37">
-        <v>0.05943661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690056</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>5.578018845005103</v>
+        <v>5.351050258531227</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08548181816917141</v>
+        <v>0.08536596111372755</v>
       </c>
       <c r="C38">
-        <v>21120.02761400781</v>
+        <v>20890.10759207868</v>
       </c>
       <c r="D38">
-        <v>29169.78761400782</v>
+        <v>29255.20259207868</v>
       </c>
       <c r="E38">
-        <v>3053.559999999999</v>
+        <v>3368.895</v>
       </c>
       <c r="F38">
-        <v>11352.06</v>
+        <v>11667.395</v>
       </c>
       <c r="G38">
         <v>3302.3</v>
@@ -4409,28 +4409,28 @@
         <v>3659.1</v>
       </c>
       <c r="M38">
-        <v>683.8096865500867</v>
+        <v>702.804400065367</v>
       </c>
       <c r="N38">
-        <v>2975.290313449913</v>
+        <v>2956.295599934633</v>
       </c>
       <c r="O38">
-        <v>743.8225783624783</v>
+        <v>739.0738999836583</v>
       </c>
       <c r="P38">
-        <v>2231.467735087435</v>
+        <v>2217.221699950975</v>
       </c>
       <c r="Q38">
-        <v>4155.767735087435</v>
+        <v>4141.521699950974</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1081530182348238</v>
+        <v>0.1089687301426577</v>
       </c>
       <c r="T38">
-        <v>1.215376383008524</v>
+        <v>1.231276126375983</v>
       </c>
       <c r="U38">
         <v>0.06023661666253409</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.351050258531229</v>
+        <v>5.206427278570925</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08536596111372755</v>
+        <v>0.08525010405828368</v>
       </c>
       <c r="C39">
-        <v>20890.10759207868</v>
+        <v>20660.68926352078</v>
       </c>
       <c r="D39">
-        <v>29255.20259207868</v>
+        <v>29341.11926352078</v>
       </c>
       <c r="E39">
-        <v>3368.895</v>
+        <v>3684.23</v>
       </c>
       <c r="F39">
-        <v>11667.395</v>
+        <v>11982.73</v>
       </c>
       <c r="G39">
         <v>3302.3</v>
@@ -4491,28 +4491,28 @@
         <v>3659.1</v>
       </c>
       <c r="M39">
-        <v>702.804400065367</v>
+        <v>721.7991135806471</v>
       </c>
       <c r="N39">
-        <v>2956.295599934633</v>
+        <v>2937.300886419353</v>
       </c>
       <c r="O39">
-        <v>739.0738999836583</v>
+        <v>734.3252216048381</v>
       </c>
       <c r="P39">
-        <v>2217.221699950975</v>
+        <v>2202.975664814514</v>
       </c>
       <c r="Q39">
-        <v>4141.521699950974</v>
+        <v>4127.275664814514</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1089687301426577</v>
+        <v>0.1098107553378411</v>
       </c>
       <c r="T39">
-        <v>1.231276126375983</v>
+        <v>1.247688764690779</v>
       </c>
       <c r="U39">
         <v>0.06023661666253409</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.206427278570925</v>
+        <v>5.069416034398006</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08525010405828368</v>
+        <v>0.08513424700283979</v>
       </c>
       <c r="C40">
-        <v>20660.68926352078</v>
+        <v>20431.77706147224</v>
       </c>
       <c r="D40">
-        <v>29341.11926352078</v>
+        <v>29427.54206147224</v>
       </c>
       <c r="E40">
-        <v>3684.23</v>
+        <v>3999.565000000001</v>
       </c>
       <c r="F40">
-        <v>11982.73</v>
+        <v>12298.065</v>
       </c>
       <c r="G40">
         <v>3302.3</v>
@@ -4573,28 +4573,28 @@
         <v>3659.1</v>
       </c>
       <c r="M40">
-        <v>721.7991135806471</v>
+        <v>740.7938270959273</v>
       </c>
       <c r="N40">
-        <v>2937.300886419353</v>
+        <v>2918.306172904073</v>
       </c>
       <c r="O40">
-        <v>734.3252216048381</v>
+        <v>729.5765432260182</v>
       </c>
       <c r="P40">
-        <v>2202.975664814514</v>
+        <v>2188.729629678055</v>
       </c>
       <c r="Q40">
-        <v>4127.275664814514</v>
+        <v>4113.029629678054</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1098107553378411</v>
+        <v>0.1106803879164731</v>
       </c>
       <c r="T40">
-        <v>1.247688764690779</v>
+        <v>1.264639522294584</v>
       </c>
       <c r="U40">
         <v>0.06023661666253409</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.069416034398006</v>
+        <v>4.93943100787498</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08513424700283979</v>
+        <v>0.08501838994739593</v>
       </c>
       <c r="C41">
-        <v>20431.77706147224</v>
+        <v>20203.37547145582</v>
       </c>
       <c r="D41">
-        <v>29427.54206147224</v>
+        <v>29514.47547145582</v>
       </c>
       <c r="E41">
-        <v>3999.565000000001</v>
+        <v>4314.900000000001</v>
       </c>
       <c r="F41">
-        <v>12298.065</v>
+        <v>12613.4</v>
       </c>
       <c r="G41">
         <v>3302.3</v>
@@ -4655,28 +4655,28 @@
         <v>3659.1</v>
       </c>
       <c r="M41">
-        <v>740.7938270959273</v>
+        <v>759.7885406112076</v>
       </c>
       <c r="N41">
-        <v>2918.306172904073</v>
+        <v>2899.311459388792</v>
       </c>
       <c r="O41">
-        <v>729.5765432260182</v>
+        <v>724.827864847198</v>
       </c>
       <c r="P41">
-        <v>2188.729629678055</v>
+        <v>2174.483594541594</v>
       </c>
       <c r="Q41">
-        <v>4113.029629678054</v>
+        <v>4098.783594541594</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1106803879164731</v>
+        <v>0.1115790082477262</v>
       </c>
       <c r="T41">
-        <v>1.264639522294584</v>
+        <v>1.28215530515185</v>
       </c>
       <c r="U41">
         <v>0.06023661666253409</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.93943100787498</v>
+        <v>4.815945232678104</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08501838994739593</v>
+        <v>0.08490253289195207</v>
       </c>
       <c r="C42">
-        <v>20203.37547145582</v>
+        <v>19975.48903215498</v>
       </c>
       <c r="D42">
-        <v>29514.47547145582</v>
+        <v>29601.92403215498</v>
       </c>
       <c r="E42">
-        <v>4314.900000000001</v>
+        <v>4630.235000000001</v>
       </c>
       <c r="F42">
-        <v>12613.4</v>
+        <v>12928.735</v>
       </c>
       <c r="G42">
         <v>3302.3</v>
@@ -4737,28 +4737,28 @@
         <v>3659.1</v>
       </c>
       <c r="M42">
-        <v>759.7885406112076</v>
+        <v>778.7832541264877</v>
       </c>
       <c r="N42">
-        <v>2899.311459388792</v>
+        <v>2880.316745873512</v>
       </c>
       <c r="O42">
-        <v>724.827864847198</v>
+        <v>720.0791864683781</v>
       </c>
       <c r="P42">
-        <v>2174.483594541594</v>
+        <v>2160.237559405135</v>
       </c>
       <c r="Q42">
-        <v>4098.783594541594</v>
+        <v>4084.537559405134</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1115790082477262</v>
+        <v>0.1125080902851235</v>
       </c>
       <c r="T42">
-        <v>1.28215530515185</v>
+        <v>1.30026484336021</v>
       </c>
       <c r="U42">
         <v>0.06023661666253409</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.815945232678104</v>
+        <v>4.698483153832298</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08490253289195207</v>
+        <v>0.08478667583650819</v>
       </c>
       <c r="C43">
-        <v>19975.48903215498</v>
+        <v>19748.1223362038</v>
       </c>
       <c r="D43">
-        <v>29601.92403215498</v>
+        <v>29689.8923362038</v>
       </c>
       <c r="E43">
-        <v>4630.235000000001</v>
+        <v>4945.570000000002</v>
       </c>
       <c r="F43">
-        <v>12928.735</v>
+        <v>13244.07</v>
       </c>
       <c r="G43">
         <v>3302.3</v>
@@ -4819,28 +4819,28 @@
         <v>3659.1</v>
       </c>
       <c r="M43">
-        <v>778.7832541264877</v>
+        <v>797.777967641768</v>
       </c>
       <c r="N43">
-        <v>2880.316745873512</v>
+        <v>2861.322032358232</v>
       </c>
       <c r="O43">
-        <v>720.0791864683781</v>
+        <v>715.330508089558</v>
       </c>
       <c r="P43">
-        <v>2160.237559405135</v>
+        <v>2145.991524268674</v>
       </c>
       <c r="Q43">
-        <v>4084.537559405134</v>
+        <v>4070.291524268674</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1125080902851235</v>
+        <v>0.1134692096341551</v>
       </c>
       <c r="T43">
-        <v>1.30026484336021</v>
+        <v>1.31899884840334</v>
       </c>
       <c r="U43">
         <v>0.06023661666253409</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.698483153832298</v>
+        <v>4.586614507312481</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0847866758365082</v>
+        <v>0.08467081878106432</v>
       </c>
       <c r="C44">
-        <v>19748.12233620379</v>
+        <v>19521.28003099092</v>
       </c>
       <c r="D44">
-        <v>29689.89233620379</v>
+        <v>29778.38503099092</v>
       </c>
       <c r="E44">
-        <v>4945.57</v>
+        <v>5260.905000000001</v>
       </c>
       <c r="F44">
-        <v>13244.07</v>
+        <v>13559.405</v>
       </c>
       <c r="G44">
         <v>3302.3</v>
@@ -4901,28 +4901,28 @@
         <v>3659.1</v>
       </c>
       <c r="M44">
-        <v>797.7779676417679</v>
+        <v>816.7726811570481</v>
       </c>
       <c r="N44">
-        <v>2861.322032358232</v>
+        <v>2842.327318842952</v>
       </c>
       <c r="O44">
-        <v>715.330508089558</v>
+        <v>710.581829710738</v>
       </c>
       <c r="P44">
-        <v>2145.991524268674</v>
+        <v>2131.745489132214</v>
       </c>
       <c r="Q44">
-        <v>4070.291524268674</v>
+        <v>4056.045489132214</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1134692096341551</v>
+        <v>0.1144640524691177</v>
       </c>
       <c r="T44">
-        <v>1.31899884840334</v>
+        <v>1.338390186956755</v>
       </c>
       <c r="U44">
         <v>0.06023661666253409</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.586614507312481</v>
+        <v>4.479949053654051</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08467081878106432</v>
+        <v>0.08455496172562045</v>
       </c>
       <c r="C45">
-        <v>19521.28003099092</v>
+        <v>19294.96681947804</v>
       </c>
       <c r="D45">
-        <v>29778.38503099092</v>
+        <v>29867.40681947803</v>
       </c>
       <c r="E45">
-        <v>5260.905000000001</v>
+        <v>5576.24</v>
       </c>
       <c r="F45">
-        <v>13559.405</v>
+        <v>13874.74</v>
       </c>
       <c r="G45">
         <v>3302.3</v>
@@ -4983,28 +4983,28 @@
         <v>3659.1</v>
       </c>
       <c r="M45">
-        <v>816.7726811570481</v>
+        <v>835.7673946723282</v>
       </c>
       <c r="N45">
-        <v>2842.327318842952</v>
+        <v>2823.332605327671</v>
       </c>
       <c r="O45">
-        <v>710.581829710738</v>
+        <v>705.8331513319179</v>
       </c>
       <c r="P45">
-        <v>2131.745489132214</v>
+        <v>2117.499453995753</v>
       </c>
       <c r="Q45">
-        <v>4056.045489132214</v>
+        <v>4041.799453995753</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1144640524691177</v>
+        <v>0.1154944254053289</v>
       </c>
       <c r="T45">
-        <v>1.338390186956755</v>
+        <v>1.358474073315651</v>
       </c>
       <c r="U45">
         <v>0.06023661666253409</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.479949053654051</v>
+        <v>4.378132029707368</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08455496172562045</v>
+        <v>0.08443910467017658</v>
       </c>
       <c r="C46">
-        <v>19294.96681947804</v>
+        <v>19069.18746103305</v>
       </c>
       <c r="D46">
-        <v>29867.40681947803</v>
+        <v>29956.96246103304</v>
       </c>
       <c r="E46">
-        <v>5576.24</v>
+        <v>5891.575000000001</v>
       </c>
       <c r="F46">
-        <v>13874.74</v>
+        <v>14190.075</v>
       </c>
       <c r="G46">
         <v>3302.3</v>
@@ -5065,28 +5065,28 @@
         <v>3659.1</v>
       </c>
       <c r="M46">
-        <v>835.7673946723282</v>
+        <v>854.7621081876084</v>
       </c>
       <c r="N46">
-        <v>2823.332605327671</v>
+        <v>2804.337891812392</v>
       </c>
       <c r="O46">
-        <v>705.8331513319179</v>
+        <v>701.0844729530979</v>
       </c>
       <c r="P46">
-        <v>2117.499453995753</v>
+        <v>2103.253418859294</v>
       </c>
       <c r="Q46">
-        <v>4041.799453995753</v>
+        <v>4027.553418859293</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1154944254053289</v>
+        <v>0.1165622664483115</v>
       </c>
       <c r="T46">
-        <v>1.358474073315651</v>
+        <v>1.379288282814869</v>
       </c>
       <c r="U46">
         <v>0.06023661666253409</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.378132029707368</v>
+        <v>4.280840206824983</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08443910467017658</v>
+        <v>0.08466824761473271</v>
       </c>
       <c r="C47">
-        <v>19069.18746103305</v>
+        <v>18577.24489548701</v>
       </c>
       <c r="D47">
-        <v>29956.96246103304</v>
+        <v>29780.35489548701</v>
       </c>
       <c r="E47">
-        <v>5891.575000000001</v>
+        <v>6206.91</v>
       </c>
       <c r="F47">
-        <v>14190.075</v>
+        <v>14505.41</v>
       </c>
       <c r="G47">
         <v>3302.3</v>
@@ -5147,45 +5147,45 @@
         <v>3659.1</v>
       </c>
       <c r="M47">
-        <v>854.7621081876084</v>
+        <v>888.2622317028886</v>
       </c>
       <c r="N47">
-        <v>2804.337891812392</v>
+        <v>2770.837768297111</v>
       </c>
       <c r="O47">
-        <v>701.0844729530979</v>
+        <v>692.7094420742778</v>
       </c>
       <c r="P47">
-        <v>2103.253418859294</v>
+        <v>2078.128326222833</v>
       </c>
       <c r="Q47">
-        <v>4027.553418859293</v>
+        <v>4002.428326222833</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1165622664483115</v>
+        <v>0.1176696571595527</v>
       </c>
       <c r="T47">
-        <v>1.379288282814869</v>
+        <v>1.400873388962206</v>
       </c>
       <c r="U47">
-        <v>0.06023661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04517746249690056</v>
+        <v>0.04592746249690056</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.280840206824983</v>
+        <v>4.119391627160748</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08466824761473271</v>
+        <v>0.08455989055928884</v>
       </c>
       <c r="C48">
-        <v>18577.24489548701</v>
+        <v>18345.16378294607</v>
       </c>
       <c r="D48">
-        <v>29780.35489548701</v>
+        <v>29863.60878294607</v>
       </c>
       <c r="E48">
-        <v>6206.91</v>
+        <v>6522.245000000001</v>
       </c>
       <c r="F48">
-        <v>14505.41</v>
+        <v>14820.745</v>
       </c>
       <c r="G48">
         <v>3302.3</v>
@@ -5229,28 +5229,28 @@
         <v>3659.1</v>
       </c>
       <c r="M48">
-        <v>888.2622317028886</v>
+        <v>907.5722802181689</v>
       </c>
       <c r="N48">
-        <v>2770.837768297111</v>
+        <v>2751.527719781831</v>
       </c>
       <c r="O48">
-        <v>692.7094420742778</v>
+        <v>687.8819299454577</v>
       </c>
       <c r="P48">
-        <v>2078.128326222833</v>
+        <v>2063.645789836373</v>
       </c>
       <c r="Q48">
-        <v>4002.428326222833</v>
+        <v>3987.945789836373</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1176696571595527</v>
+        <v>0.1188188361995199</v>
       </c>
       <c r="T48">
-        <v>1.400873388962206</v>
+        <v>1.42327302741699</v>
       </c>
       <c r="U48">
         <v>0.06123661666253409</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.119391627160748</v>
+        <v>4.031744996795625</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08455989055928884</v>
+        <v>0.08445153350384496</v>
       </c>
       <c r="C49">
-        <v>18345.16378294607</v>
+        <v>18113.5494641016</v>
       </c>
       <c r="D49">
-        <v>29863.60878294607</v>
+        <v>29947.3294641016</v>
       </c>
       <c r="E49">
-        <v>6522.245000000001</v>
+        <v>6837.580000000002</v>
       </c>
       <c r="F49">
-        <v>14820.745</v>
+        <v>15136.08</v>
       </c>
       <c r="G49">
         <v>3302.3</v>
@@ -5311,28 +5311,28 @@
         <v>3659.1</v>
       </c>
       <c r="M49">
-        <v>907.5722802181689</v>
+        <v>926.8823287334491</v>
       </c>
       <c r="N49">
-        <v>2751.527719781831</v>
+        <v>2732.217671266551</v>
       </c>
       <c r="O49">
-        <v>687.8819299454577</v>
+        <v>683.0544178166377</v>
       </c>
       <c r="P49">
-        <v>2063.645789836373</v>
+        <v>2049.163253449913</v>
       </c>
       <c r="Q49">
-        <v>3987.945789836373</v>
+        <v>3973.463253449913</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1188188361995199</v>
+        <v>0.1200122144333321</v>
       </c>
       <c r="T49">
-        <v>1.42327302741699</v>
+        <v>1.446534190427728</v>
       </c>
       <c r="U49">
         <v>0.06123661666253409</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.031744996795625</v>
+        <v>3.947750309362383</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08445153350384496</v>
+        <v>0.08434317644840109</v>
       </c>
       <c r="C50">
-        <v>18113.5494641016</v>
+        <v>17882.40587586763</v>
       </c>
       <c r="D50">
-        <v>29947.3294641016</v>
+        <v>30031.52087586762</v>
       </c>
       <c r="E50">
-        <v>6837.58</v>
+        <v>7152.914999999999</v>
       </c>
       <c r="F50">
-        <v>15136.08</v>
+        <v>15451.415</v>
       </c>
       <c r="G50">
         <v>3302.3</v>
@@ -5393,28 +5393,28 @@
         <v>3659.1</v>
       </c>
       <c r="M50">
-        <v>926.882328733449</v>
+        <v>946.1923772487291</v>
       </c>
       <c r="N50">
-        <v>2732.217671266551</v>
+        <v>2712.907622751271</v>
       </c>
       <c r="O50">
-        <v>683.0544178166377</v>
+        <v>678.2269056878176</v>
       </c>
       <c r="P50">
-        <v>2049.163253449913</v>
+        <v>2034.680717063453</v>
       </c>
       <c r="Q50">
-        <v>3973.463253449913</v>
+        <v>3958.980717063453</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1200122144333321</v>
+        <v>0.1212523918135683</v>
       </c>
       <c r="T50">
-        <v>1.446534190427728</v>
+        <v>1.470707555909475</v>
       </c>
       <c r="U50">
         <v>0.06123661666253409</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.947750309362384</v>
+        <v>3.867183976518253</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08434317644840109</v>
+        <v>0.08423481939295721</v>
       </c>
       <c r="C51">
-        <v>17882.40587586763</v>
+        <v>17651.73699955458</v>
       </c>
       <c r="D51">
-        <v>30031.52087586762</v>
+        <v>30116.18699955458</v>
       </c>
       <c r="E51">
-        <v>7152.914999999999</v>
+        <v>7468.25</v>
       </c>
       <c r="F51">
-        <v>15451.415</v>
+        <v>15766.75</v>
       </c>
       <c r="G51">
         <v>3302.3</v>
@@ -5475,28 +5475,28 @@
         <v>3659.1</v>
       </c>
       <c r="M51">
-        <v>946.1923772487291</v>
+        <v>965.5024257640093</v>
       </c>
       <c r="N51">
-        <v>2712.907622751271</v>
+        <v>2693.597574235991</v>
       </c>
       <c r="O51">
-        <v>678.2269056878176</v>
+        <v>673.3993935589976</v>
       </c>
       <c r="P51">
-        <v>2034.680717063453</v>
+        <v>2020.198180676993</v>
       </c>
       <c r="Q51">
-        <v>3958.980717063453</v>
+        <v>3944.498180676993</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1212523918135683</v>
+        <v>0.1225421762890139</v>
       </c>
       <c r="T51">
-        <v>1.470707555909475</v>
+        <v>1.495847856010492</v>
       </c>
       <c r="U51">
         <v>0.06123661666253409</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.867183976518253</v>
+        <v>3.789840296987888</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08423481939295721</v>
+        <v>0.08412646233751335</v>
       </c>
       <c r="C52">
-        <v>17651.73699955458</v>
+        <v>17421.54686149699</v>
       </c>
       <c r="D52">
-        <v>30116.18699955458</v>
+        <v>30201.33186149699</v>
       </c>
       <c r="E52">
-        <v>7468.25</v>
+        <v>7783.585000000001</v>
       </c>
       <c r="F52">
-        <v>15766.75</v>
+        <v>16082.085</v>
       </c>
       <c r="G52">
         <v>3302.3</v>
@@ -5557,28 +5557,28 @@
         <v>3659.1</v>
       </c>
       <c r="M52">
-        <v>965.5024257640093</v>
+        <v>984.8124742792896</v>
       </c>
       <c r="N52">
-        <v>2693.597574235991</v>
+        <v>2674.28752572071</v>
       </c>
       <c r="O52">
-        <v>673.3993935589976</v>
+        <v>668.5718814301775</v>
       </c>
       <c r="P52">
-        <v>2020.198180676993</v>
+        <v>2005.715644290533</v>
       </c>
       <c r="Q52">
-        <v>3944.498180676993</v>
+        <v>3930.015644290532</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1225421762890139</v>
+        <v>0.1238846050287634</v>
       </c>
       <c r="T52">
-        <v>1.495847856010492</v>
+        <v>1.522014290809509</v>
       </c>
       <c r="U52">
         <v>0.06123661666253409</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.789840296987888</v>
+        <v>3.715529702929302</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08412646233751335</v>
+        <v>0.08401810528206947</v>
       </c>
       <c r="C53">
-        <v>17421.54686149699</v>
+        <v>17191.83953369168</v>
       </c>
       <c r="D53">
-        <v>30201.33186149699</v>
+        <v>30286.95953369168</v>
       </c>
       <c r="E53">
-        <v>7783.585000000001</v>
+        <v>8098.920000000002</v>
       </c>
       <c r="F53">
-        <v>16082.085</v>
+        <v>16397.42</v>
       </c>
       <c r="G53">
         <v>3302.3</v>
@@ -5639,28 +5639,28 @@
         <v>3659.1</v>
       </c>
       <c r="M53">
-        <v>984.8124742792896</v>
+        <v>1004.12252279457</v>
       </c>
       <c r="N53">
-        <v>2674.28752572071</v>
+        <v>2654.97747720543</v>
       </c>
       <c r="O53">
-        <v>668.5718814301775</v>
+        <v>663.7443693013576</v>
       </c>
       <c r="P53">
-        <v>2005.715644290533</v>
+        <v>1991.233107904073</v>
       </c>
       <c r="Q53">
-        <v>3930.015644290532</v>
+        <v>3915.533107904072</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1238846050287634</v>
+        <v>0.1252829682993358</v>
       </c>
       <c r="T53">
-        <v>1.522014290809509</v>
+        <v>1.549270993725152</v>
       </c>
       <c r="U53">
         <v>0.06123661666253409</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.715529702929302</v>
+        <v>3.6440772086422</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08401810528206947</v>
+        <v>0.08390974822662561</v>
       </c>
       <c r="C54">
-        <v>17191.83953369168</v>
+        <v>16962.61913444691</v>
       </c>
       <c r="D54">
-        <v>30286.95953369168</v>
+        <v>30373.07413444691</v>
       </c>
       <c r="E54">
-        <v>8098.920000000002</v>
+        <v>8414.255000000001</v>
       </c>
       <c r="F54">
-        <v>16397.42</v>
+        <v>16712.755</v>
       </c>
       <c r="G54">
         <v>3302.3</v>
@@ -5721,28 +5721,28 @@
         <v>3659.1</v>
       </c>
       <c r="M54">
-        <v>1004.12252279457</v>
+        <v>1023.43257130985</v>
       </c>
       <c r="N54">
-        <v>2654.97747720543</v>
+        <v>2635.66742869015</v>
       </c>
       <c r="O54">
-        <v>663.7443693013576</v>
+        <v>658.9168571725374</v>
       </c>
       <c r="P54">
-        <v>1991.233107904073</v>
+        <v>1976.750571517612</v>
       </c>
       <c r="Q54">
-        <v>3915.533107904072</v>
+        <v>3901.050571517612</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1252829682993358</v>
+        <v>0.1267408363899326</v>
       </c>
       <c r="T54">
-        <v>1.549270993725152</v>
+        <v>1.577687556339333</v>
       </c>
       <c r="U54">
         <v>0.06123661666253409</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.6440772086422</v>
+        <v>3.575321034894234</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08390974822662561</v>
+        <v>0.08380139117118174</v>
       </c>
       <c r="C55">
-        <v>16962.61913444691</v>
+        <v>16733.88982904272</v>
       </c>
       <c r="D55">
-        <v>30373.07413444691</v>
+        <v>30459.67982904272</v>
       </c>
       <c r="E55">
-        <v>8414.255000000001</v>
+        <v>8729.59</v>
       </c>
       <c r="F55">
-        <v>16712.755</v>
+        <v>17028.09</v>
       </c>
       <c r="G55">
         <v>3302.3</v>
@@ -5803,28 +5803,28 @@
         <v>3659.1</v>
       </c>
       <c r="M55">
-        <v>1023.43257130985</v>
+        <v>1042.74261982513</v>
       </c>
       <c r="N55">
-        <v>2635.66742869015</v>
+        <v>2616.35738017487</v>
       </c>
       <c r="O55">
-        <v>658.9168571725374</v>
+        <v>654.0893450437175</v>
       </c>
       <c r="P55">
-        <v>1976.750571517612</v>
+        <v>1962.268035131152</v>
       </c>
       <c r="Q55">
-        <v>3901.050571517612</v>
+        <v>3886.568035131152</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1267408363899326</v>
+        <v>0.1282620900496857</v>
       </c>
       <c r="T55">
-        <v>1.577687556339333</v>
+        <v>1.60733962167587</v>
       </c>
       <c r="U55">
         <v>0.06123661666253409</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.575321034894234</v>
+        <v>3.509111386099897</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08380139117118174</v>
+        <v>0.08369303411573786</v>
       </c>
       <c r="C56">
-        <v>16733.88982904272</v>
+        <v>16505.65583040242</v>
       </c>
       <c r="D56">
-        <v>30459.67982904272</v>
+        <v>30546.78083040243</v>
       </c>
       <c r="E56">
-        <v>8729.59</v>
+        <v>9044.925000000003</v>
       </c>
       <c r="F56">
-        <v>17028.09</v>
+        <v>17343.425</v>
       </c>
       <c r="G56">
         <v>3302.3</v>
@@ -5885,28 +5885,28 @@
         <v>3659.1</v>
       </c>
       <c r="M56">
-        <v>1042.74261982513</v>
+        <v>1062.05266834041</v>
       </c>
       <c r="N56">
-        <v>2616.35738017487</v>
+        <v>2597.047331659589</v>
       </c>
       <c r="O56">
-        <v>654.0893450437175</v>
+        <v>649.2618329148974</v>
       </c>
       <c r="P56">
-        <v>1962.268035131152</v>
+        <v>1947.785498744692</v>
       </c>
       <c r="Q56">
-        <v>3886.568035131152</v>
+        <v>3872.085498744692</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1282620900496857</v>
+        <v>0.1298509549832057</v>
       </c>
       <c r="T56">
-        <v>1.60733962167587</v>
+        <v>1.63830955658292</v>
       </c>
       <c r="U56">
         <v>0.06123661666253409</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.509111386099897</v>
+        <v>3.44530936089808</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08369303411573786</v>
+        <v>0.08358467706029399</v>
       </c>
       <c r="C57">
-        <v>16505.65583040242</v>
+        <v>16277.92139977583</v>
       </c>
       <c r="D57">
-        <v>30546.78083040243</v>
+        <v>30634.38139977583</v>
       </c>
       <c r="E57">
-        <v>9044.925000000003</v>
+        <v>9360.260000000002</v>
       </c>
       <c r="F57">
-        <v>17343.425</v>
+        <v>17658.76</v>
       </c>
       <c r="G57">
         <v>3302.3</v>
@@ -5967,28 +5967,28 @@
         <v>3659.1</v>
       </c>
       <c r="M57">
-        <v>1062.05266834041</v>
+        <v>1081.362716855691</v>
       </c>
       <c r="N57">
-        <v>2597.047331659589</v>
+        <v>2577.737283144309</v>
       </c>
       <c r="O57">
-        <v>649.2618329148974</v>
+        <v>644.4343207860773</v>
       </c>
       <c r="P57">
-        <v>1947.785498744692</v>
+        <v>1933.302962358232</v>
       </c>
       <c r="Q57">
-        <v>3872.085498744692</v>
+        <v>3857.602962358232</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1298509549832057</v>
+        <v>0.1315120410500674</v>
       </c>
       <c r="T57">
-        <v>1.63830955658292</v>
+        <v>1.670687215803926</v>
       </c>
       <c r="U57">
         <v>0.06123661666253409</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.44530936089808</v>
+        <v>3.383785979453471</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08358467706029399</v>
+        <v>0.08347632000485011</v>
       </c>
       <c r="C58">
-        <v>16277.92139977583</v>
+        <v>16050.69084743412</v>
       </c>
       <c r="D58">
-        <v>30634.38139977583</v>
+        <v>30722.48584743412</v>
       </c>
       <c r="E58">
-        <v>9360.260000000002</v>
+        <v>9675.595000000001</v>
       </c>
       <c r="F58">
-        <v>17658.76</v>
+        <v>17974.095</v>
       </c>
       <c r="G58">
         <v>3302.3</v>
@@ -6049,28 +6049,28 @@
         <v>3659.1</v>
       </c>
       <c r="M58">
-        <v>1081.362716855691</v>
+        <v>1100.672765370971</v>
       </c>
       <c r="N58">
-        <v>2577.737283144309</v>
+        <v>2558.427234629029</v>
       </c>
       <c r="O58">
-        <v>644.4343207860773</v>
+        <v>639.6068086572573</v>
       </c>
       <c r="P58">
-        <v>1933.302962358232</v>
+        <v>1918.820425971772</v>
       </c>
       <c r="Q58">
-        <v>3857.602962358232</v>
+        <v>3843.120425971772</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1315120410500674</v>
+        <v>0.1332503869339925</v>
       </c>
       <c r="T58">
-        <v>1.670687215803926</v>
+        <v>1.704570812663118</v>
       </c>
       <c r="U58">
         <v>0.06123661666253409</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.383785979453471</v>
+        <v>3.32442131314727</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08347632000485011</v>
+        <v>0.08336796294940624</v>
       </c>
       <c r="C59">
-        <v>16050.69084743412</v>
+        <v>15823.96853337685</v>
       </c>
       <c r="D59">
-        <v>30722.48584743412</v>
+        <v>30811.09853337685</v>
       </c>
       <c r="E59">
-        <v>9675.595000000001</v>
+        <v>9990.930000000004</v>
       </c>
       <c r="F59">
-        <v>17974.095</v>
+        <v>18289.43</v>
       </c>
       <c r="G59">
         <v>3302.3</v>
@@ -6131,28 +6131,28 @@
         <v>3659.1</v>
       </c>
       <c r="M59">
-        <v>1100.672765370971</v>
+        <v>1119.982813886251</v>
       </c>
       <c r="N59">
-        <v>2558.427234629029</v>
+        <v>2539.117186113749</v>
       </c>
       <c r="O59">
-        <v>639.6068086572573</v>
+        <v>634.7792965284373</v>
       </c>
       <c r="P59">
-        <v>1918.820425971772</v>
+        <v>1904.337889585312</v>
       </c>
       <c r="Q59">
-        <v>3843.120425971772</v>
+        <v>3828.637889585311</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1332503869339925</v>
+        <v>0.1350715111933427</v>
       </c>
       <c r="T59">
-        <v>1.704570812663118</v>
+        <v>1.740067914134654</v>
       </c>
       <c r="U59">
         <v>0.06123661666253409</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.32442131314727</v>
+        <v>3.267103704299903</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08336796294940624</v>
+        <v>0.08325960589396238</v>
       </c>
       <c r="C60">
-        <v>15823.96853337685</v>
+        <v>15597.75886805117</v>
       </c>
       <c r="D60">
-        <v>30811.09853337685</v>
+        <v>30900.22386805117</v>
       </c>
       <c r="E60">
-        <v>9990.93</v>
+        <v>10306.265</v>
       </c>
       <c r="F60">
-        <v>18289.43</v>
+        <v>18604.765</v>
       </c>
       <c r="G60">
         <v>3302.3</v>
@@ -6213,28 +6213,28 @@
         <v>3659.1</v>
       </c>
       <c r="M60">
-        <v>1119.982813886251</v>
+        <v>1139.292862401531</v>
       </c>
       <c r="N60">
-        <v>2539.117186113749</v>
+        <v>2519.807137598469</v>
       </c>
       <c r="O60">
-        <v>634.7792965284373</v>
+        <v>629.9517843996173</v>
       </c>
       <c r="P60">
-        <v>1904.337889585312</v>
+        <v>1889.855353198852</v>
       </c>
       <c r="Q60">
-        <v>3828.637889585311</v>
+        <v>3814.155353198852</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1350715111933427</v>
+        <v>0.1369814707824172</v>
       </c>
       <c r="T60">
-        <v>1.740067914134653</v>
+        <v>1.777296581531629</v>
       </c>
       <c r="U60">
         <v>0.06123661666253409</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.267103704299904</v>
+        <v>3.211729065243973</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08325960589396238</v>
+        <v>0.08315124883851852</v>
       </c>
       <c r="C61">
-        <v>15597.75886805117</v>
+        <v>15372.06631308357</v>
       </c>
       <c r="D61">
-        <v>30900.22386805117</v>
+        <v>30989.86631308356</v>
       </c>
       <c r="E61">
-        <v>10306.265</v>
+        <v>10621.6</v>
       </c>
       <c r="F61">
-        <v>18604.765</v>
+        <v>18920.1</v>
       </c>
       <c r="G61">
         <v>3302.3</v>
@@ -6295,28 +6295,28 @@
         <v>3659.1</v>
       </c>
       <c r="M61">
-        <v>1139.292862401531</v>
+        <v>1158.602910916811</v>
       </c>
       <c r="N61">
-        <v>2519.807137598469</v>
+        <v>2500.497089083189</v>
       </c>
       <c r="O61">
-        <v>629.9517843996173</v>
+        <v>625.1242722707972</v>
       </c>
       <c r="P61">
-        <v>1889.855353198852</v>
+        <v>1875.372816812392</v>
       </c>
       <c r="Q61">
-        <v>3814.155353198852</v>
+        <v>3799.672816812391</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1369814707824172</v>
+        <v>0.1389869283509454</v>
       </c>
       <c r="T61">
-        <v>1.777296581531629</v>
+        <v>1.816386682298454</v>
       </c>
       <c r="U61">
         <v>0.06123661666253409</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.211729065243973</v>
+        <v>3.158200247489907</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08315124883851852</v>
+        <v>0.08304289178307464</v>
       </c>
       <c r="C62">
-        <v>15372.06631308357</v>
+        <v>15146.8953820244</v>
       </c>
       <c r="D62">
-        <v>30989.86631308356</v>
+        <v>31080.03038202439</v>
       </c>
       <c r="E62">
-        <v>10621.6</v>
+        <v>10936.935</v>
       </c>
       <c r="F62">
-        <v>18920.1</v>
+        <v>19235.435</v>
       </c>
       <c r="G62">
         <v>3302.3</v>
@@ -6377,28 +6377,28 @@
         <v>3659.1</v>
       </c>
       <c r="M62">
-        <v>1158.602910916811</v>
+        <v>1177.912959432092</v>
       </c>
       <c r="N62">
-        <v>2500.497089083189</v>
+        <v>2481.187040567908</v>
       </c>
       <c r="O62">
-        <v>625.1242722707972</v>
+        <v>620.2967601419771</v>
       </c>
       <c r="P62">
-        <v>1875.372816812392</v>
+        <v>1860.890280425931</v>
       </c>
       <c r="Q62">
-        <v>3799.672816812391</v>
+        <v>3785.190280425931</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1389869283509454</v>
+        <v>0.1410952298973469</v>
       </c>
       <c r="T62">
-        <v>1.816386682298454</v>
+        <v>1.857481403617424</v>
       </c>
       <c r="U62">
         <v>0.06123661666253409</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.158200247489907</v>
+        <v>3.106426472940892</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08304289178307464</v>
+        <v>0.08293453472763077</v>
       </c>
       <c r="C63">
-        <v>15146.8953820244</v>
+        <v>14922.25064110542</v>
       </c>
       <c r="D63">
-        <v>31080.03038202439</v>
+        <v>31170.72064110542</v>
       </c>
       <c r="E63">
-        <v>10936.935</v>
+        <v>11252.27</v>
       </c>
       <c r="F63">
-        <v>19235.435</v>
+        <v>19550.77</v>
       </c>
       <c r="G63">
         <v>3302.3</v>
@@ -6459,28 +6459,28 @@
         <v>3659.1</v>
       </c>
       <c r="M63">
-        <v>1177.912959432092</v>
+        <v>1197.223007947372</v>
       </c>
       <c r="N63">
-        <v>2481.187040567908</v>
+        <v>2461.876992052628</v>
       </c>
       <c r="O63">
-        <v>620.2967601419771</v>
+        <v>615.4692480131571</v>
       </c>
       <c r="P63">
-        <v>1860.890280425931</v>
+        <v>1846.407744039471</v>
       </c>
       <c r="Q63">
-        <v>3785.190280425931</v>
+        <v>3770.707744039471</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1410952298973469</v>
+        <v>0.1433144946830327</v>
       </c>
       <c r="T63">
-        <v>1.857481403617424</v>
+        <v>1.900739005005813</v>
       </c>
       <c r="U63">
         <v>0.06123661666253409</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.106426472940892</v>
+        <v>3.056322820151523</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08293453472763077</v>
+        <v>0.08282617767218689</v>
       </c>
       <c r="C64">
-        <v>14922.25064110542</v>
+        <v>14698.13671001071</v>
       </c>
       <c r="D64">
-        <v>31170.72064110542</v>
+        <v>31261.94171001071</v>
       </c>
       <c r="E64">
-        <v>11252.27</v>
+        <v>11567.605</v>
       </c>
       <c r="F64">
-        <v>19550.77</v>
+        <v>19866.105</v>
       </c>
       <c r="G64">
         <v>3302.3</v>
@@ -6541,28 +6541,28 @@
         <v>3659.1</v>
       </c>
       <c r="M64">
-        <v>1197.223007947372</v>
+        <v>1216.533056462652</v>
       </c>
       <c r="N64">
-        <v>2461.876992052628</v>
+        <v>2442.566943537348</v>
       </c>
       <c r="O64">
-        <v>615.4692480131571</v>
+        <v>610.6417358843371</v>
       </c>
       <c r="P64">
-        <v>1846.407744039471</v>
+        <v>1831.925207653011</v>
       </c>
       <c r="Q64">
-        <v>3770.707744039471</v>
+        <v>3756.225207653011</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1433144946830327</v>
+        <v>0.1456537197274042</v>
       </c>
       <c r="T64">
-        <v>1.900739005005813</v>
+        <v>1.946334855117898</v>
       </c>
       <c r="U64">
         <v>0.06123661666253409</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.056322820151523</v>
+        <v>3.007809759514197</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08282617767218689</v>
+        <v>0.08391782061674302</v>
       </c>
       <c r="C65">
-        <v>14698.13671001071</v>
+        <v>13487.50188571099</v>
       </c>
       <c r="D65">
-        <v>31261.94171001071</v>
+        <v>30366.64188571099</v>
       </c>
       <c r="E65">
-        <v>11567.605</v>
+        <v>11882.94</v>
       </c>
       <c r="F65">
-        <v>19866.105</v>
+        <v>20181.44</v>
       </c>
       <c r="G65">
         <v>3302.3</v>
@@ -6623,45 +6623,45 @@
         <v>3659.1</v>
       </c>
       <c r="M65">
-        <v>1216.533056462652</v>
+        <v>1286.296704977932</v>
       </c>
       <c r="N65">
-        <v>2442.566943537348</v>
+        <v>2372.803295022068</v>
       </c>
       <c r="O65">
-        <v>610.6417358843371</v>
+        <v>593.2008237555169</v>
       </c>
       <c r="P65">
-        <v>1831.925207653011</v>
+        <v>1779.602471266551</v>
       </c>
       <c r="Q65">
-        <v>3756.225207653011</v>
+        <v>3703.90247126655</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1456537197274042</v>
+        <v>0.1481229017186852</v>
       </c>
       <c r="T65">
-        <v>1.946334855117898</v>
+        <v>1.994463808013989</v>
       </c>
       <c r="U65">
-        <v>0.06123661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.04592746249690056</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.007809759514197</v>
+        <v>2.844678048104598</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08391782061674302</v>
+        <v>0.08382821356129916</v>
       </c>
       <c r="C66">
-        <v>13487.50188571099</v>
+        <v>13243.72074292046</v>
       </c>
       <c r="D66">
-        <v>30366.64188571099</v>
+        <v>30438.19574292047</v>
       </c>
       <c r="E66">
-        <v>11882.94</v>
+        <v>12198.275</v>
       </c>
       <c r="F66">
-        <v>20181.44</v>
+        <v>20496.775</v>
       </c>
       <c r="G66">
         <v>3302.3</v>
@@ -6705,28 +6705,28 @@
         <v>3659.1</v>
       </c>
       <c r="M66">
-        <v>1286.296704977932</v>
+        <v>1306.395090993212</v>
       </c>
       <c r="N66">
-        <v>2372.803295022068</v>
+        <v>2352.704909006788</v>
       </c>
       <c r="O66">
-        <v>593.2008237555169</v>
+        <v>588.1762272516969</v>
       </c>
       <c r="P66">
-        <v>1779.602471266551</v>
+        <v>1764.528681755091</v>
       </c>
       <c r="Q66">
-        <v>3703.90247126655</v>
+        <v>3688.828681755091</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1481229017186852</v>
+        <v>0.1507331798237537</v>
       </c>
       <c r="T66">
-        <v>1.994463808013989</v>
+        <v>2.045342986789856</v>
       </c>
       <c r="U66">
         <v>0.06373661666253409</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.844678048104598</v>
+        <v>2.800913770441451</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08382821356129916</v>
+        <v>0.08373860650585528</v>
       </c>
       <c r="C67">
-        <v>13243.72074292046</v>
+        <v>13000.27760571534</v>
       </c>
       <c r="D67">
-        <v>30438.19574292047</v>
+        <v>30510.08760571534</v>
       </c>
       <c r="E67">
-        <v>12198.275</v>
+        <v>12513.61</v>
       </c>
       <c r="F67">
-        <v>20496.775</v>
+        <v>20812.11</v>
       </c>
       <c r="G67">
         <v>3302.3</v>
@@ -6787,28 +6787,28 @@
         <v>3659.1</v>
       </c>
       <c r="M67">
-        <v>1306.395090993212</v>
+        <v>1326.493477008492</v>
       </c>
       <c r="N67">
-        <v>2352.704909006788</v>
+        <v>2332.606522991508</v>
       </c>
       <c r="O67">
-        <v>588.1762272516969</v>
+        <v>583.1516307478769</v>
       </c>
       <c r="P67">
-        <v>1764.528681755091</v>
+        <v>1749.454892243631</v>
       </c>
       <c r="Q67">
-        <v>3688.828681755091</v>
+        <v>3673.75489224363</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1507331798237537</v>
+        <v>0.1534970036997086</v>
       </c>
       <c r="T67">
-        <v>2.045342986789856</v>
+        <v>2.099215058434892</v>
       </c>
       <c r="U67">
         <v>0.06373661666253409</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.800913770441451</v>
+        <v>2.758475683010519</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08373860650585528</v>
+        <v>0.0836489994504114</v>
       </c>
       <c r="C68">
-        <v>13000.27760571534</v>
+        <v>12757.17487476818</v>
       </c>
       <c r="D68">
-        <v>30510.08760571534</v>
+        <v>30582.31987476817</v>
       </c>
       <c r="E68">
-        <v>12513.61</v>
+        <v>12828.945</v>
       </c>
       <c r="F68">
-        <v>20812.11</v>
+        <v>21127.445</v>
       </c>
       <c r="G68">
         <v>3302.3</v>
@@ -6869,28 +6869,28 @@
         <v>3659.1</v>
       </c>
       <c r="M68">
-        <v>1326.493477008492</v>
+        <v>1346.591863023773</v>
       </c>
       <c r="N68">
-        <v>2332.606522991508</v>
+        <v>2312.508136976227</v>
       </c>
       <c r="O68">
-        <v>583.1516307478769</v>
+        <v>578.1270342440569</v>
       </c>
       <c r="P68">
-        <v>1749.454892243631</v>
+        <v>1734.381102732171</v>
       </c>
       <c r="Q68">
-        <v>3673.75489224363</v>
+        <v>3658.68110273217</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1534970036997086</v>
+        <v>0.156428332052994</v>
       </c>
       <c r="T68">
-        <v>2.099215058434892</v>
+        <v>2.156352104119021</v>
       </c>
       <c r="U68">
         <v>0.06373661666253409</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.758475683010519</v>
+        <v>2.717304404159616</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0836489994504114</v>
+        <v>0.08355939239496754</v>
       </c>
       <c r="C69">
-        <v>12757.17487476818</v>
+        <v>12514.41497353978</v>
       </c>
       <c r="D69">
-        <v>30582.31987476817</v>
+        <v>30654.89497353978</v>
       </c>
       <c r="E69">
-        <v>12828.945</v>
+        <v>13144.28</v>
       </c>
       <c r="F69">
-        <v>21127.445</v>
+        <v>21442.78</v>
       </c>
       <c r="G69">
         <v>3302.3</v>
@@ -6951,28 +6951,28 @@
         <v>3659.1</v>
       </c>
       <c r="M69">
-        <v>1346.591863023773</v>
+        <v>1366.690249039053</v>
       </c>
       <c r="N69">
-        <v>2312.508136976227</v>
+        <v>2292.409750960947</v>
       </c>
       <c r="O69">
-        <v>578.1270342440569</v>
+        <v>573.1024377402367</v>
       </c>
       <c r="P69">
-        <v>1734.381102732171</v>
+        <v>1719.30731322071</v>
       </c>
       <c r="Q69">
-        <v>3658.68110273217</v>
+        <v>3643.60731322071</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.156428332052994</v>
+        <v>0.1595428684283599</v>
       </c>
       <c r="T69">
-        <v>2.156352104119021</v>
+        <v>2.217060215158408</v>
       </c>
       <c r="U69">
         <v>0.06373661666253409</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.717304404159616</v>
+        <v>2.677344045274916</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08355939239496754</v>
+        <v>0.08346978533952366</v>
       </c>
       <c r="C70">
-        <v>12514.41497353978</v>
+        <v>12272.0003485502</v>
       </c>
       <c r="D70">
-        <v>30654.89497353978</v>
+        <v>30727.8153485502</v>
       </c>
       <c r="E70">
-        <v>13144.28</v>
+        <v>13459.615</v>
       </c>
       <c r="F70">
-        <v>21442.78</v>
+        <v>21758.115</v>
       </c>
       <c r="G70">
         <v>3302.3</v>
@@ -7033,28 +7033,28 @@
         <v>3659.1</v>
       </c>
       <c r="M70">
-        <v>1366.690249039053</v>
+        <v>1386.788635054333</v>
       </c>
       <c r="N70">
-        <v>2292.409750960947</v>
+        <v>2272.311364945667</v>
       </c>
       <c r="O70">
-        <v>573.1024377402367</v>
+        <v>568.0778412364167</v>
       </c>
       <c r="P70">
-        <v>1719.30731322071</v>
+        <v>1704.23352370925</v>
       </c>
       <c r="Q70">
-        <v>3643.60731322071</v>
+        <v>3628.53352370925</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1595428684283599</v>
+        <v>0.1628583426343944</v>
       </c>
       <c r="T70">
-        <v>2.217060215158408</v>
+        <v>2.281684978522916</v>
       </c>
       <c r="U70">
         <v>0.06373661666253409</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.677344045274916</v>
+        <v>2.638541957662236</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08346978533952366</v>
+        <v>0.08338017828407979</v>
       </c>
       <c r="C71">
-        <v>12272.0003485502</v>
+        <v>12029.93346965364</v>
       </c>
       <c r="D71">
-        <v>30727.8153485502</v>
+        <v>30801.08346965363</v>
       </c>
       <c r="E71">
-        <v>13459.615</v>
+        <v>13774.95</v>
       </c>
       <c r="F71">
-        <v>21758.115</v>
+        <v>22073.45</v>
       </c>
       <c r="G71">
         <v>3302.3</v>
@@ -7115,28 +7115,28 @@
         <v>3659.1</v>
       </c>
       <c r="M71">
-        <v>1386.788635054333</v>
+        <v>1406.887021069613</v>
       </c>
       <c r="N71">
-        <v>2272.311364945667</v>
+        <v>2252.212978930387</v>
       </c>
       <c r="O71">
-        <v>568.0778412364167</v>
+        <v>563.0532447325967</v>
       </c>
       <c r="P71">
-        <v>1704.23352370925</v>
+        <v>1689.15973419779</v>
       </c>
       <c r="Q71">
-        <v>3628.53352370925</v>
+        <v>3613.45973419779</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1628583426343944</v>
+        <v>0.1663948484541647</v>
       </c>
       <c r="T71">
-        <v>2.281684978522916</v>
+        <v>2.350618059445059</v>
       </c>
       <c r="U71">
         <v>0.06373661666253409</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.638541957662236</v>
+        <v>2.600848501124204</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08338017828407979</v>
+        <v>0.08329057122863592</v>
       </c>
       <c r="C72">
-        <v>12029.93346965364</v>
+        <v>11788.21683031729</v>
       </c>
       <c r="D72">
-        <v>30801.08346965363</v>
+        <v>30874.70183031729</v>
       </c>
       <c r="E72">
-        <v>13774.95</v>
+        <v>14090.285</v>
       </c>
       <c r="F72">
-        <v>22073.45</v>
+        <v>22388.785</v>
       </c>
       <c r="G72">
         <v>3302.3</v>
@@ -7197,28 +7197,28 @@
         <v>3659.1</v>
       </c>
       <c r="M72">
-        <v>1406.887021069613</v>
+        <v>1426.985407084893</v>
       </c>
       <c r="N72">
-        <v>2252.212978930387</v>
+        <v>2232.114592915106</v>
       </c>
       <c r="O72">
-        <v>563.0532447325967</v>
+        <v>558.0286482287765</v>
       </c>
       <c r="P72">
-        <v>1689.15973419779</v>
+        <v>1674.08594468633</v>
       </c>
       <c r="Q72">
-        <v>3613.45973419779</v>
+        <v>3598.385944686329</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1663948484541647</v>
+        <v>0.1701752512270225</v>
       </c>
       <c r="T72">
-        <v>2.350618059445059</v>
+        <v>2.424305145948039</v>
       </c>
       <c r="U72">
         <v>0.06373661666253409</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.600848501124204</v>
+        <v>2.564216832094285</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08329057122863592</v>
+        <v>0.08320096417319206</v>
       </c>
       <c r="C73">
-        <v>11788.21683031729</v>
+        <v>11546.85294790429</v>
       </c>
       <c r="D73">
-        <v>30874.70183031729</v>
+        <v>30948.67294790429</v>
       </c>
       <c r="E73">
-        <v>14090.285</v>
+        <v>14405.62</v>
       </c>
       <c r="F73">
-        <v>22388.785</v>
+        <v>22704.12</v>
       </c>
       <c r="G73">
         <v>3302.3</v>
@@ -7279,28 +7279,28 @@
         <v>3659.1</v>
       </c>
       <c r="M73">
-        <v>1426.985407084893</v>
+        <v>1447.083793100174</v>
       </c>
       <c r="N73">
-        <v>2232.114592915107</v>
+        <v>2212.016206899826</v>
       </c>
       <c r="O73">
-        <v>558.0286482287767</v>
+        <v>553.0040517249565</v>
       </c>
       <c r="P73">
-        <v>1674.08594468633</v>
+        <v>1659.01215517487</v>
       </c>
       <c r="Q73">
-        <v>3598.38594468633</v>
+        <v>3583.312155174869</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1701752512270225</v>
+        <v>0.1742256827693701</v>
       </c>
       <c r="T73">
-        <v>2.424305145948038</v>
+        <v>2.503255595772659</v>
       </c>
       <c r="U73">
         <v>0.06373661666253409</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.564216832094286</v>
+        <v>2.528602709426309</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08320096417319206</v>
+        <v>0.08502760711774818</v>
       </c>
       <c r="C74">
-        <v>11546.85294790429</v>
+        <v>9790.385560859282</v>
       </c>
       <c r="D74">
-        <v>30948.67294790429</v>
+        <v>29507.54056085928</v>
       </c>
       <c r="E74">
-        <v>14405.62</v>
+        <v>14720.955</v>
       </c>
       <c r="F74">
-        <v>22704.12</v>
+        <v>23019.455</v>
       </c>
       <c r="G74">
         <v>3302.3</v>
@@ -7361,45 +7361,45 @@
         <v>3659.1</v>
       </c>
       <c r="M74">
-        <v>1447.083793100174</v>
+        <v>1547.750271615453</v>
       </c>
       <c r="N74">
-        <v>2212.016206899826</v>
+        <v>2111.349728384546</v>
       </c>
       <c r="O74">
-        <v>553.0040517249565</v>
+        <v>527.8374320961366</v>
       </c>
       <c r="P74">
-        <v>1659.01215517487</v>
+        <v>1583.51229628841</v>
       </c>
       <c r="Q74">
-        <v>3583.312155174869</v>
+        <v>3507.812296288409</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1742256827693701</v>
+        <v>0.1785761462778176</v>
       </c>
       <c r="T74">
-        <v>2.503255595772659</v>
+        <v>2.588054227065771</v>
       </c>
       <c r="U74">
-        <v>0.06373661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690056</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.528602709426309</v>
+        <v>2.364141080835243</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08502760711774818</v>
+        <v>0.08496425006230429</v>
       </c>
       <c r="C75">
-        <v>9790.385560859282</v>
+        <v>9522.785698908723</v>
       </c>
       <c r="D75">
-        <v>29507.54056085928</v>
+        <v>29555.27569890872</v>
       </c>
       <c r="E75">
-        <v>14720.955</v>
+        <v>15036.29</v>
       </c>
       <c r="F75">
-        <v>23019.455</v>
+        <v>23334.79</v>
       </c>
       <c r="G75">
         <v>3302.3</v>
@@ -7443,28 +7443,28 @@
         <v>3659.1</v>
       </c>
       <c r="M75">
-        <v>1547.750271615453</v>
+        <v>1568.952330130734</v>
       </c>
       <c r="N75">
-        <v>2111.349728384546</v>
+        <v>2090.147669869266</v>
       </c>
       <c r="O75">
-        <v>527.8374320961366</v>
+        <v>522.5369174673165</v>
       </c>
       <c r="P75">
-        <v>1583.51229628841</v>
+        <v>1567.610752401949</v>
       </c>
       <c r="Q75">
-        <v>3507.812296288409</v>
+        <v>3491.910752401949</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1785761462778176</v>
+        <v>0.1832612608253765</v>
       </c>
       <c r="T75">
-        <v>2.588054227065771</v>
+        <v>2.679375829996814</v>
       </c>
       <c r="U75">
         <v>0.06723661666253408</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.364141080835243</v>
+        <v>2.332193228391524</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08496425006230429</v>
+        <v>0.08490089300686043</v>
       </c>
       <c r="C76">
-        <v>9522.785698908723</v>
+        <v>9255.340532033137</v>
       </c>
       <c r="D76">
-        <v>29555.27569890872</v>
+        <v>29603.16553203314</v>
       </c>
       <c r="E76">
-        <v>15036.29</v>
+        <v>15351.625</v>
       </c>
       <c r="F76">
-        <v>23334.79</v>
+        <v>23650.125</v>
       </c>
       <c r="G76">
         <v>3302.3</v>
@@ -7525,28 +7525,28 @@
         <v>3659.1</v>
       </c>
       <c r="M76">
-        <v>1568.952330130734</v>
+        <v>1590.154388646014</v>
       </c>
       <c r="N76">
-        <v>2090.147669869266</v>
+        <v>2068.945611353986</v>
       </c>
       <c r="O76">
-        <v>522.5369174673165</v>
+        <v>517.2364028384966</v>
       </c>
       <c r="P76">
-        <v>1567.610752401949</v>
+        <v>1551.70920851549</v>
       </c>
       <c r="Q76">
-        <v>3491.910752401949</v>
+        <v>3476.009208515489</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1832612608253765</v>
+        <v>0.18832118453674</v>
       </c>
       <c r="T76">
-        <v>2.679375829996814</v>
+        <v>2.778003161162341</v>
       </c>
       <c r="U76">
         <v>0.06723661666253408</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.332193228391524</v>
+        <v>2.301097318679637</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08490089300686043</v>
+        <v>0.08483753595141655</v>
       </c>
       <c r="C77">
-        <v>9255.340532033137</v>
+        <v>8988.050813432608</v>
       </c>
       <c r="D77">
-        <v>29603.16553203314</v>
+        <v>29651.2108134326</v>
       </c>
       <c r="E77">
-        <v>15351.625</v>
+        <v>15666.96</v>
       </c>
       <c r="F77">
-        <v>23650.125</v>
+        <v>23965.46</v>
       </c>
       <c r="G77">
         <v>3302.3</v>
@@ -7607,28 +7607,28 @@
         <v>3659.1</v>
       </c>
       <c r="M77">
-        <v>1590.154388646014</v>
+        <v>1611.356447161294</v>
       </c>
       <c r="N77">
-        <v>2068.945611353986</v>
+        <v>2047.743552838706</v>
       </c>
       <c r="O77">
-        <v>517.2364028384966</v>
+        <v>511.9358882096765</v>
       </c>
       <c r="P77">
-        <v>1551.70920851549</v>
+        <v>1535.807664629029</v>
       </c>
       <c r="Q77">
-        <v>3476.009208515489</v>
+        <v>3460.107664629029</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.18832118453674</v>
+        <v>0.1938027685573839</v>
       </c>
       <c r="T77">
-        <v>2.778003161162341</v>
+        <v>2.884849436591662</v>
       </c>
       <c r="U77">
         <v>0.06723661666253408</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.301097318679637</v>
+        <v>2.270819722381221</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08483753595141655</v>
+        <v>0.0863911788959727</v>
       </c>
       <c r="C78">
-        <v>8988.050813432608</v>
+        <v>7537.804344221564</v>
       </c>
       <c r="D78">
-        <v>29651.2108134326</v>
+        <v>28516.29934422157</v>
       </c>
       <c r="E78">
-        <v>15666.96</v>
+        <v>15982.295</v>
       </c>
       <c r="F78">
-        <v>23965.46</v>
+        <v>24280.795</v>
       </c>
       <c r="G78">
         <v>3302.3</v>
@@ -7689,45 +7689,45 @@
         <v>3659.1</v>
       </c>
       <c r="M78">
-        <v>1611.356447161294</v>
+        <v>1700.544731676575</v>
       </c>
       <c r="N78">
-        <v>2047.743552838706</v>
+        <v>1958.555268323425</v>
       </c>
       <c r="O78">
-        <v>511.9358882096765</v>
+        <v>489.6388170808563</v>
       </c>
       <c r="P78">
-        <v>1535.807664629029</v>
+        <v>1468.916451242569</v>
       </c>
       <c r="Q78">
-        <v>3460.107664629029</v>
+        <v>3393.216451242569</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1938027685573839</v>
+        <v>0.1997610120580837</v>
       </c>
       <c r="T78">
-        <v>2.884849436591662</v>
+        <v>3.000986692493098</v>
       </c>
       <c r="U78">
-        <v>0.06723661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.05042746249690056</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.270819722381221</v>
+        <v>2.151722287476953</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0863911788959727</v>
+        <v>0.08634882184052883</v>
       </c>
       <c r="C79">
-        <v>7537.804344221564</v>
+        <v>7252.257299026445</v>
       </c>
       <c r="D79">
-        <v>28516.29934422157</v>
+        <v>28546.08729902645</v>
       </c>
       <c r="E79">
-        <v>15982.295</v>
+        <v>16297.63</v>
       </c>
       <c r="F79">
-        <v>24280.795</v>
+        <v>24596.13</v>
       </c>
       <c r="G79">
         <v>3302.3</v>
@@ -7771,28 +7771,28 @@
         <v>3659.1</v>
       </c>
       <c r="M79">
-        <v>1700.544731676575</v>
+        <v>1722.629728191855</v>
       </c>
       <c r="N79">
-        <v>1958.555268323425</v>
+        <v>1936.470271808145</v>
       </c>
       <c r="O79">
-        <v>489.6388170808563</v>
+        <v>484.1175679520363</v>
       </c>
       <c r="P79">
-        <v>1468.916451242569</v>
+        <v>1452.352703856109</v>
       </c>
       <c r="Q79">
-        <v>3393.216451242569</v>
+        <v>3376.652703856108</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1997610120580837</v>
+        <v>0.2062609140588472</v>
       </c>
       <c r="T79">
-        <v>3.000986692493098</v>
+        <v>3.127681880749209</v>
       </c>
       <c r="U79">
         <v>0.07003661666253409</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.151722287476953</v>
+        <v>2.124136104304172</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08634882184052883</v>
+        <v>0.08630646478508497</v>
       </c>
       <c r="C80">
-        <v>7252.257299026445</v>
+        <v>6966.772551544054</v>
       </c>
       <c r="D80">
-        <v>28546.08729902645</v>
+        <v>28575.93755154406</v>
       </c>
       <c r="E80">
-        <v>16297.63</v>
+        <v>16612.965</v>
       </c>
       <c r="F80">
-        <v>24596.13</v>
+        <v>24911.465</v>
       </c>
       <c r="G80">
         <v>3302.3</v>
@@ -7853,28 +7853,28 @@
         <v>3659.1</v>
       </c>
       <c r="M80">
-        <v>1722.629728191855</v>
+        <v>1744.714724707135</v>
       </c>
       <c r="N80">
-        <v>1936.470271808145</v>
+        <v>1914.385275292865</v>
       </c>
       <c r="O80">
-        <v>484.1175679520363</v>
+        <v>478.5963188232163</v>
       </c>
       <c r="P80">
-        <v>1452.352703856109</v>
+        <v>1435.788956469649</v>
       </c>
       <c r="Q80">
-        <v>3376.652703856108</v>
+        <v>3360.088956469649</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2062609140588472</v>
+        <v>0.2133798543453977</v>
       </c>
       <c r="T80">
-        <v>3.127681880749209</v>
+        <v>3.266443277410666</v>
       </c>
       <c r="U80">
         <v>0.07003661666253409</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.124136104304172</v>
+        <v>2.097248305515511</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08630646478508497</v>
+        <v>0.08626410772964108</v>
       </c>
       <c r="C81">
-        <v>6966.772551544054</v>
+        <v>6681.350297410569</v>
       </c>
       <c r="D81">
-        <v>28575.93755154406</v>
+        <v>28605.85029741057</v>
       </c>
       <c r="E81">
-        <v>16612.965</v>
+        <v>16928.3</v>
       </c>
       <c r="F81">
-        <v>24911.465</v>
+        <v>25226.8</v>
       </c>
       <c r="G81">
         <v>3302.3</v>
@@ -7935,28 +7935,28 @@
         <v>3659.1</v>
       </c>
       <c r="M81">
-        <v>1744.714724707135</v>
+        <v>1766.799721222415</v>
       </c>
       <c r="N81">
-        <v>1914.385275292865</v>
+        <v>1892.300278777585</v>
       </c>
       <c r="O81">
-        <v>478.5963188232163</v>
+        <v>473.0750696943962</v>
       </c>
       <c r="P81">
-        <v>1435.788956469649</v>
+        <v>1419.225209083188</v>
       </c>
       <c r="Q81">
-        <v>3360.088956469649</v>
+        <v>3343.525209083188</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2133798543453977</v>
+        <v>0.2212106886606032</v>
       </c>
       <c r="T81">
-        <v>3.266443277410666</v>
+        <v>3.419080813738267</v>
       </c>
       <c r="U81">
         <v>0.07003661666253409</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.097248305515511</v>
+        <v>2.071032701696567</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08626410772964108</v>
+        <v>0.08622175067419721</v>
       </c>
       <c r="C82">
-        <v>6681.350297410569</v>
+        <v>6395.99073308213</v>
       </c>
       <c r="D82">
-        <v>28605.85029741057</v>
+        <v>28635.82573308213</v>
       </c>
       <c r="E82">
-        <v>16928.3</v>
+        <v>17243.635</v>
       </c>
       <c r="F82">
-        <v>25226.8</v>
+        <v>25542.135</v>
       </c>
       <c r="G82">
         <v>3302.3</v>
@@ -8017,28 +8017,28 @@
         <v>3659.1</v>
       </c>
       <c r="M82">
-        <v>1766.799721222415</v>
+        <v>1788.884717737695</v>
       </c>
       <c r="N82">
-        <v>1892.300278777585</v>
+        <v>1870.215282262305</v>
       </c>
       <c r="O82">
-        <v>473.0750696943962</v>
+        <v>467.5538205655761</v>
       </c>
       <c r="P82">
-        <v>1419.225209083188</v>
+        <v>1402.661461696728</v>
       </c>
       <c r="Q82">
-        <v>3343.525209083188</v>
+        <v>3326.961461696728</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2212106886606032</v>
+        <v>0.2298658213247777</v>
       </c>
       <c r="T82">
-        <v>3.419080813738267</v>
+        <v>3.587785459152984</v>
       </c>
       <c r="U82">
         <v>0.07003661666253409</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.071032701696567</v>
+        <v>2.04546439673735</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08622175067419721</v>
+        <v>0.08617939361875335</v>
       </c>
       <c r="C83">
-        <v>6395.99073308213</v>
+        <v>6110.694055839249</v>
       </c>
       <c r="D83">
-        <v>28635.82573308213</v>
+        <v>28665.86405583925</v>
       </c>
       <c r="E83">
-        <v>17243.635</v>
+        <v>17558.97</v>
       </c>
       <c r="F83">
-        <v>25542.135</v>
+        <v>25857.47</v>
       </c>
       <c r="G83">
         <v>3302.3</v>
@@ -8099,28 +8099,28 @@
         <v>3659.1</v>
       </c>
       <c r="M83">
-        <v>1788.884717737695</v>
+        <v>1810.969714252976</v>
       </c>
       <c r="N83">
-        <v>1870.215282262305</v>
+        <v>1848.130285747024</v>
       </c>
       <c r="O83">
-        <v>467.5538205655761</v>
+        <v>462.0325714367561</v>
       </c>
       <c r="P83">
-        <v>1402.661461696728</v>
+        <v>1386.097714310268</v>
       </c>
       <c r="Q83">
-        <v>3326.961461696728</v>
+        <v>3310.397714310268</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2298658213247777</v>
+        <v>0.2394826353960827</v>
       </c>
       <c r="T83">
-        <v>3.587785459152984</v>
+        <v>3.775235065169336</v>
       </c>
       <c r="U83">
         <v>0.07003661666253409</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.04546439673735</v>
+        <v>2.020519708972261</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08617939361875335</v>
+        <v>0.09099253656330947</v>
       </c>
       <c r="C84">
-        <v>6110.694055839249</v>
+        <v>2742.357126268784</v>
       </c>
       <c r="D84">
-        <v>28665.86405583925</v>
+        <v>25612.86212626879</v>
       </c>
       <c r="E84">
-        <v>17558.97</v>
+        <v>17874.305</v>
       </c>
       <c r="F84">
-        <v>25857.47</v>
+        <v>26172.805</v>
       </c>
       <c r="G84">
         <v>3302.3</v>
@@ -8181,45 +8181,45 @@
         <v>3659.1</v>
       </c>
       <c r="M84">
-        <v>1810.969714252976</v>
+        <v>2037.202589768256</v>
       </c>
       <c r="N84">
-        <v>1848.130285747024</v>
+        <v>1621.897410231744</v>
       </c>
       <c r="O84">
-        <v>462.0325714367561</v>
+        <v>405.4743525579361</v>
       </c>
       <c r="P84">
-        <v>1386.097714310268</v>
+        <v>1216.423057673808</v>
       </c>
       <c r="Q84">
-        <v>3310.397714310268</v>
+        <v>3140.723057673808</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2394826353960827</v>
+        <v>0.2502308393581295</v>
       </c>
       <c r="T84">
-        <v>3.775235065169336</v>
+        <v>3.984737566011143</v>
       </c>
       <c r="U84">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V84">
         <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.05252746249690057</v>
+        <v>0.05837746249690056</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.020519708972261</v>
+        <v>1.796139479881697</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09099253656330947</v>
+        <v>0.09100867950786559</v>
       </c>
       <c r="C85">
-        <v>2742.357126268784</v>
+        <v>2417.87638218316</v>
       </c>
       <c r="D85">
-        <v>25612.86212626879</v>
+        <v>25603.71638218316</v>
       </c>
       <c r="E85">
-        <v>17874.305</v>
+        <v>18189.64</v>
       </c>
       <c r="F85">
-        <v>26172.805</v>
+        <v>26488.14</v>
       </c>
       <c r="G85">
         <v>3302.3</v>
@@ -8263,28 +8263,28 @@
         <v>3659.1</v>
       </c>
       <c r="M85">
-        <v>2037.202589768256</v>
+        <v>2061.747199283536</v>
       </c>
       <c r="N85">
-        <v>1621.897410231744</v>
+        <v>1597.352800716464</v>
       </c>
       <c r="O85">
-        <v>405.4743525579361</v>
+        <v>399.338200179116</v>
       </c>
       <c r="P85">
-        <v>1216.423057673808</v>
+        <v>1198.014600537348</v>
       </c>
       <c r="Q85">
-        <v>3140.723057673808</v>
+        <v>3122.314600537348</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2502308393581295</v>
+        <v>0.2623225688154321</v>
       </c>
       <c r="T85">
-        <v>3.984737566011143</v>
+        <v>4.220427879458175</v>
       </c>
       <c r="U85">
         <v>0.07783661666253408</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.796139479881697</v>
+        <v>1.774756867025962</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09100867950786559</v>
+        <v>0.09102482245242172</v>
       </c>
       <c r="C86">
-        <v>2417.876382183164</v>
+        <v>2093.402167221662</v>
       </c>
       <c r="D86">
-        <v>25603.71638218316</v>
+        <v>25594.57716722166</v>
       </c>
       <c r="E86">
-        <v>18189.64</v>
+        <v>18504.975</v>
       </c>
       <c r="F86">
-        <v>26488.14</v>
+        <v>26803.475</v>
       </c>
       <c r="G86">
         <v>3302.3</v>
@@ -8345,28 +8345,28 @@
         <v>3659.1</v>
       </c>
       <c r="M86">
-        <v>2061.747199283535</v>
+        <v>2086.291808798816</v>
       </c>
       <c r="N86">
-        <v>1597.352800716465</v>
+        <v>1572.808191201184</v>
       </c>
       <c r="O86">
-        <v>399.3382001791161</v>
+        <v>393.2020478002961</v>
       </c>
       <c r="P86">
-        <v>1198.014600537349</v>
+        <v>1179.606143400888</v>
       </c>
       <c r="Q86">
-        <v>3122.314600537348</v>
+        <v>3103.906143400888</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.262322568815432</v>
+        <v>0.2760265288670416</v>
       </c>
       <c r="T86">
-        <v>4.220427879458172</v>
+        <v>4.487543568031475</v>
       </c>
       <c r="U86">
         <v>0.07783661666253408</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.774756867025963</v>
+        <v>1.753877374472716</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09102482245242172</v>
+        <v>0.09355646539697784</v>
       </c>
       <c r="C87">
-        <v>2093.402167221662</v>
+        <v>421.2596613547248</v>
       </c>
       <c r="D87">
-        <v>25594.57716722166</v>
+        <v>24237.76966135473</v>
       </c>
       <c r="E87">
-        <v>18504.975</v>
+        <v>18820.31</v>
       </c>
       <c r="F87">
-        <v>26803.475</v>
+        <v>27118.81</v>
       </c>
       <c r="G87">
         <v>3302.3</v>
@@ -8427,45 +8427,45 @@
         <v>3659.1</v>
       </c>
       <c r="M87">
-        <v>2086.291808798816</v>
+        <v>2216.599777314096</v>
       </c>
       <c r="N87">
-        <v>1572.808191201184</v>
+        <v>1442.500222685904</v>
       </c>
       <c r="O87">
-        <v>393.2020478002961</v>
+        <v>360.6250556714759</v>
       </c>
       <c r="P87">
-        <v>1179.606143400888</v>
+        <v>1081.875167014428</v>
       </c>
       <c r="Q87">
-        <v>3103.906143400888</v>
+        <v>3006.175167014428</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2760265288670416</v>
+        <v>0.2916881974974526</v>
       </c>
       <c r="T87">
-        <v>4.487543568031475</v>
+        <v>4.792818640686677</v>
       </c>
       <c r="U87">
-        <v>0.07783661666253408</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V87">
         <v>0.25</v>
       </c>
       <c r="W87">
-        <v>0.05837746249690056</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.753877374472716</v>
+        <v>1.65077161761417</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09355646539697784</v>
+        <v>0.09360185834153398</v>
       </c>
       <c r="C88">
-        <v>421.2596613547248</v>
+        <v>82.90832323369978</v>
       </c>
       <c r="D88">
-        <v>24237.76966135473</v>
+        <v>24214.7533232337</v>
       </c>
       <c r="E88">
-        <v>18820.31</v>
+        <v>19135.645</v>
       </c>
       <c r="F88">
-        <v>27118.81</v>
+        <v>27434.145</v>
       </c>
       <c r="G88">
         <v>3302.3</v>
@@ -8509,28 +8509,28 @@
         <v>3659.1</v>
       </c>
       <c r="M88">
-        <v>2216.599777314096</v>
+        <v>2242.374193329376</v>
       </c>
       <c r="N88">
-        <v>1442.500222685904</v>
+        <v>1416.725806670624</v>
       </c>
       <c r="O88">
-        <v>360.6250556714759</v>
+        <v>354.1814516676559</v>
       </c>
       <c r="P88">
-        <v>1081.875167014428</v>
+        <v>1062.544355002968</v>
       </c>
       <c r="Q88">
-        <v>3006.175167014428</v>
+        <v>2986.844355002967</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2916881974974526</v>
+        <v>0.3097593536094653</v>
       </c>
       <c r="T88">
-        <v>4.792818640686677</v>
+        <v>5.145059109134986</v>
       </c>
       <c r="U88">
         <v>0.0817366166625341</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.65077161761417</v>
+        <v>1.631797231204812</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09360185834153398</v>
+        <v>0.09364725128609011</v>
       </c>
       <c r="C89">
-        <v>82.90832323369978</v>
+        <v>-255.3993434398726</v>
       </c>
       <c r="D89">
-        <v>24214.7533232337</v>
+        <v>24191.78065656013</v>
       </c>
       <c r="E89">
-        <v>19135.645</v>
+        <v>19450.98</v>
       </c>
       <c r="F89">
-        <v>27434.145</v>
+        <v>27749.48</v>
       </c>
       <c r="G89">
         <v>3302.3</v>
@@ -8591,28 +8591,28 @@
         <v>3659.1</v>
       </c>
       <c r="M89">
-        <v>2242.374193329376</v>
+        <v>2268.148609344657</v>
       </c>
       <c r="N89">
-        <v>1416.725806670624</v>
+        <v>1390.951390655343</v>
       </c>
       <c r="O89">
-        <v>354.1814516676559</v>
+        <v>347.7378476638359</v>
       </c>
       <c r="P89">
-        <v>1062.544355002968</v>
+        <v>1043.213542991507</v>
       </c>
       <c r="Q89">
-        <v>2986.844355002967</v>
+        <v>2967.513542991507</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3097593536094653</v>
+        <v>0.3308423690734801</v>
       </c>
       <c r="T89">
-        <v>5.145059109134986</v>
+        <v>5.556006322324683</v>
       </c>
       <c r="U89">
         <v>0.0817366166625341</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.631797231204812</v>
+        <v>1.613254080850212</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09364725128609011</v>
+        <v>0.09369264423064624</v>
       </c>
       <c r="C90">
-        <v>-255.3993434398726</v>
+        <v>-593.6634628421925</v>
       </c>
       <c r="D90">
-        <v>24191.78065656013</v>
+        <v>24168.85153715781</v>
       </c>
       <c r="E90">
-        <v>19450.98</v>
+        <v>19766.315</v>
       </c>
       <c r="F90">
-        <v>27749.48</v>
+        <v>28064.815</v>
       </c>
       <c r="G90">
         <v>3302.3</v>
@@ -8673,28 +8673,28 @@
         <v>3659.1</v>
       </c>
       <c r="M90">
-        <v>2268.148609344657</v>
+        <v>2293.923025359937</v>
       </c>
       <c r="N90">
-        <v>1390.951390655343</v>
+        <v>1365.176974640063</v>
       </c>
       <c r="O90">
-        <v>347.7378476638359</v>
+        <v>341.2942436600158</v>
       </c>
       <c r="P90">
-        <v>1043.213542991507</v>
+        <v>1023.882730980047</v>
       </c>
       <c r="Q90">
-        <v>2967.513542991507</v>
+        <v>2948.182730980047</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3308423690734801</v>
+        <v>0.3557586600764067</v>
       </c>
       <c r="T90">
-        <v>5.556006322324683</v>
+        <v>6.041671210639778</v>
       </c>
       <c r="U90">
         <v>0.0817366166625341</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.613254080850212</v>
+        <v>1.59512763050358</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09369264423064624</v>
+        <v>0.09373803717520236</v>
       </c>
       <c r="C91">
-        <v>-593.6634628421925</v>
+        <v>-931.8841586791277</v>
       </c>
       <c r="D91">
-        <v>24168.85153715781</v>
+        <v>24145.96584132087</v>
       </c>
       <c r="E91">
-        <v>19766.315</v>
+        <v>20081.65</v>
       </c>
       <c r="F91">
-        <v>28064.815</v>
+        <v>28380.15</v>
       </c>
       <c r="G91">
         <v>3302.3</v>
@@ -8755,28 +8755,28 @@
         <v>3659.1</v>
       </c>
       <c r="M91">
-        <v>2293.923025359937</v>
+        <v>2319.697441375217</v>
       </c>
       <c r="N91">
-        <v>1365.176974640063</v>
+        <v>1339.402558624783</v>
       </c>
       <c r="O91">
-        <v>341.2942436600158</v>
+        <v>334.8506396561957</v>
       </c>
       <c r="P91">
-        <v>1023.882730980047</v>
+        <v>1004.551918968587</v>
       </c>
       <c r="Q91">
-        <v>2948.182730980047</v>
+        <v>2928.851918968587</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3557586600764067</v>
+        <v>0.3856582092799186</v>
       </c>
       <c r="T91">
-        <v>6.041671210639778</v>
+        <v>6.624469076617892</v>
       </c>
       <c r="U91">
         <v>0.0817366166625341</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.59512763050358</v>
+        <v>1.577403990164651</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09373803717520236</v>
+        <v>0.09378343011975851</v>
       </c>
       <c r="C92">
-        <v>-931.8841586791277</v>
+        <v>-1270.061554188454</v>
       </c>
       <c r="D92">
-        <v>24145.96584132087</v>
+        <v>24123.12344581155</v>
       </c>
       <c r="E92">
-        <v>20081.65</v>
+        <v>20396.985</v>
       </c>
       <c r="F92">
-        <v>28380.15</v>
+        <v>28695.485</v>
       </c>
       <c r="G92">
         <v>3302.3</v>
@@ -8837,28 +8837,28 @@
         <v>3659.1</v>
       </c>
       <c r="M92">
-        <v>2319.697441375217</v>
+        <v>2345.471857390497</v>
       </c>
       <c r="N92">
-        <v>1339.402558624783</v>
+        <v>1313.628142609502</v>
       </c>
       <c r="O92">
-        <v>334.8506396561957</v>
+        <v>328.4070356523756</v>
       </c>
       <c r="P92">
-        <v>1004.551918968587</v>
+        <v>985.2211069571268</v>
       </c>
       <c r="Q92">
-        <v>2928.851918968587</v>
+        <v>2909.521106957126</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3856582092799186</v>
+        <v>0.4222021027508777</v>
       </c>
       <c r="T92">
-        <v>6.624469076617892</v>
+        <v>7.336777579480032</v>
       </c>
       <c r="U92">
         <v>0.0817366166625341</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.577403990164651</v>
+        <v>1.560069880382622</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09378343011975851</v>
+        <v>0.09382882306431463</v>
       </c>
       <c r="C93">
-        <v>-1270.061554188454</v>
+        <v>-1608.195772142008</v>
       </c>
       <c r="D93">
-        <v>24123.12344581155</v>
+        <v>24100.32422785799</v>
       </c>
       <c r="E93">
-        <v>20396.985</v>
+        <v>20712.32</v>
       </c>
       <c r="F93">
-        <v>28695.485</v>
+        <v>29010.82</v>
       </c>
       <c r="G93">
         <v>3302.3</v>
@@ -8919,28 +8919,28 @@
         <v>3659.1</v>
       </c>
       <c r="M93">
-        <v>2345.471857390497</v>
+        <v>2371.246273405777</v>
       </c>
       <c r="N93">
-        <v>1313.628142609502</v>
+        <v>1287.853726594223</v>
       </c>
       <c r="O93">
-        <v>328.4070356523756</v>
+        <v>321.9634316485557</v>
       </c>
       <c r="P93">
-        <v>985.2211069571268</v>
+        <v>965.8902949456671</v>
       </c>
       <c r="Q93">
-        <v>2909.521106957126</v>
+        <v>2890.190294945667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4222021027508777</v>
+        <v>0.4678819695895765</v>
       </c>
       <c r="T93">
-        <v>7.336777579480032</v>
+        <v>8.227163208057707</v>
       </c>
       <c r="U93">
         <v>0.0817366166625341</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.560069880382622</v>
+        <v>1.543112599074116</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09382882306431463</v>
+        <v>0.09387421600887075</v>
       </c>
       <c r="C94">
-        <v>-1608.195772142008</v>
+        <v>-1946.28693484798</v>
       </c>
       <c r="D94">
-        <v>24100.32422785799</v>
+        <v>24077.56806515202</v>
       </c>
       <c r="E94">
-        <v>20712.32</v>
+        <v>21027.655</v>
       </c>
       <c r="F94">
-        <v>29010.82</v>
+        <v>29326.155</v>
       </c>
       <c r="G94">
         <v>3302.3</v>
@@ -9001,28 +9001,28 @@
         <v>3659.1</v>
       </c>
       <c r="M94">
-        <v>2371.246273405777</v>
+        <v>2397.020689421058</v>
       </c>
       <c r="N94">
-        <v>1287.853726594223</v>
+        <v>1262.079310578942</v>
       </c>
       <c r="O94">
-        <v>321.9634316485557</v>
+        <v>315.5198276447355</v>
       </c>
       <c r="P94">
-        <v>965.8902949456671</v>
+        <v>946.5594829342066</v>
       </c>
       <c r="Q94">
-        <v>2890.190294945667</v>
+        <v>2870.859482934206</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4678819695895765</v>
+        <v>0.5266132269536178</v>
       </c>
       <c r="T94">
-        <v>8.227163208057707</v>
+        <v>9.371944730514718</v>
       </c>
       <c r="U94">
         <v>0.0817366166625341</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.543112599074116</v>
+        <v>1.52651999048192</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09387421600887075</v>
+        <v>0.09391960895342688</v>
       </c>
       <c r="C95">
-        <v>-1946.28693484798</v>
+        <v>-2284.335164153017</v>
       </c>
       <c r="D95">
-        <v>24077.56806515202</v>
+        <v>24054.85483584699</v>
       </c>
       <c r="E95">
-        <v>21027.655</v>
+        <v>21342.99</v>
       </c>
       <c r="F95">
-        <v>29326.155</v>
+        <v>29641.49</v>
       </c>
       <c r="G95">
         <v>3302.3</v>
@@ -9083,28 +9083,28 @@
         <v>3659.1</v>
       </c>
       <c r="M95">
-        <v>2397.020689421058</v>
+        <v>2422.795105436338</v>
       </c>
       <c r="N95">
-        <v>1262.079310578942</v>
+        <v>1236.304894563662</v>
       </c>
       <c r="O95">
-        <v>315.5198276447355</v>
+        <v>309.0762236409155</v>
       </c>
       <c r="P95">
-        <v>946.5594829342066</v>
+        <v>927.2286709227465</v>
       </c>
       <c r="Q95">
-        <v>2870.859482934206</v>
+        <v>2851.528670922746</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5266132269536178</v>
+        <v>0.6049215701056729</v>
       </c>
       <c r="T95">
-        <v>9.371944730514718</v>
+        <v>10.89832009379073</v>
       </c>
       <c r="U95">
         <v>0.0817366166625341</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.52651999048192</v>
+        <v>1.510280416115092</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09391960895342688</v>
+        <v>0.104082501897983</v>
       </c>
       <c r="C96">
-        <v>-2284.335164153017</v>
+        <v>-6794.186640495493</v>
       </c>
       <c r="D96">
-        <v>24054.85483584699</v>
+        <v>19860.33835950451</v>
       </c>
       <c r="E96">
-        <v>21342.99</v>
+        <v>21658.325</v>
       </c>
       <c r="F96">
-        <v>29641.49</v>
+        <v>29956.825</v>
       </c>
       <c r="G96">
         <v>3302.3</v>
@@ -9165,45 +9165,45 @@
         <v>3659.1</v>
       </c>
       <c r="M96">
-        <v>2422.795105436338</v>
+        <v>2873.956436451618</v>
       </c>
       <c r="N96">
-        <v>1236.304894563662</v>
+        <v>785.1435635483822</v>
       </c>
       <c r="O96">
-        <v>309.0762236409155</v>
+        <v>196.2858908870955</v>
       </c>
       <c r="P96">
-        <v>927.2286709227465</v>
+        <v>588.8576726612866</v>
       </c>
       <c r="Q96">
-        <v>2851.528670922746</v>
+        <v>2513.157672661287</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6049215701056729</v>
+        <v>0.7145532505185503</v>
       </c>
       <c r="T96">
-        <v>10.89832009379073</v>
+        <v>13.03524560237716</v>
       </c>
       <c r="U96">
-        <v>0.0817366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V96">
         <v>0.25</v>
       </c>
       <c r="W96">
-        <v>0.06130246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y96">
-        <v>1.510280416115092</v>
+        <v>1.273192576474045</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.104082501897983</v>
+        <v>0.1042343948425392</v>
       </c>
       <c r="C97">
-        <v>-6794.186640495493</v>
+        <v>-7161.146120930949</v>
       </c>
       <c r="D97">
-        <v>19860.33835950451</v>
+        <v>19808.71387906906</v>
       </c>
       <c r="E97">
-        <v>21658.325</v>
+        <v>21973.66</v>
       </c>
       <c r="F97">
-        <v>29956.825</v>
+        <v>30272.16</v>
       </c>
       <c r="G97">
         <v>3302.3</v>
@@ -9247,28 +9247,28 @@
         <v>3659.1</v>
       </c>
       <c r="M97">
-        <v>2873.956436451618</v>
+        <v>2904.208609466898</v>
       </c>
       <c r="N97">
-        <v>785.1435635483822</v>
+        <v>754.8913905331019</v>
       </c>
       <c r="O97">
-        <v>196.2858908870955</v>
+        <v>188.7228476332755</v>
       </c>
       <c r="P97">
-        <v>588.8576726612866</v>
+        <v>566.1685428998264</v>
       </c>
       <c r="Q97">
-        <v>2513.157672661287</v>
+        <v>2490.468542899826</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7145532505185503</v>
+        <v>0.8790007711378663</v>
       </c>
       <c r="T97">
-        <v>13.03524560237716</v>
+        <v>16.24063386525679</v>
       </c>
       <c r="U97">
         <v>0.09593661666253409</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.273192576474045</v>
+        <v>1.25993015380244</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1042343948425391</v>
+        <v>0.1268025012303168</v>
       </c>
       <c r="C98">
-        <v>-7161.146120930942</v>
+        <v>-12995.3867773968</v>
       </c>
       <c r="D98">
-        <v>19808.71387906906</v>
+        <v>14289.8082226032</v>
       </c>
       <c r="E98">
-        <v>21973.66</v>
+        <v>22288.995</v>
       </c>
       <c r="F98">
-        <v>30272.16</v>
+        <v>30587.495</v>
       </c>
       <c r="G98">
         <v>3302.3</v>
@@ -9329,45 +9329,45 @@
         <v>3659.1</v>
       </c>
       <c r="M98">
-        <v>2904.208609466898</v>
+        <v>3809.263139482178</v>
       </c>
       <c r="N98">
-        <v>754.8913905331019</v>
+        <v>-150.1631394821784</v>
       </c>
       <c r="O98">
-        <v>188.7228476332755</v>
+        <v>-37.5407848705446</v>
       </c>
       <c r="P98">
-        <v>566.1685428998264</v>
+        <v>-112.6223546116338</v>
       </c>
       <c r="Q98">
-        <v>2490.468542899826</v>
+        <v>1811.677645388366</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8790007711378642</v>
+        <v>1.167053591750588</v>
       </c>
       <c r="T98">
-        <v>16.24063386525675</v>
+        <v>21.85531949143179</v>
       </c>
       <c r="U98">
-        <v>0.09593661666253409</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V98">
-        <v>0.25</v>
+        <v>0.2401448696254552</v>
       </c>
       <c r="W98">
-        <v>0.07195246249690057</v>
+        <v>0.09462978709051455</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>1.25993015380244</v>
+        <v>0.9605794785018209</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1268025012303168</v>
+        <v>0.1275898673969421</v>
       </c>
       <c r="C99">
-        <v>-12995.3867773968</v>
+        <v>-13448.28541309066</v>
       </c>
       <c r="D99">
-        <v>14289.8082226032</v>
+        <v>14152.24458690934</v>
       </c>
       <c r="E99">
-        <v>22288.995</v>
+        <v>22604.33</v>
       </c>
       <c r="F99">
-        <v>30587.495</v>
+        <v>30902.83</v>
       </c>
       <c r="G99">
         <v>3302.3</v>
@@ -9411,37 +9411,37 @@
         <v>3659.1</v>
       </c>
       <c r="M99">
-        <v>3809.263139482178</v>
+        <v>3848.533893497458</v>
       </c>
       <c r="N99">
-        <v>-150.1631394821784</v>
+        <v>-189.4338934974585</v>
       </c>
       <c r="O99">
-        <v>-37.5407848705446</v>
+        <v>-47.35847337436462</v>
       </c>
       <c r="P99">
-        <v>-112.6223546116338</v>
+        <v>-142.0754201230939</v>
       </c>
       <c r="Q99">
-        <v>1811.677645388366</v>
+        <v>1782.224579876906</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.167053591750588</v>
+        <v>1.727680387625881</v>
       </c>
       <c r="T99">
-        <v>21.85531949143179</v>
+        <v>32.78297923714769</v>
       </c>
       <c r="U99">
         <v>0.1245366166625341</v>
       </c>
       <c r="V99">
-        <v>0.2401448696254552</v>
+        <v>0.2376944117721343</v>
       </c>
       <c r="W99">
-        <v>0.09462978709051455</v>
+        <v>0.09493495882084128</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9605794785018209</v>
+        <v>0.9507776470885371</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1275898673969421</v>
+        <v>0.1283772335635674</v>
       </c>
       <c r="C100">
-        <v>-13448.28541309066</v>
+        <v>-13898.56073609097</v>
       </c>
       <c r="D100">
-        <v>14152.24458690934</v>
+        <v>14017.30426390903</v>
       </c>
       <c r="E100">
-        <v>22604.33</v>
+        <v>22919.665</v>
       </c>
       <c r="F100">
-        <v>30902.83</v>
+        <v>31218.165</v>
       </c>
       <c r="G100">
         <v>3302.3</v>
@@ -9493,37 +9493,37 @@
         <v>3659.1</v>
       </c>
       <c r="M100">
-        <v>3848.533893497458</v>
+        <v>3887.804647512739</v>
       </c>
       <c r="N100">
-        <v>-189.4338934974585</v>
+        <v>-228.704647512739</v>
       </c>
       <c r="O100">
-        <v>-47.35847337436462</v>
+        <v>-57.17616187818476</v>
       </c>
       <c r="P100">
-        <v>-142.0754201230939</v>
+        <v>-171.5284856345543</v>
       </c>
       <c r="Q100">
-        <v>1782.224579876906</v>
+        <v>1752.771514365445</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.727680387625881</v>
+        <v>3.409560775251763</v>
       </c>
       <c r="T100">
-        <v>32.78297923714769</v>
+        <v>65.56595847429537</v>
       </c>
       <c r="U100">
         <v>0.1245366166625341</v>
       </c>
       <c r="V100">
-        <v>0.2376944117721343</v>
+        <v>0.2352934581178703</v>
       </c>
       <c r="W100">
-        <v>0.09493495882084128</v>
+        <v>0.09523396546570687</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.9507776470885371</v>
+        <v>0.941173832471481</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1283772335635674</v>
-      </c>
-      <c r="C101">
-        <v>-13898.56073609097</v>
-      </c>
-      <c r="D101">
-        <v>14017.30426390903</v>
-      </c>
-      <c r="E101">
-        <v>22919.665</v>
-      </c>
-      <c r="F101">
-        <v>31218.165</v>
-      </c>
-      <c r="G101">
-        <v>3302.3</v>
-      </c>
-      <c r="H101">
-        <v>23235</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5583.4</v>
-      </c>
-      <c r="K101">
-        <v>1924.3</v>
-      </c>
-      <c r="L101">
-        <v>3659.1</v>
-      </c>
-      <c r="M101">
-        <v>3887.804647512739</v>
-      </c>
-      <c r="N101">
-        <v>-228.704647512739</v>
-      </c>
-      <c r="O101">
-        <v>-57.17616187818476</v>
-      </c>
-      <c r="P101">
-        <v>-171.5284856345543</v>
-      </c>
-      <c r="Q101">
-        <v>1752.771514365445</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.409560775251763</v>
-      </c>
-      <c r="T101">
-        <v>65.56595847429537</v>
-      </c>
-      <c r="U101">
-        <v>0.1245366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.2352934581178703</v>
-      </c>
-      <c r="W101">
-        <v>0.09523396546570687</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.941173832471481</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
